--- a/META_Model.xlsx
+++ b/META_Model.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\OneDrive\Desktop\Equity Research\Models\Communication Services\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9CFA4C9-EE62-448F-B200-0ACE7C01D1BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94D6381D-96AC-493A-AE4C-6C069857806C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -4743,7 +4743,7 @@
     <t>Q3'25</t>
   </si>
   <si>
-    <t>10/31/25</t>
+    <t>12/24/25</t>
   </si>
 </sst>
 </file>
@@ -17256,8 +17256,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>48</xdr:col>
-      <xdr:colOff>603160</xdr:colOff>
+      <xdr:col>49</xdr:col>
+      <xdr:colOff>40822</xdr:colOff>
       <xdr:row>129</xdr:row>
       <xdr:rowOff>2400</xdr:rowOff>
     </xdr:to>
@@ -17282,8 +17282,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="18688050" y="19069050"/>
-          <a:ext cx="6089560" cy="4524375"/>
+          <a:off x="18764250" y="18492107"/>
+          <a:ext cx="6164036" cy="4424722"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -19918,7 +19918,7 @@
         <v>0</v>
       </c>
       <c r="C3" s="68">
-        <v>648.35</v>
+        <v>667.31</v>
       </c>
       <c r="D3" s="42" t="s">
         <v>1533</v>
@@ -19942,7 +19942,7 @@
       </c>
       <c r="C5" s="65">
         <f>C3*C4</f>
-        <v>1631896.95</v>
+        <v>1679619.2699999998</v>
       </c>
     </row>
     <row r="6" spans="2:17">
@@ -19974,7 +19974,7 @@
       </c>
       <c r="C8" s="65">
         <f>C5-C6+C7</f>
-        <v>1616282.95</v>
+        <v>1664005.2699999998</v>
       </c>
       <c r="D8" s="44"/>
     </row>
@@ -20216,6 +20216,9 @@
     <hyperlink ref="Q14" r:id="rId5" xr:uid="{A830EA4F-4102-445A-8955-1CC4FA5A5BE6}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="D3" twoDigitTextYear="1"/>
+  </ignoredErrors>
   <drawing r:id="rId6"/>
 </worksheet>
 </file>
@@ -21336,39 +21339,39 @@
       </c>
       <c r="CC7" s="56">
         <f t="shared" si="6"/>
-        <v>1641.69</v>
+        <v>2280.125</v>
       </c>
       <c r="CD7" s="56">
         <f t="shared" si="6"/>
-        <v>1658.1069</v>
+        <v>2302.92625</v>
       </c>
       <c r="CE7" s="56">
         <f t="shared" si="6"/>
-        <v>1674.6879690000001</v>
+        <v>2325.9555125000002</v>
       </c>
       <c r="CF7" s="56">
         <f t="shared" si="6"/>
-        <v>1758.4223674500001</v>
+        <v>2442.2532881250004</v>
       </c>
       <c r="CG7" s="56">
         <f t="shared" si="6"/>
-        <v>1846.3434858225003</v>
+        <v>2564.3659525312505</v>
       </c>
       <c r="CH7" s="56">
         <f t="shared" si="6"/>
-        <v>1938.6606601136255</v>
+        <v>2692.5842501578131</v>
       </c>
       <c r="CI7" s="56">
         <f t="shared" si="6"/>
-        <v>2035.5936931193069</v>
+        <v>2827.2134626657039</v>
       </c>
       <c r="CJ7" s="56">
         <f t="shared" si="6"/>
-        <v>2137.3733777752723</v>
+        <v>2968.5741357989891</v>
       </c>
       <c r="CK7" s="56">
         <f t="shared" si="6"/>
-        <v>2244.242046664036</v>
+        <v>3117.0028425889386</v>
       </c>
     </row>
     <row r="8" spans="2:142" s="2" customFormat="1" ht="15">
@@ -21498,39 +21501,39 @@
       </c>
       <c r="CC8" s="58">
         <f t="shared" ref="CC8:CK8" si="8">SUM(CC6:CC7)</f>
-        <v>236327.10200000001</v>
+        <v>236965.53700000001</v>
       </c>
       <c r="CD8" s="58">
         <f t="shared" si="8"/>
-        <v>271924.52667200001</v>
+        <v>272569.34602200001</v>
       </c>
       <c r="CE8" s="58">
         <f t="shared" si="8"/>
-        <v>307465.62797704001</v>
+        <v>308116.89552054001</v>
       </c>
       <c r="CF8" s="58">
         <f t="shared" si="8"/>
-        <v>346116.7624685886</v>
+        <v>346800.59338926355</v>
       </c>
       <c r="CG8" s="58">
         <f t="shared" si="8"/>
-        <v>387905.04173872049</v>
+        <v>388623.06420542923</v>
       </c>
       <c r="CH8" s="58">
         <f t="shared" si="8"/>
-        <v>432802.28406778694</v>
+        <v>433556.20765783114</v>
       </c>
       <c r="CI8" s="58">
         <f t="shared" si="8"/>
-        <v>480728.36529487278</v>
+        <v>481519.98506441916</v>
       </c>
       <c r="CJ8" s="58">
         <f t="shared" si="8"/>
-        <v>531546.13820019539</v>
+        <v>532377.33895821904</v>
       </c>
       <c r="CK8" s="58">
         <f t="shared" si="8"/>
-        <v>582468.07956006867</v>
+        <v>583340.8403559936</v>
       </c>
       <c r="CL8" s="34"/>
       <c r="CM8" s="34"/>
@@ -22075,7 +22078,7 @@
         <v>-0.15</v>
       </c>
       <c r="CC13" s="57">
-        <v>-0.1</v>
+        <v>0.25</v>
       </c>
       <c r="CD13" s="57">
         <v>0.01</v>
@@ -22369,39 +22372,39 @@
       </c>
       <c r="CC14" s="66">
         <f t="shared" ref="CC14:CK14" si="20">CC8/CB8-1</f>
-        <v>0.17949978973073444</v>
+        <v>0.18268619510652062</v>
       </c>
       <c r="CD14" s="66">
         <f t="shared" si="20"/>
-        <v>0.15062777129979787</v>
+        <v>0.15024889050427626</v>
       </c>
       <c r="CE14" s="66">
         <f t="shared" si="20"/>
-        <v>0.13070208024269281</v>
+        <v>0.13041653442449408</v>
       </c>
       <c r="CF14" s="66">
         <f t="shared" si="20"/>
-        <v>0.12570879790971246</v>
+        <v>0.12554877201190284</v>
       </c>
       <c r="CG14" s="66">
         <f t="shared" si="20"/>
-        <v>0.12073463004821772</v>
+        <v>0.12059515356486816</v>
       </c>
       <c r="CH14" s="66">
         <f t="shared" si="20"/>
-        <v>0.11574286873875606</v>
+        <v>0.11562140179268909</v>
       </c>
       <c r="CI14" s="66">
         <f t="shared" si="20"/>
-        <v>0.11073435374841845</v>
+        <v>0.11062874100153985</v>
       </c>
       <c r="CJ14" s="66">
         <f t="shared" si="20"/>
-        <v>0.10570995300880903</v>
+        <v>0.1056183657403047</v>
       </c>
       <c r="CK14" s="66">
         <f t="shared" si="20"/>
-        <v>9.5799663849113648E-2</v>
+        <v>9.572815683233693E-2</v>
       </c>
       <c r="CL14" s="34"/>
       <c r="CM14" s="34"/>
@@ -22581,39 +22584,39 @@
       </c>
       <c r="CC16" s="57">
         <f t="shared" si="23"/>
-        <v>0.97850506709975227</v>
+        <v>0.97586876863026717</v>
       </c>
       <c r="CD16" s="57">
         <f t="shared" si="23"/>
-        <v>0.97797120427012652</v>
+        <v>0.97565761044360255</v>
       </c>
       <c r="CE16" s="57">
         <f t="shared" si="23"/>
-        <v>0.97736395831874978</v>
+        <v>0.97529810138752138</v>
       </c>
       <c r="CF16" s="57">
         <f t="shared" si="23"/>
-        <v>0.9767485651265041</v>
+        <v>0.97482258551951795</v>
       </c>
       <c r="CG16" s="57">
         <f t="shared" si="23"/>
-        <v>0.97610831646615481</v>
+        <v>0.97430485247824938</v>
       </c>
       <c r="CH16" s="57">
         <f t="shared" si="23"/>
-        <v>0.97545841730546179</v>
+        <v>0.97376216408863736</v>
       </c>
       <c r="CI16" s="57">
         <f t="shared" si="23"/>
-        <v>0.97481350023527558</v>
+        <v>0.97321090499033736</v>
       </c>
       <c r="CJ16" s="57">
         <f t="shared" si="23"/>
-        <v>0.97418759307432756</v>
+        <v>0.97266659395102684</v>
       </c>
       <c r="CK16" s="57">
         <f t="shared" si="23"/>
-        <v>0.97347667608271216</v>
+        <v>0.97202021663421234</v>
       </c>
     </row>
     <row r="17" spans="2:141">
@@ -22738,39 +22741,39 @@
       </c>
       <c r="CC17" s="57">
         <f t="shared" si="26"/>
-        <v>1.4548247623330143E-2</v>
+        <v>1.4509051584155042E-2</v>
       </c>
       <c r="CD17" s="57">
         <f t="shared" si="26"/>
-        <v>1.5931122525131423E-2</v>
+        <v>1.5893434148865532E-2</v>
       </c>
       <c r="CE17" s="57">
         <f t="shared" si="26"/>
-        <v>1.7189293112902577E-2</v>
+        <v>1.715296005599173E-2</v>
       </c>
       <c r="CF17" s="57">
         <f t="shared" si="26"/>
-        <v>1.8171003764327585E-2</v>
+        <v>1.813517368078502E-2</v>
       </c>
       <c r="CG17" s="57">
         <f t="shared" si="26"/>
-        <v>1.9131901403799802E-2</v>
+        <v>1.9096553180021906E-2</v>
       </c>
       <c r="CH17" s="57">
         <f t="shared" si="26"/>
-        <v>2.0062261000824651E-2</v>
+        <v>2.0027374147468642E-2</v>
       </c>
       <c r="CI17" s="57">
         <f t="shared" si="26"/>
-        <v>2.0952104958687316E-2</v>
+        <v>2.0917659658360503E-2</v>
       </c>
       <c r="CJ17" s="57">
         <f t="shared" si="26"/>
-        <v>2.1791357341881909E-2</v>
+        <v>2.1757334494898261E-2</v>
       </c>
       <c r="CK17" s="57">
         <f t="shared" si="26"/>
-        <v>2.2670336731519587E-2</v>
+        <v>2.2636418686080469E-2</v>
       </c>
     </row>
     <row r="18" spans="2:141">
@@ -22895,39 +22898,39 @@
       </c>
       <c r="CC18" s="57">
         <f t="shared" si="29"/>
-        <v>6.9466852769175837E-3</v>
+        <v>9.6221797855778491E-3</v>
       </c>
       <c r="CD18" s="57">
         <f t="shared" si="29"/>
-        <v>6.0976732047419791E-3</v>
+        <v>8.4489554075318617E-3</v>
       </c>
       <c r="CE18" s="57">
         <f t="shared" si="29"/>
-        <v>5.4467485683474754E-3</v>
+        <v>7.5489385564867376E-3</v>
       </c>
       <c r="CF18" s="57">
         <f t="shared" si="29"/>
-        <v>5.0804311091682064E-3</v>
+        <v>7.0422407996969969E-3</v>
       </c>
       <c r="CG18" s="57">
         <f t="shared" si="29"/>
-        <v>4.7597821300454602E-3</v>
+        <v>6.5985943417287921E-3</v>
       </c>
       <c r="CH18" s="57">
         <f t="shared" si="29"/>
-        <v>4.4793216937135802E-3</v>
+        <v>6.2104617638939208E-3</v>
       </c>
       <c r="CI18" s="57">
         <f t="shared" si="29"/>
-        <v>4.2343948060370833E-3</v>
+        <v>5.8714353513021292E-3</v>
       </c>
       <c r="CJ18" s="57">
         <f t="shared" si="29"/>
-        <v>4.0210495837903664E-3</v>
+        <v>5.5760715540748487E-3</v>
       </c>
       <c r="CK18" s="57">
         <f t="shared" si="29"/>
-        <v>3.8529871857683356E-3</v>
+        <v>5.3433646797072104E-3</v>
       </c>
     </row>
     <row r="19" spans="2:141">
@@ -24793,39 +24796,39 @@
       </c>
       <c r="CC37" s="58">
         <f t="shared" ref="CC37:CK37" si="61">CC8</f>
-        <v>236327.10200000001</v>
+        <v>236965.53700000001</v>
       </c>
       <c r="CD37" s="58">
         <f t="shared" si="61"/>
-        <v>271924.52667200001</v>
+        <v>272569.34602200001</v>
       </c>
       <c r="CE37" s="58">
         <f t="shared" si="61"/>
-        <v>307465.62797704001</v>
+        <v>308116.89552054001</v>
       </c>
       <c r="CF37" s="58">
         <f t="shared" si="61"/>
-        <v>346116.7624685886</v>
+        <v>346800.59338926355</v>
       </c>
       <c r="CG37" s="58">
         <f t="shared" si="61"/>
-        <v>387905.04173872049</v>
+        <v>388623.06420542923</v>
       </c>
       <c r="CH37" s="58">
         <f t="shared" si="61"/>
-        <v>432802.28406778694</v>
+        <v>433556.20765783114</v>
       </c>
       <c r="CI37" s="58">
         <f t="shared" si="61"/>
-        <v>480728.36529487278</v>
+        <v>481519.98506441916</v>
       </c>
       <c r="CJ37" s="58">
         <f t="shared" si="61"/>
-        <v>531546.13820019539</v>
+        <v>532377.33895821904</v>
       </c>
       <c r="CK37" s="58">
         <f t="shared" si="61"/>
-        <v>582468.07956006867</v>
+        <v>583340.8403559936</v>
       </c>
       <c r="CL37" s="34"/>
       <c r="CM37" s="34"/>
@@ -25112,39 +25115,39 @@
       </c>
       <c r="CC38" s="56">
         <f t="shared" ref="CC38:CK38" si="62">CC37*(1-CC52)</f>
-        <v>42538.878360000017</v>
+        <v>42653.796660000015</v>
       </c>
       <c r="CD38" s="56">
         <f t="shared" si="62"/>
-        <v>48946.414800960018</v>
+        <v>49062.482283960017</v>
       </c>
       <c r="CE38" s="56">
         <f t="shared" si="62"/>
-        <v>55343.813035867221</v>
+        <v>55461.041193697216</v>
       </c>
       <c r="CF38" s="56">
         <f t="shared" si="62"/>
-        <v>62301.017244345967</v>
+        <v>62424.106810067453</v>
       </c>
       <c r="CG38" s="56">
         <f t="shared" si="62"/>
-        <v>69822.907512969701</v>
+        <v>69952.151556977275</v>
       </c>
       <c r="CH38" s="56">
         <f t="shared" si="62"/>
-        <v>77904.411132201669</v>
+        <v>78040.117378409632</v>
       </c>
       <c r="CI38" s="56">
         <f t="shared" si="62"/>
-        <v>86531.105753077121</v>
+        <v>86673.597311595469</v>
       </c>
       <c r="CJ38" s="56">
         <f t="shared" si="62"/>
-        <v>95678.304876035196</v>
+        <v>95827.921012479448</v>
       </c>
       <c r="CK38" s="56">
         <f t="shared" si="62"/>
-        <v>104844.25432081238</v>
+        <v>105001.35126407888</v>
       </c>
     </row>
     <row r="39" spans="2:141">
@@ -25429,39 +25432,39 @@
       </c>
       <c r="CC39" s="56">
         <f t="shared" ref="CC39:CK39" si="65">CC37-CC38</f>
-        <v>193788.22363999998</v>
+        <v>194311.74033999999</v>
       </c>
       <c r="CD39" s="56">
         <f t="shared" si="65"/>
-        <v>222978.11187103999</v>
+        <v>223506.86373804</v>
       </c>
       <c r="CE39" s="56">
         <f t="shared" si="65"/>
-        <v>252121.81494117278</v>
+        <v>252655.85432684279</v>
       </c>
       <c r="CF39" s="56">
         <f t="shared" si="65"/>
-        <v>283815.74522424262</v>
+        <v>284376.48657919612</v>
       </c>
       <c r="CG39" s="56">
         <f t="shared" si="65"/>
-        <v>318082.13422575081</v>
+        <v>318670.91264845198</v>
       </c>
       <c r="CH39" s="56">
         <f t="shared" si="65"/>
-        <v>354897.87293558527</v>
+        <v>355516.09027942154</v>
       </c>
       <c r="CI39" s="56">
         <f t="shared" si="65"/>
-        <v>394197.25954179565</v>
+        <v>394846.38775282371</v>
       </c>
       <c r="CJ39" s="56">
         <f t="shared" si="65"/>
-        <v>435867.83332416019</v>
+        <v>436549.41794573958</v>
       </c>
       <c r="CK39" s="56">
         <f t="shared" si="65"/>
-        <v>477623.82523925626</v>
+        <v>478339.48909191473</v>
       </c>
     </row>
     <row r="40" spans="2:141">
@@ -25696,39 +25699,39 @@
       </c>
       <c r="CC40" s="56">
         <f t="shared" ref="CC40:CK40" si="66">CC37*CC53</f>
-        <v>69716.495089999997</v>
+        <v>69904.833415000001</v>
       </c>
       <c r="CD40" s="56">
         <f t="shared" si="66"/>
-        <v>81577.358001600005</v>
+        <v>81770.803806600001</v>
       </c>
       <c r="CE40" s="56">
         <f t="shared" si="66"/>
-        <v>83015.719553800809</v>
+        <v>83191.561790545806</v>
       </c>
       <c r="CF40" s="56">
         <f t="shared" si="66"/>
-        <v>86529.190617147149</v>
+        <v>86700.148347315888</v>
       </c>
       <c r="CG40" s="56">
         <f t="shared" si="66"/>
-        <v>93097.21001729292</v>
+        <v>93269.535409303004</v>
       </c>
       <c r="CH40" s="56">
         <f t="shared" si="66"/>
-        <v>99544.525335590995</v>
+        <v>99717.927761301165</v>
       </c>
       <c r="CI40" s="56">
         <f t="shared" si="66"/>
-        <v>105760.24036487201</v>
+        <v>105934.39671417221</v>
       </c>
       <c r="CJ40" s="56">
         <f t="shared" si="66"/>
-        <v>111624.68902204103</v>
+        <v>111799.241181226</v>
       </c>
       <c r="CK40" s="56">
         <f t="shared" si="66"/>
-        <v>116493.61591201375</v>
+        <v>116668.16807119873</v>
       </c>
     </row>
     <row r="41" spans="2:141">
@@ -26275,39 +26278,39 @@
       </c>
       <c r="CC43" s="56">
         <f t="shared" ref="CC43:CK43" si="68">CC37*CC54</f>
-        <v>29540.887750000002</v>
+        <v>29620.692125000001</v>
       </c>
       <c r="CD43" s="56">
         <f t="shared" si="68"/>
-        <v>33174.792253984</v>
+        <v>33253.460214684004</v>
       </c>
       <c r="CE43" s="56">
         <f t="shared" si="68"/>
-        <v>36895.875357244797</v>
+        <v>36974.027462464801</v>
       </c>
       <c r="CF43" s="56">
         <f t="shared" si="68"/>
-        <v>40841.77797129345</v>
+        <v>40922.470019933098</v>
       </c>
       <c r="CG43" s="56">
         <f t="shared" si="68"/>
-        <v>44996.984841691577</v>
+        <v>45080.275447829794</v>
       </c>
       <c r="CH43" s="56">
         <f t="shared" si="68"/>
-        <v>49339.46038372771</v>
+        <v>49425.407672992755</v>
       </c>
       <c r="CI43" s="56">
         <f t="shared" si="68"/>
-        <v>54322.305278320629</v>
+        <v>54411.758312279366</v>
       </c>
       <c r="CJ43" s="56">
         <f t="shared" si="68"/>
-        <v>59533.167478421885</v>
+        <v>59626.261963320532</v>
       </c>
       <c r="CK43" s="56">
         <f t="shared" si="68"/>
-        <v>64653.956831167627</v>
+        <v>64750.833279515289</v>
       </c>
     </row>
     <row r="44" spans="2:141">
@@ -26592,39 +26595,39 @@
       </c>
       <c r="CC44" s="56">
         <f t="shared" ref="CC44:CK44" si="71">CC39-SUM(CC40:CC43)</f>
-        <v>94530.840799999976</v>
+        <v>94786.214799999987</v>
       </c>
       <c r="CD44" s="56">
         <f t="shared" si="71"/>
-        <v>108225.96161545598</v>
+        <v>108482.599716756</v>
       </c>
       <c r="CE44" s="56">
         <f t="shared" si="71"/>
-        <v>132210.22003012718</v>
+        <v>132490.26507383218</v>
       </c>
       <c r="CF44" s="56">
         <f t="shared" si="71"/>
-        <v>156444.77663580203</v>
+        <v>156753.86821194715</v>
       </c>
       <c r="CG44" s="56">
         <f t="shared" si="71"/>
-        <v>179987.93936676631</v>
+        <v>180321.10179131918</v>
       </c>
       <c r="CH44" s="56">
         <f t="shared" si="71"/>
-        <v>206013.88721626656</v>
+        <v>206372.75484512761</v>
       </c>
       <c r="CI44" s="56">
         <f t="shared" si="71"/>
-        <v>234114.71389860302</v>
+        <v>234500.23272637214</v>
       </c>
       <c r="CJ44" s="56">
         <f t="shared" si="71"/>
-        <v>264709.97682369727</v>
+        <v>265123.91480119305</v>
       </c>
       <c r="CK44" s="56">
         <f t="shared" si="71"/>
-        <v>296476.25249607489</v>
+        <v>296920.48774120072</v>
       </c>
     </row>
     <row r="45" spans="2:141">
@@ -27176,39 +27179,39 @@
       </c>
       <c r="CC46" s="56">
         <f t="shared" ref="CC46:CK46" si="75">CC44+CC45</f>
-        <v>96657.613768749972</v>
+        <v>96912.987768749983</v>
       </c>
       <c r="CD46" s="56">
         <f t="shared" si="75"/>
-        <v>110964.1818127216</v>
+        <v>111220.81991402162</v>
       </c>
       <c r="CE46" s="56">
         <f t="shared" si="75"/>
-        <v>135735.67853410667</v>
+        <v>136015.72357781167</v>
       </c>
       <c r="CF46" s="56">
         <f t="shared" si="75"/>
-        <v>160983.80445967562</v>
+        <v>161292.89603582074</v>
       </c>
       <c r="CG46" s="56">
         <f t="shared" si="75"/>
-        <v>185831.93769000357</v>
+        <v>186165.10011455644</v>
       </c>
       <c r="CH46" s="56">
         <f t="shared" si="75"/>
-        <v>213538.03505743452</v>
+        <v>213896.90268629557</v>
       </c>
       <c r="CI46" s="56">
         <f t="shared" si="75"/>
-        <v>243802.05424410678</v>
+        <v>244187.5730718759</v>
       </c>
       <c r="CJ46" s="56">
         <f t="shared" si="75"/>
-        <v>277182.42751853337</v>
+        <v>277596.36549602915</v>
       </c>
       <c r="CK46" s="56">
         <f t="shared" si="75"/>
-        <v>312534.53276567638</v>
+        <v>312978.76801080222</v>
       </c>
     </row>
     <row r="47" spans="2:141">
@@ -27443,39 +27446,39 @@
       </c>
       <c r="CC47" s="56">
         <f t="shared" ref="CC47:CK47" si="76">CC46*CC56</f>
-        <v>20298.098891437494</v>
+        <v>20351.727431437495</v>
       </c>
       <c r="CD47" s="56">
         <f t="shared" si="76"/>
-        <v>23302.478180671533</v>
+        <v>23356.372181944538</v>
       </c>
       <c r="CE47" s="56">
         <f t="shared" si="76"/>
-        <v>28504.492492162401</v>
+        <v>28563.301951340451</v>
       </c>
       <c r="CF47" s="56">
         <f t="shared" si="76"/>
-        <v>33806.598936531882</v>
+        <v>33871.508167522356</v>
       </c>
       <c r="CG47" s="56">
         <f t="shared" si="76"/>
-        <v>39024.706914900751</v>
+        <v>39094.67102405685</v>
       </c>
       <c r="CH47" s="56">
         <f t="shared" si="76"/>
-        <v>44842.987362061249</v>
+        <v>44918.349564122065</v>
       </c>
       <c r="CI47" s="56">
         <f t="shared" si="76"/>
-        <v>51198.43139126242</v>
+        <v>51279.39034509394</v>
       </c>
       <c r="CJ47" s="56">
         <f t="shared" si="76"/>
-        <v>58208.309778892006</v>
+        <v>58295.236754166115</v>
       </c>
       <c r="CK47" s="56">
         <f t="shared" si="76"/>
-        <v>65632.251880792042</v>
+        <v>65725.541282268459</v>
       </c>
     </row>
     <row r="48" spans="2:141" s="2" customFormat="1" ht="15">
@@ -27765,239 +27768,239 @@
       </c>
       <c r="CC48" s="58">
         <f t="shared" ref="CC48:CK48" si="79">CC46-CC47</f>
-        <v>76359.514877312482</v>
+        <v>76561.260337312488</v>
       </c>
       <c r="CD48" s="58">
         <f t="shared" si="79"/>
-        <v>87661.703632050063</v>
+        <v>87864.447732077082</v>
       </c>
       <c r="CE48" s="58">
         <f t="shared" si="79"/>
-        <v>107231.18604194427</v>
+        <v>107452.42162647122</v>
       </c>
       <c r="CF48" s="58">
         <f t="shared" si="79"/>
-        <v>127177.20552314374</v>
+        <v>127421.38786829839</v>
       </c>
       <c r="CG48" s="58">
         <f t="shared" si="79"/>
-        <v>146807.23077510283</v>
+        <v>147070.42909049959</v>
       </c>
       <c r="CH48" s="58">
         <f t="shared" si="79"/>
-        <v>168695.04769537327</v>
+        <v>168978.5531221735</v>
       </c>
       <c r="CI48" s="58">
         <f t="shared" si="79"/>
-        <v>192603.62285284436</v>
+        <v>192908.18272678196</v>
       </c>
       <c r="CJ48" s="58">
         <f t="shared" si="79"/>
-        <v>218974.11773964137</v>
+        <v>219301.12874186304</v>
       </c>
       <c r="CK48" s="58">
         <f t="shared" si="79"/>
-        <v>246902.28088488436</v>
+        <v>247253.22672853374</v>
       </c>
       <c r="CL48" s="58">
         <f>CK48*(1+$CK$62)</f>
-        <v>253074.83790700644</v>
+        <v>253434.55739674706</v>
       </c>
       <c r="CM48" s="58">
         <f t="shared" ref="CM48:EI48" si="80">CL48*(1+$CK$62)</f>
-        <v>259401.70885468158</v>
+        <v>259770.42133166571</v>
       </c>
       <c r="CN48" s="58">
         <f t="shared" si="80"/>
-        <v>265886.75157604861</v>
+        <v>266264.68186495733</v>
       </c>
       <c r="CO48" s="58">
         <f t="shared" si="80"/>
-        <v>272533.9203654498</v>
+        <v>272921.29891158122</v>
       </c>
       <c r="CP48" s="58">
         <f t="shared" si="80"/>
-        <v>279347.26837458601</v>
+        <v>279744.33138437074</v>
       </c>
       <c r="CQ48" s="58">
         <f t="shared" si="80"/>
-        <v>286330.95008395065</v>
+        <v>286737.93966897996</v>
       </c>
       <c r="CR48" s="58">
         <f t="shared" si="80"/>
-        <v>293489.22383604938</v>
+        <v>293906.38816070446</v>
       </c>
       <c r="CS48" s="58">
         <f t="shared" si="80"/>
-        <v>300826.45443195058</v>
+        <v>301254.04786472203</v>
       </c>
       <c r="CT48" s="58">
         <f t="shared" si="80"/>
-        <v>308347.11579274933</v>
+        <v>308785.39906134008</v>
       </c>
       <c r="CU48" s="58">
         <f t="shared" si="80"/>
-        <v>316055.79368756805</v>
+        <v>316505.03403787356</v>
       </c>
       <c r="CV48" s="58">
         <f t="shared" si="80"/>
-        <v>323957.1885297572</v>
+        <v>324417.65988882037</v>
       </c>
       <c r="CW48" s="58">
         <f t="shared" si="80"/>
-        <v>332056.11824300111</v>
+        <v>332528.10138604086</v>
       </c>
       <c r="CX48" s="58">
         <f t="shared" si="80"/>
-        <v>340357.52119907609</v>
+        <v>340841.30392069183</v>
       </c>
       <c r="CY48" s="58">
         <f t="shared" si="80"/>
-        <v>348866.45922905294</v>
+        <v>349362.33651870908</v>
       </c>
       <c r="CZ48" s="58">
         <f t="shared" si="80"/>
-        <v>357588.12070977921</v>
+        <v>358096.3949316768</v>
       </c>
       <c r="DA48" s="58">
         <f t="shared" si="80"/>
-        <v>366527.82372752368</v>
+        <v>367048.80480496871</v>
       </c>
       <c r="DB48" s="58">
         <f t="shared" si="80"/>
-        <v>375691.01932071173</v>
+        <v>376225.02492509288</v>
       </c>
       <c r="DC48" s="58">
         <f t="shared" si="80"/>
-        <v>385083.29480372951</v>
+        <v>385630.65054822015</v>
       </c>
       <c r="DD48" s="58">
         <f t="shared" si="80"/>
-        <v>394710.37717382272</v>
+        <v>395271.41681192559</v>
       </c>
       <c r="DE48" s="58">
         <f t="shared" si="80"/>
-        <v>404578.13660316827</v>
+        <v>405153.2022322237</v>
       </c>
       <c r="DF48" s="58">
         <f t="shared" si="80"/>
-        <v>414692.59001824743</v>
+        <v>415282.03228802927</v>
       </c>
       <c r="DG48" s="58">
         <f t="shared" si="80"/>
-        <v>425059.90476870356</v>
+        <v>425664.08309522999</v>
       </c>
       <c r="DH48" s="58">
         <f t="shared" si="80"/>
-        <v>435686.40238792112</v>
+        <v>436305.68517261068</v>
       </c>
       <c r="DI48" s="58">
         <f t="shared" si="80"/>
-        <v>446578.5624476191</v>
+        <v>447213.32730192592</v>
       </c>
       <c r="DJ48" s="58">
         <f t="shared" si="80"/>
-        <v>457743.02650880953</v>
+        <v>458393.66048447404</v>
       </c>
       <c r="DK48" s="58">
         <f t="shared" si="80"/>
-        <v>469186.60217152972</v>
+        <v>469853.50199658587</v>
       </c>
       <c r="DL48" s="58">
         <f t="shared" si="80"/>
-        <v>480916.26722581795</v>
+        <v>481599.83954650047</v>
       </c>
       <c r="DM48" s="58">
         <f t="shared" si="80"/>
-        <v>492939.17390646337</v>
+        <v>493639.83553516294</v>
       </c>
       <c r="DN48" s="58">
         <f t="shared" si="80"/>
-        <v>505262.65325412492</v>
+        <v>505980.831423542</v>
       </c>
       <c r="DO48" s="58">
         <f t="shared" si="80"/>
-        <v>517894.21958547801</v>
+        <v>518630.35220913048</v>
       </c>
       <c r="DP48" s="58">
         <f t="shared" si="80"/>
-        <v>530841.57507511496</v>
+        <v>531596.1110143587</v>
       </c>
       <c r="DQ48" s="58">
         <f t="shared" si="80"/>
-        <v>544112.61445199279</v>
+        <v>544886.01378971757</v>
       </c>
       <c r="DR48" s="58">
         <f t="shared" si="80"/>
-        <v>557715.42981329258</v>
+        <v>558508.1641344605</v>
       </c>
       <c r="DS48" s="58">
         <f t="shared" si="80"/>
-        <v>571658.3155586248</v>
+        <v>572470.86823782197</v>
       </c>
       <c r="DT48" s="58">
         <f t="shared" si="80"/>
-        <v>585949.77344759041</v>
+        <v>586782.63994376746</v>
       </c>
       <c r="DU48" s="58">
         <f t="shared" si="80"/>
-        <v>600598.51778378012</v>
+        <v>601452.20594236162</v>
       </c>
       <c r="DV48" s="58">
         <f t="shared" si="80"/>
-        <v>615613.48072837456</v>
+        <v>616488.51109092066</v>
       </c>
       <c r="DW48" s="58">
         <f t="shared" si="80"/>
-        <v>631003.81774658384</v>
+        <v>631900.72386819357</v>
       </c>
       <c r="DX48" s="58">
         <f t="shared" si="80"/>
-        <v>646778.91319024842</v>
+        <v>647698.24196489831</v>
       </c>
       <c r="DY48" s="58">
         <f t="shared" si="80"/>
-        <v>662948.38602000463</v>
+        <v>663890.69801402069</v>
       </c>
       <c r="DZ48" s="58">
         <f t="shared" si="80"/>
-        <v>679522.09567050473</v>
+        <v>680487.96546437114</v>
       </c>
       <c r="EA48" s="58">
         <f t="shared" si="80"/>
-        <v>696510.14806226734</v>
+        <v>697500.16460098035</v>
       </c>
       <c r="EB48" s="58">
         <f t="shared" si="80"/>
-        <v>713922.90176382393</v>
+        <v>714937.66871600482</v>
       </c>
       <c r="EC48" s="58">
         <f t="shared" si="80"/>
-        <v>731770.9743079195</v>
+        <v>732811.11043390492</v>
       </c>
       <c r="ED48" s="58">
         <f t="shared" si="80"/>
-        <v>750065.24866561743</v>
+        <v>751131.38819475251</v>
       </c>
       <c r="EE48" s="58">
         <f t="shared" si="80"/>
-        <v>768816.87988225778</v>
+        <v>769909.67289962131</v>
       </c>
       <c r="EF48" s="58">
         <f t="shared" si="80"/>
-        <v>788037.30187931412</v>
+        <v>789157.41472211177</v>
       </c>
       <c r="EG48" s="58">
         <f t="shared" si="80"/>
-        <v>807738.2344262969</v>
+        <v>808886.35009016446</v>
       </c>
       <c r="EH48" s="58">
         <f t="shared" si="80"/>
-        <v>827931.69028695428</v>
+        <v>829108.50884241855</v>
       </c>
       <c r="EI48" s="58">
         <f t="shared" si="80"/>
-        <v>848629.98254412808</v>
+        <v>849836.22156347893</v>
       </c>
       <c r="EJ48" s="34"/>
       <c r="EK48" s="34"/>
@@ -29707,11 +29710,11 @@
       </c>
       <c r="CC55" s="57">
         <f t="shared" ref="CC55:CK55" si="100">CC44/CC37</f>
-        <v>0.39999999999999986</v>
+        <v>0.39999999999999991</v>
       </c>
       <c r="CD55" s="57">
         <f t="shared" si="100"/>
-        <v>0.39799999999999991</v>
+        <v>0.39799999999999996</v>
       </c>
       <c r="CE55" s="57">
         <f t="shared" si="100"/>
@@ -29719,7 +29722,7 @@
       </c>
       <c r="CF55" s="57">
         <f t="shared" si="100"/>
-        <v>0.45199999999999996</v>
+        <v>0.45200000000000007</v>
       </c>
       <c r="CG55" s="57">
         <f t="shared" si="100"/>
@@ -29731,7 +29734,7 @@
       </c>
       <c r="CI55" s="57">
         <f t="shared" si="100"/>
-        <v>0.48699999999999993</v>
+        <v>0.48699999999999999</v>
       </c>
       <c r="CJ55" s="57">
         <f t="shared" si="100"/>
@@ -29739,7 +29742,7 @@
       </c>
       <c r="CK55" s="57">
         <f t="shared" si="100"/>
-        <v>0.5089999999999999</v>
+        <v>0.50900000000000001</v>
       </c>
     </row>
     <row r="56" spans="2:89">
@@ -30331,39 +30334,39 @@
       </c>
       <c r="CC57" s="57">
         <f t="shared" ref="CC57:CK57" si="109">CC48/CC37</f>
-        <v>0.32310942854667796</v>
+        <v>0.3230902742507763</v>
       </c>
       <c r="CD57" s="57">
         <f t="shared" si="109"/>
-        <v>0.32237512630770926</v>
+        <v>0.32235630680562749</v>
       </c>
       <c r="CE57" s="57">
         <f t="shared" si="109"/>
-        <v>0.34875828803196096</v>
+        <v>0.34873914150322249</v>
       </c>
       <c r="CF57" s="57">
         <f t="shared" si="109"/>
-        <v>0.36744018005971485</v>
+        <v>0.36741975157255652</v>
       </c>
       <c r="CG57" s="57">
         <f t="shared" si="109"/>
-        <v>0.37846177537951964</v>
+        <v>0.37843978558297042</v>
       </c>
       <c r="CH57" s="57">
         <f t="shared" si="109"/>
-        <v>0.38977393120446585</v>
+        <v>0.38975004886917414</v>
       </c>
       <c r="CI57" s="57">
         <f t="shared" si="109"/>
-        <v>0.40064959082392343</v>
+        <v>0.40062341898638776</v>
       </c>
       <c r="CJ57" s="57">
         <f t="shared" si="109"/>
-        <v>0.4119569346907182</v>
+        <v>0.41192799297393418</v>
       </c>
       <c r="CK57" s="57">
         <f t="shared" si="109"/>
-        <v>0.4238898053801794</v>
+        <v>0.42385721969619561</v>
       </c>
     </row>
     <row r="58" spans="2:89">
@@ -30459,39 +30462,39 @@
       </c>
       <c r="CC59" s="56">
         <f t="shared" ref="CC59:CK59" si="115">CB59+CC48</f>
-        <v>186055.06817181248</v>
+        <v>186256.81363181249</v>
       </c>
       <c r="CD59" s="56">
         <f t="shared" si="115"/>
-        <v>273716.77180386253</v>
+        <v>274121.26136388956</v>
       </c>
       <c r="CE59" s="56">
         <f t="shared" si="115"/>
-        <v>380947.95784580678</v>
+        <v>381573.68299036077</v>
       </c>
       <c r="CF59" s="56">
         <f t="shared" si="115"/>
-        <v>508125.16336895054</v>
+        <v>508995.07085865916</v>
       </c>
       <c r="CG59" s="56">
         <f t="shared" si="115"/>
-        <v>654932.39414405334</v>
+        <v>656065.49994915875</v>
       </c>
       <c r="CH59" s="56">
         <f t="shared" si="115"/>
-        <v>823627.44183942664</v>
+        <v>825044.05307133228</v>
       </c>
       <c r="CI59" s="56">
         <f t="shared" si="115"/>
-        <v>1016231.0646922709</v>
+        <v>1017952.2357981142</v>
       </c>
       <c r="CJ59" s="56">
         <f t="shared" si="115"/>
-        <v>1235205.1824319123</v>
+        <v>1237253.3645399772</v>
       </c>
       <c r="CK59" s="56">
         <f t="shared" si="115"/>
-        <v>1482107.4633167966</v>
+        <v>1484506.591268511</v>
       </c>
     </row>
     <row r="60" spans="2:89">
@@ -31343,7 +31346,7 @@
       </c>
       <c r="CK68" s="56">
         <f>NPV(CK66,CB48:EJ48)</f>
-        <v>2183957.4908089112</v>
+        <v>2187277.4285540604</v>
       </c>
     </row>
     <row r="69" spans="2:141" s="2" customFormat="1" ht="15" customHeight="1">
@@ -31530,7 +31533,7 @@
       </c>
       <c r="CK70" s="55">
         <f>CK68/CK69</f>
-        <v>867.68275359909069</v>
+        <v>869.00175945731439</v>
       </c>
     </row>
     <row r="71" spans="2:141" ht="15" customHeight="1">
@@ -31622,7 +31625,7 @@
       </c>
       <c r="CK71" s="55">
         <f>Main!C3</f>
-        <v>648.35</v>
+        <v>667.31</v>
       </c>
     </row>
     <row r="72" spans="2:141" ht="15" customHeight="1">
@@ -31721,7 +31724,7 @@
       </c>
       <c r="CK72" s="63">
         <f>CK70/CK71-1</f>
-        <v>0.33829375121321914</v>
+        <v>0.30224597182316226</v>
       </c>
       <c r="CL72" s="64" t="str">
         <f>IF(CK72&gt;0,"Upside","Downside")</f>

--- a/META_Model.xlsx
+++ b/META_Model.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\OneDrive\Desktop\Equity Research\Models\Communication Services\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94D6381D-96AC-493A-AE4C-6C069857806C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC054366-E3D7-4D81-A9A7-8DE95392ED04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5114,7 +5114,7 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -5237,6 +5237,7 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Comma" xfId="3" builtinId="3"/>
@@ -23011,7 +23012,9 @@
       <c r="BD20" s="1">
         <v>18454</v>
       </c>
-      <c r="BE20" s="1"/>
+      <c r="BE20" s="1">
+        <v>18454</v>
+      </c>
       <c r="BW20" s="1">
         <f>SUM(AI20:AL20)</f>
         <v>38433</v>
@@ -23108,7 +23111,9 @@
       <c r="BD21" s="1">
         <v>11128</v>
       </c>
-      <c r="BE21" s="1"/>
+      <c r="BE21" s="1">
+        <v>11128</v>
+      </c>
       <c r="BW21" s="1">
         <f>SUM(AI21:AL21)</f>
         <v>20349</v>
@@ -23205,7 +23210,9 @@
       <c r="BD22" s="1">
         <v>12858</v>
       </c>
-      <c r="BE22" s="1"/>
+      <c r="BE22" s="1">
+        <v>12858</v>
+      </c>
       <c r="BW22" s="1">
         <f>SUM(AI22:AL22)</f>
         <v>19848</v>
@@ -23302,7 +23309,9 @@
       <c r="BD23" s="1">
         <v>5076</v>
       </c>
-      <c r="BE23" s="1"/>
+      <c r="BE23" s="1">
+        <v>5076</v>
+      </c>
       <c r="BW23" s="1">
         <f>SUM(AI23:AL23)</f>
         <v>7335</v>
@@ -23418,7 +23427,7 @@
       </c>
       <c r="BE24" s="2">
         <f>SUM(BE20:BE23)</f>
-        <v>0</v>
+        <v>47516</v>
       </c>
       <c r="BF24" s="34"/>
       <c r="BG24" s="34"/>
@@ -23589,7 +23598,7 @@
       </c>
       <c r="BE26" s="47">
         <f t="shared" si="32"/>
-        <v>-1</v>
+        <v>0.18150969972469433</v>
       </c>
       <c r="BW26" s="47"/>
       <c r="BX26" s="47">
@@ -23687,7 +23696,7 @@
       </c>
       <c r="BE27" s="47">
         <f t="shared" si="32"/>
-        <v>-1</v>
+        <v>0.20890820206409555</v>
       </c>
       <c r="BW27" s="47"/>
       <c r="BX27" s="47">
@@ -23785,7 +23794,7 @@
       </c>
       <c r="BE28" s="47">
         <f t="shared" si="32"/>
-        <v>-1</v>
+        <v>0.1436449346259896</v>
       </c>
       <c r="BW28" s="47"/>
       <c r="BX28" s="47">
@@ -23883,7 +23892,7 @@
       </c>
       <c r="BE29" s="47">
         <f t="shared" si="32"/>
-        <v>-1</v>
+        <v>0.12251216275984067</v>
       </c>
       <c r="BW29" s="47"/>
       <c r="BX29" s="47">
@@ -23981,7 +23990,7 @@
       </c>
       <c r="BE30" s="50">
         <f t="shared" si="32"/>
-        <v>-1</v>
+        <v>0.17066200202025184</v>
       </c>
       <c r="BF30" s="34"/>
       <c r="BG30" s="34"/>
@@ -24163,9 +24172,9 @@
         <f>BD20/BD24</f>
         <v>0.38837444229312229</v>
       </c>
-      <c r="BE32" s="47" t="e">
+      <c r="BE32" s="47">
         <f>BE20/BE24</f>
-        <v>#DIV/0!</v>
+        <v>0.38837444229312229</v>
       </c>
       <c r="BW32" s="47">
         <f t="shared" ref="BW32:BZ32" si="40">BW20/BW24</f>
@@ -24280,9 +24289,9 @@
         <f>BD21/BD24</f>
         <v>0.23419479754188063</v>
       </c>
-      <c r="BE33" s="47" t="e">
+      <c r="BE33" s="47">
         <f>BE21/BE24</f>
-        <v>#DIV/0!</v>
+        <v>0.23419479754188063</v>
       </c>
       <c r="BW33" s="47">
         <f t="shared" ref="BW33:BZ33" si="42">BW21/BW24</f>
@@ -24397,9 +24406,9 @@
         <f>BD22/BD24</f>
         <v>0.27060358616045121</v>
       </c>
-      <c r="BE34" s="47" t="e">
+      <c r="BE34" s="47">
         <f>BE22/BE24</f>
-        <v>#DIV/0!</v>
+        <v>0.27060358616045121</v>
       </c>
       <c r="BW34" s="47">
         <f t="shared" ref="BW34:BZ34" si="44">BW22/BW24</f>
@@ -24514,9 +24523,9 @@
         <f>BD23/BD24</f>
         <v>0.10682717400454583</v>
       </c>
-      <c r="BE35" s="47" t="e">
+      <c r="BE35" s="47">
         <f>BE23/BE24</f>
-        <v>#DIV/0!</v>
+        <v>0.10682717400454583</v>
       </c>
       <c r="BW35" s="47">
         <f t="shared" ref="BW35:BZ35" si="46">BW23/BW24</f>
@@ -25111,11 +25120,11 @@
       </c>
       <c r="CB38" s="56">
         <f>CB37*(1-CB52)</f>
-        <v>36065.185200000014</v>
+        <v>38068.806599999989</v>
       </c>
       <c r="CC38" s="56">
         <f t="shared" ref="CC38:CK38" si="62">CC37*(1-CC52)</f>
-        <v>42653.796660000015</v>
+        <v>43838.624345000011</v>
       </c>
       <c r="CD38" s="56">
         <f t="shared" si="62"/>
@@ -25428,11 +25437,11 @@
       </c>
       <c r="CB39" s="56">
         <f>CB37-CB38</f>
-        <v>164296.95480000001</v>
+        <v>162293.33340000003</v>
       </c>
       <c r="CC39" s="56">
         <f t="shared" ref="CC39:CK39" si="65">CC37-CC38</f>
-        <v>194311.74033999999</v>
+        <v>193126.91265499999</v>
       </c>
       <c r="CD39" s="56">
         <f t="shared" si="65"/>
@@ -25699,7 +25708,7 @@
       </c>
       <c r="CC40" s="56">
         <f t="shared" ref="CC40:CK40" si="66">CC37*CC53</f>
-        <v>69904.833415000001</v>
+        <v>75828.971839999998</v>
       </c>
       <c r="CD40" s="56">
         <f t="shared" si="66"/>
@@ -26591,11 +26600,11 @@
       </c>
       <c r="CB44" s="56">
         <f>CB39-SUM(CB40:CB43)</f>
-        <v>81647.572050000002</v>
+        <v>79643.950650000028</v>
       </c>
       <c r="CC44" s="56">
         <f t="shared" ref="CC44:CK44" si="71">CC39-SUM(CC40:CC43)</f>
-        <v>94786.214799999987</v>
+        <v>87677.248689999993</v>
       </c>
       <c r="CD44" s="56">
         <f t="shared" si="71"/>
@@ -27175,11 +27184,11 @@
       </c>
       <c r="CB46" s="56">
         <f>CB44+CB45</f>
-        <v>83299.434550000005</v>
+        <v>81295.813150000031</v>
       </c>
       <c r="CC46" s="56">
         <f t="shared" ref="CC46:CK46" si="75">CC44+CC45</f>
-        <v>96912.987768749983</v>
+        <v>89804.021658749989</v>
       </c>
       <c r="CD46" s="56">
         <f t="shared" si="75"/>
@@ -27442,11 +27451,11 @@
       </c>
       <c r="CB47" s="56">
         <f>CB46*CB56</f>
-        <v>17492.8812555</v>
+        <v>23982.264879250008</v>
       </c>
       <c r="CC47" s="56">
         <f t="shared" ref="CC47:CK47" si="76">CC46*CC56</f>
-        <v>20351.727431437495</v>
+        <v>18858.844548337496</v>
       </c>
       <c r="CD47" s="56">
         <f t="shared" si="76"/>
@@ -27764,11 +27773,11 @@
       </c>
       <c r="CB48" s="58">
         <f>CB46-CB47</f>
-        <v>65806.553294500001</v>
+        <v>57313.54827075002</v>
       </c>
       <c r="CC48" s="58">
         <f t="shared" ref="CC48:CK48" si="79">CC46-CC47</f>
-        <v>76561.260337312488</v>
+        <v>70945.177110412493</v>
       </c>
       <c r="CD48" s="58">
         <f t="shared" si="79"/>
@@ -28226,6 +28235,46 @@
         <f>AVERAGE(AY49:BB49)</f>
         <v>2535.5</v>
       </c>
+      <c r="CB49" s="70">
+        <f>CA49</f>
+        <v>2535.5</v>
+      </c>
+      <c r="CC49" s="70">
+        <f>CB49</f>
+        <v>2535.5</v>
+      </c>
+      <c r="CD49" s="70">
+        <f t="shared" ref="CD49:CK49" si="81">CC49</f>
+        <v>2535.5</v>
+      </c>
+      <c r="CE49" s="70">
+        <f t="shared" si="81"/>
+        <v>2535.5</v>
+      </c>
+      <c r="CF49" s="70">
+        <f t="shared" si="81"/>
+        <v>2535.5</v>
+      </c>
+      <c r="CG49" s="70">
+        <f t="shared" si="81"/>
+        <v>2535.5</v>
+      </c>
+      <c r="CH49" s="70">
+        <f t="shared" si="81"/>
+        <v>2535.5</v>
+      </c>
+      <c r="CI49" s="70">
+        <f t="shared" si="81"/>
+        <v>2535.5</v>
+      </c>
+      <c r="CJ49" s="70">
+        <f t="shared" si="81"/>
+        <v>2535.5</v>
+      </c>
+      <c r="CK49" s="70">
+        <f t="shared" si="81"/>
+        <v>2535.5</v>
+      </c>
     </row>
     <row r="50" spans="2:89">
       <c r="B50" s="1" t="s">
@@ -28236,219 +28285,219 @@
         <v>0.15219005196733482</v>
       </c>
       <c r="D50" s="39">
-        <f t="shared" ref="D50:I50" si="81">D48/D49</f>
+        <f t="shared" ref="D50:I50" si="82">D48/D49</f>
         <v>-8.3555082490686536E-2</v>
       </c>
       <c r="E50" s="39">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>-2.4380165289256198E-2</v>
       </c>
       <c r="F50" s="39">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>2.6823134953897737E-2</v>
       </c>
       <c r="G50" s="39">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>9.1785414920368819E-2</v>
       </c>
       <c r="H50" s="39">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>0.13834648940589947</v>
       </c>
       <c r="I50" s="39">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>0.17489711934156379</v>
       </c>
       <c r="J50" s="39">
-        <f t="shared" ref="J50:BC50" si="82">J48/J49</f>
+        <f t="shared" ref="J50:BC50" si="83">J48/J49</f>
         <v>0.21611570247933884</v>
       </c>
       <c r="K50" s="39">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>0.25225933202357564</v>
       </c>
       <c r="L50" s="39">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>0.30898437499999998</v>
       </c>
       <c r="M50" s="39">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>0.31155778894472363</v>
       </c>
       <c r="N50" s="39">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>0.26817138485080338</v>
       </c>
       <c r="O50" s="39">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>0.18390804597701149</v>
       </c>
       <c r="P50" s="39">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>0.25715307582260372</v>
       </c>
       <c r="Q50" s="39">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>0.31908831908831908</v>
       </c>
       <c r="R50" s="39">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>0.55690331787370673</v>
       </c>
       <c r="S50" s="39">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>0.61132606401688361</v>
       </c>
       <c r="T50" s="39">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>0.79936974789915971</v>
       </c>
       <c r="U50" s="39">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>0.91501219087425989</v>
       </c>
       <c r="V50" s="39">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>1.2465944813133076</v>
       </c>
       <c r="W50" s="39">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>1.0598408855067452</v>
       </c>
       <c r="X50" s="39">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>1.3427586206896551</v>
       </c>
       <c r="Y50" s="39">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>1.6208677685950412</v>
       </c>
       <c r="Z50" s="39">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>1.4715615305067218</v>
       </c>
       <c r="AA50" s="39">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>1.7164487267721955</v>
       </c>
       <c r="AB50" s="39">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>1.7637305699481864</v>
       </c>
       <c r="AC50" s="39">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>1.7805892547660311</v>
       </c>
       <c r="AD50" s="39">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>2.3809688581314878</v>
       </c>
       <c r="AE50" s="39">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>0.85049019607843135</v>
       </c>
       <c r="AF50" s="39">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>0.91628721541155866</v>
       </c>
       <c r="AG50" s="39">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>2.1341976173791171</v>
       </c>
       <c r="AH50" s="39">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>2.5749824807288015</v>
       </c>
       <c r="AI50" s="39">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>1.7193967029112591</v>
       </c>
       <c r="AJ50" s="39">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>1.8168421052631578</v>
       </c>
       <c r="AK50" s="39">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>2.7529824561403511</v>
       </c>
       <c r="AL50" s="39">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>3.9354612416695898</v>
       </c>
       <c r="AM50" s="39">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>3.335792061819459</v>
       </c>
       <c r="AN50" s="39">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>3.667607621736062</v>
       </c>
       <c r="AO50" s="39">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>3.2672352523098791</v>
       </c>
       <c r="AP50" s="39">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>3.6536412078152751</v>
       </c>
       <c r="AQ50" s="39">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>2.7394495412844035</v>
       </c>
       <c r="AR50" s="39">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>2.4730029585798818</v>
       </c>
       <c r="AS50" s="39">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>1.638702460850112</v>
       </c>
       <c r="AT50" s="39">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>1.731671008559732</v>
       </c>
       <c r="AU50" s="39">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>2.206803247004252</v>
       </c>
       <c r="AV50" s="39">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>3.0327102803738319</v>
       </c>
       <c r="AW50" s="39">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>4.4965062111801242</v>
       </c>
       <c r="AX50" s="39">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>5.4459984459984456</v>
       </c>
       <c r="AY50" s="39">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>4.8601178781925345</v>
       </c>
       <c r="AZ50" s="39">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>5.3137332280978686</v>
       </c>
       <c r="BA50" s="39">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>6.2032423882957692</v>
       </c>
       <c r="BB50" s="39">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>8.2233622730860301</v>
       </c>
       <c r="BC50" s="39">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>6.5864661654135341</v>
       </c>
       <c r="BD50" s="39">
-        <f t="shared" ref="BD50:BE50" si="83">BD48/BD49</f>
+        <f t="shared" ref="BD50:BE50" si="84">BD48/BD49</f>
         <v>7.2823669579030978</v>
       </c>
       <c r="BE50" s="39">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>1.0762812872467222</v>
       </c>
       <c r="BO50" s="39">
@@ -28503,6 +28552,46 @@
         <f>SUM(AY50:BB50)</f>
         <v>24.600455767672202</v>
       </c>
+      <c r="CB50" s="55">
+        <f>CB48/CB49</f>
+        <v>22.604436312660233</v>
+      </c>
+      <c r="CC50" s="55">
+        <f t="shared" ref="CC50:CK50" si="85">CC48/CC49</f>
+        <v>27.980744275453556</v>
+      </c>
+      <c r="CD50" s="55">
+        <f t="shared" si="85"/>
+        <v>34.653696601095277</v>
+      </c>
+      <c r="CE50" s="55">
+        <f t="shared" si="85"/>
+        <v>42.379184234459167</v>
+      </c>
+      <c r="CF50" s="55">
+        <f t="shared" si="85"/>
+        <v>50.254935069334806</v>
+      </c>
+      <c r="CG50" s="55">
+        <f t="shared" si="85"/>
+        <v>58.004507627883882</v>
+      </c>
+      <c r="CH50" s="55">
+        <f t="shared" si="85"/>
+        <v>66.645061377311578</v>
+      </c>
+      <c r="CI50" s="55">
+        <f t="shared" si="85"/>
+        <v>76.082895967967644</v>
+      </c>
+      <c r="CJ50" s="55">
+        <f t="shared" si="85"/>
+        <v>86.492261385077114</v>
+      </c>
+      <c r="CK50" s="55">
+        <f t="shared" si="85"/>
+        <v>97.516555601866983</v>
+      </c>
     </row>
     <row r="51" spans="2:89">
       <c r="BE51" s="1"/>
@@ -28516,278 +28605,278 @@
         <v>0.73818525519848777</v>
       </c>
       <c r="D52" s="47">
-        <f t="shared" ref="D52:BC52" si="84">D39/D37</f>
+        <f t="shared" ref="D52:BC52" si="86">D39/D37</f>
         <v>0.69003378378378377</v>
       </c>
       <c r="E52" s="47">
-        <f t="shared" si="84"/>
+        <f t="shared" si="86"/>
         <v>0.74484944532488118</v>
       </c>
       <c r="F52" s="47">
-        <f t="shared" si="84"/>
+        <f t="shared" si="86"/>
         <v>0.74889589905362774</v>
       </c>
       <c r="G52" s="47">
-        <f t="shared" si="84"/>
+        <f t="shared" si="86"/>
         <v>0.71673525377229086</v>
       </c>
       <c r="H52" s="47">
-        <f t="shared" si="84"/>
+        <f t="shared" si="86"/>
         <v>0.74351902923331492</v>
       </c>
       <c r="I52" s="47">
-        <f t="shared" si="84"/>
+        <f t="shared" si="86"/>
         <v>0.74851190476190477</v>
       </c>
       <c r="J52" s="47">
-        <f t="shared" si="84"/>
+        <f t="shared" si="86"/>
         <v>0.8104448742746615</v>
       </c>
       <c r="K52" s="47">
-        <f t="shared" si="84"/>
+        <f t="shared" si="86"/>
         <v>0.815347721822542</v>
       </c>
       <c r="L52" s="47">
-        <f t="shared" si="84"/>
+        <f t="shared" si="86"/>
         <v>0.83745704467353954</v>
       </c>
       <c r="M52" s="47">
-        <f t="shared" si="84"/>
+        <f t="shared" si="86"/>
         <v>0.82360287230721196</v>
       </c>
       <c r="N52" s="47">
-        <f t="shared" si="84"/>
+        <f t="shared" si="86"/>
         <v>0.83043365359646848</v>
       </c>
       <c r="O52" s="47">
-        <f t="shared" si="84"/>
+        <f t="shared" si="86"/>
         <v>0.81541066892464009</v>
       </c>
       <c r="P52" s="47">
-        <f t="shared" si="84"/>
+        <f t="shared" si="86"/>
         <v>0.83473527956457194</v>
       </c>
       <c r="Q52" s="47">
-        <f t="shared" si="84"/>
+        <f t="shared" si="86"/>
         <v>0.84003554765607646</v>
       </c>
       <c r="R52" s="47">
-        <f t="shared" si="84"/>
+        <f t="shared" si="86"/>
         <v>0.85878123930160899</v>
       </c>
       <c r="S52" s="47">
-        <f t="shared" si="84"/>
+        <f t="shared" si="86"/>
         <v>0.84429580081753997</v>
       </c>
       <c r="T52" s="47">
-        <f t="shared" si="84"/>
+        <f t="shared" si="86"/>
         <v>0.85752019888129272</v>
       </c>
       <c r="U52" s="47">
-        <f t="shared" si="84"/>
+        <f t="shared" si="86"/>
         <v>0.85922122379118526</v>
       </c>
       <c r="V52" s="47">
-        <f t="shared" si="84"/>
+        <f t="shared" si="86"/>
         <v>0.88114428425473945</v>
       </c>
       <c r="W52" s="47">
-        <f t="shared" si="84"/>
+        <f t="shared" si="86"/>
         <v>0.85570219123505975</v>
       </c>
       <c r="X52" s="47">
-        <f t="shared" si="84"/>
+        <f t="shared" si="86"/>
         <v>0.86728891749812254</v>
       </c>
       <c r="Y52" s="47">
-        <f t="shared" si="84"/>
+        <f t="shared" si="86"/>
         <v>0.85979860573199074</v>
       </c>
       <c r="Z52" s="47">
-        <f t="shared" si="84"/>
+        <f t="shared" si="86"/>
         <v>0.87588652482269502</v>
       </c>
       <c r="AA52" s="47">
-        <f t="shared" si="84"/>
+        <f t="shared" si="86"/>
         <v>0.8389603877653351</v>
       </c>
       <c r="AB52" s="47">
-        <f t="shared" si="84"/>
+        <f t="shared" si="86"/>
         <v>0.83266570931902351</v>
       </c>
       <c r="AC52" s="47">
-        <f t="shared" si="84"/>
+        <f t="shared" si="86"/>
         <v>0.82385080498288044</v>
       </c>
       <c r="AD52" s="47">
-        <f t="shared" si="84"/>
+        <f t="shared" si="86"/>
         <v>0.83469315360056762</v>
       </c>
       <c r="AE52" s="47">
-        <f t="shared" si="84"/>
+        <f t="shared" si="86"/>
         <v>0.81322544272733299</v>
       </c>
       <c r="AF52" s="47">
-        <f t="shared" si="84"/>
+        <f t="shared" si="86"/>
         <v>0.80415729006277392</v>
       </c>
       <c r="AG52" s="47">
-        <f t="shared" si="84"/>
+        <f t="shared" si="86"/>
         <v>0.82126671198731027</v>
       </c>
       <c r="AH52" s="47">
-        <f t="shared" si="84"/>
+        <f t="shared" si="86"/>
         <v>0.83436106631249407</v>
       </c>
       <c r="AI52" s="47">
-        <f t="shared" si="84"/>
+        <f t="shared" si="86"/>
         <v>0.80498393189378137</v>
       </c>
       <c r="AJ52" s="47">
-        <f t="shared" si="84"/>
+        <f t="shared" si="86"/>
         <v>0.7950981966072671</v>
       </c>
       <c r="AK52" s="47">
-        <f t="shared" si="84"/>
+        <f t="shared" si="86"/>
         <v>0.80465766185374943</v>
       </c>
       <c r="AL52" s="47">
-        <f t="shared" si="84"/>
+        <f t="shared" si="86"/>
         <v>0.81439920202344052</v>
       </c>
       <c r="AM52" s="47">
-        <f t="shared" si="84"/>
+        <f t="shared" si="86"/>
         <v>0.80394329601467274</v>
       </c>
       <c r="AN52" s="47">
-        <f t="shared" si="84"/>
+        <f t="shared" si="86"/>
         <v>0.81432059703545756</v>
       </c>
       <c r="AO52" s="47">
-        <f t="shared" si="84"/>
+        <f t="shared" si="86"/>
         <v>0.80106859703550504</v>
       </c>
       <c r="AP52" s="47">
-        <f t="shared" si="84"/>
+        <f t="shared" si="86"/>
         <v>0.81146981081642955</v>
       </c>
       <c r="AQ52" s="47">
-        <f t="shared" si="84"/>
+        <f t="shared" si="86"/>
         <v>0.78482872294682526</v>
       </c>
       <c r="AR52" s="47">
-        <f t="shared" si="84"/>
+        <f t="shared" si="86"/>
         <v>0.81985982929706469</v>
       </c>
       <c r="AS52" s="47">
-        <f t="shared" si="84"/>
+        <f t="shared" si="86"/>
         <v>0.79375045103557773</v>
       </c>
       <c r="AT52" s="47">
-        <f t="shared" si="84"/>
+        <f t="shared" si="86"/>
         <v>0.74083631276231932</v>
       </c>
       <c r="AU52" s="47">
-        <f t="shared" si="84"/>
+        <f t="shared" si="86"/>
         <v>0.7867690696456624</v>
       </c>
       <c r="AV52" s="47">
-        <f t="shared" si="84"/>
+        <f t="shared" si="86"/>
         <v>0.81421294415450485</v>
       </c>
       <c r="AW52" s="47">
-        <f t="shared" si="84"/>
+        <f t="shared" si="86"/>
         <v>0.81813389562467054</v>
       </c>
       <c r="AX52" s="47">
-        <f t="shared" si="84"/>
+        <f t="shared" si="86"/>
         <v>0.8081372157957718</v>
       </c>
       <c r="AY52" s="47">
-        <f t="shared" si="84"/>
+        <f t="shared" si="86"/>
         <v>0.81785763269784661</v>
       </c>
       <c r="AZ52" s="47">
-        <f t="shared" si="84"/>
+        <f t="shared" si="86"/>
         <v>0.81295590079598679</v>
       </c>
       <c r="BA52" s="47">
-        <f t="shared" si="84"/>
+        <f t="shared" si="86"/>
         <v>0.81830052477272164</v>
       </c>
       <c r="BB52" s="47">
-        <f t="shared" si="84"/>
+        <f t="shared" si="86"/>
         <v>0.81734385979415536</v>
       </c>
       <c r="BC52" s="47">
-        <f t="shared" si="84"/>
+        <f t="shared" si="86"/>
         <v>0.82105213404546962</v>
       </c>
       <c r="BD52" s="47">
-        <f t="shared" ref="BD52:BE52" si="85">BD39/BD37</f>
+        <f t="shared" ref="BD52:BE52" si="87">BD39/BD37</f>
         <v>0.82130229817324696</v>
       </c>
       <c r="BE52" s="47">
-        <f t="shared" si="85"/>
+        <f t="shared" si="87"/>
         <v>0.82034268763904605</v>
       </c>
       <c r="BO52" s="47">
-        <f t="shared" ref="BO52:BV52" si="86">BO39/BO37</f>
+        <f t="shared" ref="BO52:BV52" si="88">BO39/BO37</f>
         <v>0.73197091766555311</v>
       </c>
       <c r="BP52" s="47">
-        <f t="shared" si="86"/>
+        <f t="shared" si="88"/>
         <v>0.76181402439024393</v>
       </c>
       <c r="BQ52" s="47">
-        <f t="shared" si="86"/>
+        <f t="shared" si="88"/>
         <v>0.82729022942403341</v>
       </c>
       <c r="BR52" s="47">
-        <f t="shared" si="86"/>
+        <f t="shared" si="88"/>
         <v>0.84008255243195007</v>
       </c>
       <c r="BS52" s="47">
-        <f t="shared" si="86"/>
+        <f t="shared" si="88"/>
         <v>0.86290614371517471</v>
       </c>
       <c r="BT52" s="47">
-        <f t="shared" si="86"/>
+        <f t="shared" si="88"/>
         <v>0.86584015939783043</v>
       </c>
       <c r="BU52" s="47">
-        <f t="shared" si="86"/>
+        <f t="shared" si="88"/>
         <v>0.8324617643898421</v>
       </c>
       <c r="BV52" s="47">
-        <f t="shared" si="86"/>
+        <f t="shared" si="88"/>
         <v>0.81936998741106415</v>
       </c>
       <c r="BW52" s="47">
-        <f t="shared" ref="BW52:CA52" si="87">BW39/BW37</f>
+        <f t="shared" ref="BW52:CA52" si="89">BW39/BW37</f>
         <v>0.80582795323678236</v>
       </c>
       <c r="BX52" s="47">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>0.80794376277251567</v>
       </c>
       <c r="BY52" s="47">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>0.78347297378418479</v>
       </c>
       <c r="BZ52" s="47">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>0.8075714222176098</v>
       </c>
       <c r="CA52" s="47">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>0.81665157050717019</v>
       </c>
       <c r="CB52" s="57">
-        <v>0.82</v>
+        <v>0.81</v>
       </c>
       <c r="CC52" s="57">
-        <v>0.82</v>
+        <v>0.81499999999999995</v>
       </c>
       <c r="CD52" s="57">
         <v>0.82</v>
@@ -28823,278 +28912,278 @@
         <v>0.14461247637051039</v>
       </c>
       <c r="D53" s="47">
-        <f t="shared" ref="D53:BC53" si="88">D40/D37</f>
+        <f t="shared" ref="D53:BC53" si="90">D40/D37</f>
         <v>0.59543918918918914</v>
       </c>
       <c r="E53" s="47">
-        <f t="shared" si="88"/>
+        <f t="shared" si="90"/>
         <v>0.19334389857369255</v>
       </c>
       <c r="F53" s="47">
-        <f t="shared" si="88"/>
+        <f t="shared" si="90"/>
         <v>0.18738170347003155</v>
       </c>
       <c r="G53" s="47">
-        <f t="shared" si="88"/>
+        <f t="shared" si="90"/>
         <v>0.20096021947873799</v>
       </c>
       <c r="H53" s="47">
-        <f t="shared" si="88"/>
+        <f t="shared" si="90"/>
         <v>0.18974076116933261</v>
       </c>
       <c r="I53" s="47">
-        <f t="shared" si="88"/>
+        <f t="shared" si="90"/>
         <v>0.18303571428571427</v>
       </c>
       <c r="J53" s="47">
-        <f t="shared" si="88"/>
+        <f t="shared" si="90"/>
         <v>0.15822050290135398</v>
       </c>
       <c r="K53" s="47">
-        <f t="shared" si="88"/>
+        <f t="shared" si="90"/>
         <v>0.18185451638689049</v>
       </c>
       <c r="L53" s="47">
-        <f t="shared" si="88"/>
+        <f t="shared" si="90"/>
         <v>0.16907216494845362</v>
       </c>
       <c r="M53" s="47">
-        <f t="shared" si="88"/>
+        <f t="shared" si="90"/>
         <v>0.18982204183577897</v>
       </c>
       <c r="N53" s="47">
-        <f t="shared" si="88"/>
+        <f t="shared" si="90"/>
         <v>0.28849649441703451</v>
       </c>
       <c r="O53" s="47">
-        <f t="shared" si="88"/>
+        <f t="shared" si="90"/>
         <v>0.29974597798475866</v>
       </c>
       <c r="P53" s="47">
-        <f t="shared" si="88"/>
+        <f t="shared" si="90"/>
         <v>0.28946066303809997</v>
       </c>
       <c r="Q53" s="47">
-        <f t="shared" si="88"/>
+        <f t="shared" si="90"/>
         <v>0.28238169295712062</v>
       </c>
       <c r="R53" s="47">
-        <f t="shared" si="88"/>
+        <f t="shared" si="90"/>
         <v>0.22475179732968162</v>
       </c>
       <c r="S53" s="47">
-        <f t="shared" si="88"/>
+        <f t="shared" si="90"/>
         <v>0.24953548866592346</v>
       </c>
       <c r="T53" s="47">
-        <f t="shared" si="88"/>
+        <f t="shared" si="90"/>
         <v>0.22855811062771908</v>
       </c>
       <c r="U53" s="47">
-        <f t="shared" si="88"/>
+        <f t="shared" si="90"/>
         <v>0.21994009413778348</v>
       </c>
       <c r="V53" s="47">
-        <f t="shared" si="88"/>
+        <f t="shared" si="90"/>
         <v>0.17743217164263822</v>
       </c>
       <c r="W53" s="47">
-        <f t="shared" si="88"/>
+        <f t="shared" si="90"/>
         <v>0.22833665338645417</v>
       </c>
       <c r="X53" s="47">
-        <f t="shared" si="88"/>
+        <f t="shared" si="90"/>
         <v>0.20587919751099668</v>
       </c>
       <c r="Y53" s="47">
-        <f t="shared" si="88"/>
+        <f t="shared" si="90"/>
         <v>0.19868319132455461</v>
       </c>
       <c r="Z53" s="47">
-        <f t="shared" si="88"/>
+        <f t="shared" si="90"/>
         <v>0.15024668516805428</v>
       </c>
       <c r="AA53" s="47">
-        <f t="shared" si="88"/>
+        <f t="shared" si="90"/>
         <v>0.18702991810128697</v>
       </c>
       <c r="AB53" s="47">
-        <f t="shared" si="88"/>
+        <f t="shared" si="90"/>
         <v>0.19068853450230519</v>
       </c>
       <c r="AC53" s="47">
-        <f t="shared" si="88"/>
+        <f t="shared" si="90"/>
         <v>0.19356013695636337</v>
       </c>
       <c r="AD53" s="47">
-        <f t="shared" si="88"/>
+        <f t="shared" si="90"/>
         <v>0.16879508099798984</v>
       </c>
       <c r="AE53" s="47">
-        <f t="shared" si="88"/>
+        <f t="shared" si="90"/>
         <v>0.1896929097300524</v>
       </c>
       <c r="AF53" s="47">
-        <f t="shared" si="88"/>
+        <f t="shared" si="90"/>
         <v>0.19631647518654508</v>
       </c>
       <c r="AG53" s="47">
-        <f t="shared" si="88"/>
+        <f t="shared" si="90"/>
         <v>0.20099705415816904</v>
       </c>
       <c r="AH53" s="47">
-        <f t="shared" si="88"/>
+        <f t="shared" si="90"/>
         <v>0.1839009581633621</v>
       </c>
       <c r="AI53" s="47">
-        <f t="shared" si="88"/>
+        <f t="shared" si="90"/>
         <v>0.22636297006258105</v>
       </c>
       <c r="AJ53" s="47">
-        <f t="shared" si="88"/>
+        <f t="shared" si="90"/>
         <v>0.23877561941456626</v>
       </c>
       <c r="AK53" s="47">
-        <f t="shared" si="88"/>
+        <f t="shared" si="90"/>
         <v>0.22184443409408477</v>
       </c>
       <c r="AL53" s="47">
-        <f t="shared" si="88"/>
+        <f t="shared" si="90"/>
         <v>0.18549392611592033</v>
       </c>
       <c r="AM53" s="47">
-        <f t="shared" si="88"/>
+        <f t="shared" si="90"/>
         <v>0.19857857934354819</v>
       </c>
       <c r="AN53" s="47">
-        <f t="shared" si="88"/>
+        <f t="shared" si="90"/>
         <v>0.2096502390205317</v>
       </c>
       <c r="AO53" s="47">
-        <f t="shared" si="88"/>
+        <f t="shared" si="90"/>
         <v>0.21771802826611514</v>
       </c>
       <c r="AP53" s="47">
-        <f t="shared" si="88"/>
+        <f t="shared" si="90"/>
         <v>0.20926019423242553</v>
       </c>
       <c r="AQ53" s="47">
-        <f t="shared" si="88"/>
+        <f t="shared" si="90"/>
         <v>0.27615737422961156</v>
       </c>
       <c r="AR53" s="47">
-        <f t="shared" si="88"/>
+        <f t="shared" si="90"/>
         <v>0.30150579418499757</v>
       </c>
       <c r="AS53" s="47">
-        <f t="shared" si="88"/>
+        <f t="shared" si="90"/>
         <v>0.33087969979071952</v>
       </c>
       <c r="AT53" s="47">
-        <f t="shared" si="88"/>
+        <f t="shared" si="90"/>
         <v>0.30377739779263174</v>
       </c>
       <c r="AU53" s="47">
-        <f t="shared" si="88"/>
+        <f t="shared" si="90"/>
         <v>0.32749170884971202</v>
       </c>
       <c r="AV53" s="47">
-        <f t="shared" si="88"/>
+        <f t="shared" si="90"/>
         <v>0.29200912528516515</v>
       </c>
       <c r="AW53" s="47">
-        <f t="shared" si="88"/>
+        <f t="shared" si="90"/>
         <v>0.27063199203420607</v>
       </c>
       <c r="AX53" s="47">
-        <f t="shared" si="88"/>
+        <f t="shared" si="90"/>
         <v>0.2621908655763861</v>
       </c>
       <c r="AY53" s="47">
-        <f t="shared" si="88"/>
+        <f t="shared" si="90"/>
         <v>0.27370731038266355</v>
       </c>
       <c r="AZ53" s="47">
-        <f t="shared" si="88"/>
+        <f t="shared" si="90"/>
         <v>0.26968851577896652</v>
       </c>
       <c r="BA53" s="47">
-        <f t="shared" si="88"/>
+        <f t="shared" si="90"/>
         <v>0.27537017418512405</v>
       </c>
       <c r="BB53" s="47">
-        <f t="shared" si="88"/>
+        <f t="shared" si="90"/>
         <v>0.25174637291778612</v>
       </c>
       <c r="BC53" s="47">
-        <f t="shared" si="88"/>
+        <f t="shared" si="90"/>
         <v>0.28713900836602541</v>
       </c>
       <c r="BD53" s="47">
-        <f t="shared" ref="BD53:BE53" si="89">BD40/BD37</f>
+        <f t="shared" ref="BD53:BE53" si="91">BD40/BD37</f>
         <v>0.27237141173499452</v>
       </c>
       <c r="BE53" s="47">
-        <f t="shared" si="89"/>
+        <f t="shared" si="91"/>
         <v>0.29553881581515162</v>
       </c>
       <c r="BO53" s="47">
-        <f t="shared" ref="BO53:BV53" si="90">BO40/BO37</f>
+        <f t="shared" ref="BO53:BV53" si="92">BO40/BO37</f>
         <v>0.27490666142660641</v>
       </c>
       <c r="BP53" s="47">
-        <f t="shared" si="90"/>
+        <f t="shared" si="92"/>
         <v>0.1797510162601626</v>
       </c>
       <c r="BQ53" s="47">
-        <f t="shared" si="90"/>
+        <f t="shared" si="92"/>
         <v>0.21386170383442965</v>
       </c>
       <c r="BR53" s="47">
-        <f t="shared" si="90"/>
+        <f t="shared" si="92"/>
         <v>0.26863007585899151</v>
       </c>
       <c r="BS53" s="47">
-        <f t="shared" si="90"/>
+        <f t="shared" si="92"/>
         <v>0.21416166148057023</v>
       </c>
       <c r="BT53" s="47">
-        <f t="shared" si="90"/>
+        <f t="shared" si="92"/>
         <v>0.19073623102846038</v>
       </c>
       <c r="BU53" s="47">
-        <f t="shared" si="90"/>
+        <f t="shared" si="92"/>
         <v>0.18397865253053475</v>
       </c>
       <c r="BV53" s="47">
-        <f t="shared" si="90"/>
+        <f t="shared" si="92"/>
         <v>0.19237025616362788</v>
       </c>
       <c r="BW53" s="47">
-        <f t="shared" ref="BW53:CA53" si="91">BW40/BW37</f>
+        <f t="shared" ref="BW53:CA53" si="93">BW40/BW37</f>
         <v>0.21458733205374281</v>
       </c>
       <c r="BX53" s="47">
-        <f t="shared" si="91"/>
+        <f t="shared" si="93"/>
         <v>0.20906647219937419</v>
       </c>
       <c r="BY53" s="47">
-        <f t="shared" si="91"/>
+        <f t="shared" si="93"/>
         <v>0.30304693462768739</v>
       </c>
       <c r="BZ53" s="47">
-        <f t="shared" si="91"/>
+        <f t="shared" si="93"/>
         <v>0.28526634149234259</v>
       </c>
       <c r="CA53" s="47">
-        <f t="shared" si="91"/>
+        <f t="shared" si="93"/>
         <v>0.26670354587510109</v>
       </c>
       <c r="CB53" s="57">
         <v>0.28999999999999998</v>
       </c>
       <c r="CC53" s="57">
-        <v>0.29499999999999998</v>
+        <v>0.32</v>
       </c>
       <c r="CD53" s="57">
         <v>0.3</v>
@@ -29130,271 +29219,271 @@
         <v>0.23345935727788281</v>
       </c>
       <c r="D54" s="47">
-        <f t="shared" ref="D54:BC54" si="92">D43/D37</f>
+        <f t="shared" ref="D54:BC54" si="94">D43/D37</f>
         <v>0.7221283783783784</v>
       </c>
       <c r="E54" s="47">
-        <f t="shared" si="92"/>
+        <f t="shared" si="94"/>
         <v>0.25277337559429475</v>
       </c>
       <c r="F54" s="47">
-        <f t="shared" si="92"/>
+        <f t="shared" si="94"/>
         <v>0.23154574132492114</v>
       </c>
       <c r="G54" s="47">
-        <f t="shared" si="92"/>
+        <f t="shared" si="94"/>
         <v>0.25994513031550071</v>
       </c>
       <c r="H54" s="47">
-        <f t="shared" si="92"/>
+        <f t="shared" si="94"/>
         <v>0.24379481522338664</v>
       </c>
       <c r="I54" s="47">
-        <f t="shared" si="92"/>
+        <f t="shared" si="94"/>
         <v>0.20039682539682541</v>
       </c>
       <c r="J54" s="47">
-        <f t="shared" si="92"/>
+        <f t="shared" si="94"/>
         <v>0.21392649903288202</v>
       </c>
       <c r="K54" s="47">
-        <f t="shared" si="92"/>
+        <f t="shared" si="94"/>
         <v>0.2038369304556355</v>
       </c>
       <c r="L54" s="47">
-        <f t="shared" si="92"/>
+        <f t="shared" si="94"/>
         <v>0.19072164948453607</v>
       </c>
       <c r="M54" s="47">
-        <f t="shared" si="92"/>
+        <f t="shared" si="94"/>
         <v>0.19762722447705278</v>
       </c>
       <c r="N54" s="47">
-        <f t="shared" si="92"/>
+        <f t="shared" si="94"/>
         <v>0.2479875357050117</v>
       </c>
       <c r="O54" s="47">
-        <f t="shared" si="92"/>
+        <f t="shared" si="94"/>
         <v>0.2523285351397121</v>
       </c>
       <c r="P54" s="47">
-        <f t="shared" si="92"/>
+        <f t="shared" si="94"/>
         <v>0.23033151904997526</v>
       </c>
       <c r="Q54" s="47">
-        <f t="shared" si="92"/>
+        <f t="shared" si="94"/>
         <v>0.23350366585203289</v>
       </c>
       <c r="R54" s="47">
-        <f t="shared" si="92"/>
+        <f t="shared" si="94"/>
         <v>0.19582334816843547</v>
       </c>
       <c r="S54" s="47">
-        <f t="shared" si="92"/>
+        <f t="shared" si="94"/>
         <v>0.22129319955406912</v>
       </c>
       <c r="T54" s="47">
-        <f t="shared" si="92"/>
+        <f t="shared" si="94"/>
         <v>0.20416407706650094</v>
       </c>
       <c r="U54" s="47">
-        <f t="shared" si="92"/>
+        <f t="shared" si="94"/>
         <v>0.19469405220367994</v>
       </c>
       <c r="V54" s="47">
-        <f t="shared" si="92"/>
+        <f t="shared" si="94"/>
         <v>0.18537859007832899</v>
       </c>
       <c r="W54" s="47">
-        <f t="shared" si="92"/>
+        <f t="shared" si="94"/>
         <v>0.21314741035856574</v>
       </c>
       <c r="X54" s="47">
-        <f t="shared" si="92"/>
+        <f t="shared" si="94"/>
         <v>0.18925008046346958</v>
       </c>
       <c r="Y54" s="47">
-        <f t="shared" si="92"/>
+        <f t="shared" si="94"/>
         <v>0.16518202943454685</v>
       </c>
       <c r="Z54" s="47">
-        <f t="shared" si="92"/>
+        <f t="shared" si="94"/>
         <v>0.1588035769349368</v>
       </c>
       <c r="AA54" s="47">
-        <f t="shared" si="92"/>
+        <f t="shared" si="94"/>
         <v>0.19655691124853752</v>
       </c>
       <c r="AB54" s="47">
-        <f t="shared" si="92"/>
+        <f t="shared" si="94"/>
         <v>0.19885118282820649</v>
       </c>
       <c r="AC54" s="47">
-        <f t="shared" si="92"/>
+        <f t="shared" si="94"/>
         <v>0.20914985065928463</v>
       </c>
       <c r="AD54" s="47">
-        <f t="shared" si="92"/>
+        <f t="shared" si="94"/>
         <v>0.20355918174293486</v>
       </c>
       <c r="AE54" s="47">
-        <f t="shared" si="92"/>
+        <f t="shared" si="94"/>
         <v>0.40352855342574784</v>
       </c>
       <c r="AF54" s="47">
-        <f t="shared" si="92"/>
+        <f t="shared" si="94"/>
         <v>0.3338860594575388</v>
       </c>
       <c r="AG54" s="47">
-        <f t="shared" si="92"/>
+        <f t="shared" si="94"/>
         <v>0.21323362791751643</v>
       </c>
       <c r="AH54" s="47">
-        <f t="shared" si="92"/>
+        <f t="shared" si="94"/>
         <v>0.23029124371501755</v>
       </c>
       <c r="AI54" s="47">
-        <f t="shared" si="92"/>
+        <f t="shared" si="94"/>
         <v>0.24637762868579804</v>
       </c>
       <c r="AJ54" s="47">
-        <f t="shared" si="92"/>
+        <f t="shared" si="94"/>
         <v>0.23722373842778402</v>
       </c>
       <c r="AK54" s="47">
-        <f t="shared" si="92"/>
+        <f t="shared" si="94"/>
         <v>0.20833721471821146</v>
       </c>
       <c r="AL54" s="47">
-        <f t="shared" si="92"/>
+        <f t="shared" si="94"/>
         <v>0.17380926935271276</v>
       </c>
       <c r="AM54" s="47">
-        <f t="shared" si="92"/>
+        <f t="shared" si="94"/>
         <v>0.17060868900691606</v>
       </c>
       <c r="AN54" s="47">
-        <f t="shared" si="92"/>
+        <f t="shared" si="94"/>
         <v>0.17935137737730852</v>
       </c>
       <c r="AO54" s="47">
-        <f t="shared" si="92"/>
+        <f t="shared" si="94"/>
         <v>0.22406066873491901</v>
       </c>
       <c r="AP54" s="47">
-        <f t="shared" si="92"/>
+        <f t="shared" si="94"/>
         <v>0.22844584360428855</v>
       </c>
       <c r="AQ54" s="47">
-        <f t="shared" si="92"/>
+        <f t="shared" si="94"/>
         <v>0.20323921456213273</v>
       </c>
       <c r="AR54" s="47">
-        <f t="shared" si="92"/>
+        <f t="shared" si="94"/>
         <v>0.22836721948511554</v>
       </c>
       <c r="AS54" s="47">
-        <f t="shared" si="92"/>
+        <f t="shared" si="94"/>
         <v>0.25849751028361118</v>
       </c>
       <c r="AT54" s="47">
-        <f t="shared" si="92"/>
+        <f t="shared" si="94"/>
         <v>0.23814705425151561</v>
       </c>
       <c r="AU54" s="47">
-        <f t="shared" si="92"/>
+        <f t="shared" si="94"/>
         <v>0.20698202129516496</v>
       </c>
       <c r="AV54" s="47">
-        <f t="shared" si="92"/>
+        <f t="shared" si="94"/>
         <v>0.22869464670770961</v>
       </c>
       <c r="AW54" s="47">
-        <f t="shared" si="92"/>
+        <f t="shared" si="94"/>
         <v>0.14487787735020208</v>
       </c>
       <c r="AX54" s="47">
-        <f t="shared" si="92"/>
+        <f t="shared" si="94"/>
         <v>0.13749002792181891</v>
       </c>
       <c r="AY54" s="47">
-        <f t="shared" si="92"/>
+        <f t="shared" si="94"/>
         <v>0.16510766698669593</v>
       </c>
       <c r="AZ54" s="47">
-        <f t="shared" si="92"/>
+        <f t="shared" si="94"/>
         <v>0.16326687312840726</v>
       </c>
       <c r="BA54" s="47">
-        <f t="shared" si="92"/>
+        <f t="shared" si="94"/>
         <v>0.11547463598511912</v>
       </c>
       <c r="BB54" s="47">
-        <f t="shared" si="92"/>
+        <f t="shared" si="94"/>
         <v>8.2709874757161156E-2</v>
       </c>
       <c r="BC54" s="47">
-        <f t="shared" si="92"/>
+        <f t="shared" si="94"/>
         <v>0.11903861606087819</v>
       </c>
       <c r="BD54" s="47">
-        <f t="shared" ref="BD54:BE54" si="93">BD43/BD37</f>
+        <f t="shared" ref="BD54:BE54" si="95">BD43/BD37</f>
         <v>0.1187389510901591</v>
       </c>
       <c r="BE54" s="47">
-        <f t="shared" si="93"/>
+        <f t="shared" si="95"/>
         <v>0.12405838960227938</v>
       </c>
       <c r="BO54" s="47">
-        <f t="shared" ref="BO54:BV54" si="94">BO43/BO37</f>
+        <f t="shared" ref="BO54:BV54" si="96">BO43/BO37</f>
         <v>0.35134604047946549</v>
       </c>
       <c r="BP54" s="47">
-        <f t="shared" si="94"/>
+        <f t="shared" si="96"/>
         <v>0.22586382113821138</v>
       </c>
       <c r="BQ54" s="47">
-        <f t="shared" si="94"/>
+        <f t="shared" si="96"/>
         <v>0.21281886731910798</v>
       </c>
       <c r="BR54" s="47">
-        <f t="shared" si="94"/>
+        <f t="shared" si="96"/>
         <v>0.22423025435073629</v>
       </c>
       <c r="BS54" s="47">
-        <f t="shared" si="94"/>
+        <f t="shared" si="96"/>
         <v>0.19910992112309139</v>
       </c>
       <c r="BT54" s="47">
-        <f t="shared" si="94"/>
+        <f t="shared" si="96"/>
         <v>0.17814183455095564</v>
       </c>
       <c r="BU54" s="47">
-        <f t="shared" si="94"/>
+        <f t="shared" si="96"/>
         <v>0.20231741824563917</v>
       </c>
       <c r="BV54" s="47">
-        <f t="shared" si="94"/>
+        <f t="shared" si="96"/>
         <v>0.28772083681061433</v>
       </c>
       <c r="BW54" s="47">
-        <f t="shared" ref="BW54:CA54" si="95">BW43/BW37</f>
+        <f t="shared" ref="BW54:CA54" si="97">BW43/BW37</f>
         <v>0.21119060082591753</v>
       </c>
       <c r="BX54" s="47">
-        <f t="shared" si="95"/>
+        <f t="shared" si="97"/>
         <v>0.20242688397255976</v>
       </c>
       <c r="BY54" s="47">
-        <f t="shared" si="95"/>
+        <f t="shared" si="97"/>
         <v>0.2322119218928213</v>
       </c>
       <c r="BZ54" s="47">
-        <f t="shared" si="95"/>
+        <f t="shared" si="97"/>
         <v>0.17574980356110362</v>
       </c>
       <c r="CA54" s="47">
-        <f t="shared" si="95"/>
+        <f t="shared" si="97"/>
         <v>0.12818767059166813</v>
       </c>
       <c r="CB54" s="57">
@@ -29437,311 +29526,311 @@
         <v>0.36011342155009451</v>
       </c>
       <c r="D55" s="47">
-        <f t="shared" ref="D55:BC55" si="96">D44/D37</f>
+        <f t="shared" ref="D55:BC55" si="98">D44/D37</f>
         <v>-0.62753378378378377</v>
       </c>
       <c r="E55" s="47">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>0.29873217115689382</v>
       </c>
       <c r="F55" s="47">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>0.3299684542586751</v>
       </c>
       <c r="G55" s="47">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>0.25582990397805211</v>
       </c>
       <c r="H55" s="47">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>0.3099834528405957</v>
       </c>
       <c r="I55" s="47">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>0.36507936507936506</v>
       </c>
       <c r="J55" s="47">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>0.43829787234042555</v>
       </c>
       <c r="K55" s="47">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>0.42965627498001596</v>
       </c>
       <c r="L55" s="47">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>0.47766323024054985</v>
       </c>
       <c r="M55" s="47">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>0.43615360599438024</v>
       </c>
       <c r="N55" s="47">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>0.29394962347442222</v>
       </c>
       <c r="O55" s="47">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>0.26333615580016934</v>
       </c>
       <c r="P55" s="47">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>0.31494309747649679</v>
       </c>
       <c r="Q55" s="47">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>0.32415018884692293</v>
       </c>
       <c r="R55" s="47">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>0.43820609380349196</v>
       </c>
       <c r="S55" s="47">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>0.37346711259754739</v>
       </c>
       <c r="T55" s="47">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>0.42479801118707272</v>
       </c>
       <c r="U55" s="47">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>0.44458707744972187</v>
       </c>
       <c r="V55" s="47">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>0.5183335225337723</v>
       </c>
       <c r="W55" s="47">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>0.41421812749003983</v>
       </c>
       <c r="X55" s="47">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>0.47215963952365625</v>
       </c>
       <c r="Y55" s="47">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>0.49593338497288925</v>
       </c>
       <c r="Z55" s="47">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>0.566836262719704</v>
       </c>
       <c r="AA55" s="47">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>0.45537355841551064</v>
       </c>
       <c r="AB55" s="47">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>0.44312599198851182</v>
       </c>
       <c r="AC55" s="47">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>0.42114081736723247</v>
       </c>
       <c r="AD55" s="47">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>0.46233889085964291</v>
       </c>
       <c r="AE55" s="47">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>0.22000397957153281</v>
       </c>
       <c r="AF55" s="47">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>0.27395475541869002</v>
       </c>
       <c r="AG55" s="47">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>0.40703602991162474</v>
       </c>
       <c r="AH55" s="47">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>0.42016886443411439</v>
       </c>
       <c r="AI55" s="47">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>0.33224333314540228</v>
       </c>
       <c r="AJ55" s="47">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>0.31909883876491679</v>
       </c>
       <c r="AK55" s="47">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>0.37447601304145317</v>
       </c>
       <c r="AL55" s="47">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>0.45509600655480748</v>
       </c>
       <c r="AM55" s="47">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>0.43475602766420846</v>
       </c>
       <c r="AN55" s="47">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>0.42531898063761736</v>
       </c>
       <c r="AO55" s="47">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>0.35928990003447087</v>
       </c>
       <c r="AP55" s="47">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>0.37376377297971547</v>
       </c>
       <c r="AQ55" s="47">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>0.30543213415508097</v>
       </c>
       <c r="AR55" s="47">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>0.28998681562695161</v>
       </c>
       <c r="AS55" s="47">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>0.20437324096124701</v>
       </c>
       <c r="AT55" s="47">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>0.19891186071817193</v>
       </c>
       <c r="AU55" s="47">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>0.25229533950078548</v>
       </c>
       <c r="AV55" s="47">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>0.29350917216163003</v>
       </c>
       <c r="AW55" s="47">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>0.40262402624026239</v>
       </c>
       <c r="AX55" s="47">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>0.40845632229756679</v>
       </c>
       <c r="AY55" s="47">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>0.37904265532848719</v>
       </c>
       <c r="AZ55" s="47">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>0.38000051188861306</v>
       </c>
       <c r="BA55" s="47">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>0.4274557146024785</v>
       </c>
       <c r="BB55" s="47">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>0.48288761211920805</v>
       </c>
       <c r="BC55" s="47">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>0.41487450961856598</v>
       </c>
       <c r="BD55" s="47">
-        <f t="shared" ref="BD55:BE55" si="97">BD44/BD37</f>
+        <f t="shared" ref="BD55:BE55" si="99">BD44/BD37</f>
         <v>0.43019193534809325</v>
       </c>
       <c r="BE55" s="47">
-        <f t="shared" si="97"/>
+        <f t="shared" si="99"/>
         <v>0.4007454822216151</v>
       </c>
       <c r="BO55" s="47">
-        <f t="shared" ref="BO55:BV55" si="98">BO44/BO37</f>
+        <f t="shared" ref="BO55:BV55" si="100">BO44/BO37</f>
         <v>0.10571821575948123</v>
       </c>
       <c r="BP55" s="47">
-        <f t="shared" si="98"/>
+        <f t="shared" si="100"/>
         <v>0.35619918699186992</v>
       </c>
       <c r="BQ55" s="47">
-        <f t="shared" si="98"/>
+        <f t="shared" si="100"/>
         <v>0.40060965827049577</v>
       </c>
       <c r="BR55" s="47">
-        <f t="shared" si="98"/>
+        <f t="shared" si="100"/>
         <v>0.34722222222222221</v>
       </c>
       <c r="BS55" s="47">
-        <f t="shared" si="98"/>
+        <f t="shared" si="100"/>
         <v>0.44963456111151312</v>
       </c>
       <c r="BT55" s="47">
-        <f t="shared" si="98"/>
+        <f t="shared" si="100"/>
         <v>0.49696209381841439</v>
       </c>
       <c r="BU55" s="47">
-        <f t="shared" si="98"/>
+        <f t="shared" si="100"/>
         <v>0.44616569361366809</v>
       </c>
       <c r="BV55" s="47">
-        <f t="shared" si="98"/>
+        <f t="shared" si="100"/>
         <v>0.33927889443682191</v>
       </c>
       <c r="BW55" s="47">
-        <f t="shared" ref="BW55:CA55" si="99">BW44/BW37</f>
+        <f t="shared" ref="BW55:CA55" si="101">BW44/BW37</f>
         <v>0.3800500203571221</v>
       </c>
       <c r="BX55" s="47">
-        <f t="shared" si="99"/>
+        <f t="shared" si="101"/>
         <v>0.39645040660058173</v>
       </c>
       <c r="BY55" s="47">
-        <f t="shared" si="99"/>
+        <f t="shared" si="101"/>
         <v>0.24821411726367604</v>
       </c>
       <c r="BZ55" s="47">
-        <f t="shared" si="99"/>
+        <f t="shared" si="101"/>
         <v>0.34655527716416362</v>
       </c>
       <c r="CA55" s="47">
-        <f t="shared" si="99"/>
+        <f t="shared" si="101"/>
         <v>0.42176035404040096</v>
       </c>
       <c r="CB55" s="57">
         <f>CB44/CB37</f>
-        <v>0.40749999999999997</v>
+        <v>0.39750000000000013</v>
       </c>
       <c r="CC55" s="57">
-        <f t="shared" ref="CC55:CK55" si="100">CC44/CC37</f>
-        <v>0.39999999999999991</v>
+        <f t="shared" ref="CC55:CK55" si="102">CC44/CC37</f>
+        <v>0.36999999999999994</v>
       </c>
       <c r="CD55" s="57">
-        <f t="shared" si="100"/>
+        <f t="shared" si="102"/>
         <v>0.39799999999999996</v>
       </c>
       <c r="CE55" s="57">
-        <f t="shared" si="100"/>
+        <f t="shared" si="102"/>
         <v>0.42999999999999994</v>
       </c>
       <c r="CF55" s="57">
-        <f t="shared" si="100"/>
+        <f t="shared" si="102"/>
         <v>0.45200000000000007</v>
       </c>
       <c r="CG55" s="57">
-        <f t="shared" si="100"/>
+        <f t="shared" si="102"/>
         <v>0.46400000000000002</v>
       </c>
       <c r="CH55" s="57">
-        <f t="shared" si="100"/>
+        <f t="shared" si="102"/>
         <v>0.47599999999999998</v>
       </c>
       <c r="CI55" s="57">
-        <f t="shared" si="100"/>
+        <f t="shared" si="102"/>
         <v>0.48699999999999999</v>
       </c>
       <c r="CJ55" s="57">
-        <f t="shared" si="100"/>
+        <f t="shared" si="102"/>
         <v>0.49799999999999994</v>
       </c>
       <c r="CK55" s="57">
-        <f t="shared" si="100"/>
+        <f t="shared" si="102"/>
         <v>0.50900000000000001</v>
       </c>
     </row>
@@ -29754,275 +29843,275 @@
         <v>0.46335078534031415</v>
       </c>
       <c r="D56" s="47">
-        <f t="shared" ref="D56:BC56" si="101">D47/D46</f>
+        <f t="shared" ref="D56:BC56" si="103">D47/D46</f>
         <v>0.79477124183006531</v>
       </c>
       <c r="E56" s="47">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>1.1586021505376345</v>
       </c>
       <c r="F56" s="47">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>0.87326732673267327</v>
       </c>
       <c r="G56" s="47">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>0.37960339943342775</v>
       </c>
       <c r="H56" s="47">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>0.38899082568807342</v>
       </c>
       <c r="I56" s="47">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>0.41460055096418735</v>
       </c>
       <c r="J56" s="47">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>0.53716814159292037</v>
       </c>
       <c r="K56" s="47">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>0.40279069767441861</v>
       </c>
       <c r="L56" s="47">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>0.42929292929292928</v>
       </c>
       <c r="M56" s="47">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>0.3967065868263473</v>
       </c>
       <c r="N56" s="49">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>0.37017070979335132</v>
       </c>
       <c r="O56" s="47">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>0.45064377682403434</v>
       </c>
       <c r="P56" s="47">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>0.43519245875883739</v>
       </c>
       <c r="Q56" s="47">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>0.37430167597765363</v>
       </c>
       <c r="R56" s="47">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>0.38951896754008603</v>
       </c>
       <c r="S56" s="47">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>0.15876089060987417</v>
       </c>
       <c r="T56" s="47">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>0.17102396514161219</v>
       </c>
       <c r="U56" s="47">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>0.16972187104930467</v>
       </c>
       <c r="V56" s="47">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>0.21283634759594178</v>
       </c>
       <c r="W56" s="47">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>0.10093896713615023</v>
       </c>
       <c r="X56" s="47">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>0.13235294117647059</v>
       </c>
       <c r="Y56" s="47">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>0.10103132161955691</v>
       </c>
       <c r="Z56" s="47">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>0.42790136692575714</v>
       </c>
       <c r="AA56" s="47">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>0.11087344028520499</v>
       </c>
       <c r="AB56" s="47">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>0.12985685071574643</v>
       </c>
       <c r="AC56" s="47">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>0.13108930987821379</v>
       </c>
       <c r="AD56" s="47">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>0.13674570317400578</v>
       </c>
       <c r="AE56" s="47">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>0.30241240666283747</v>
       </c>
       <c r="AF56" s="47">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>0.45860927152317882</v>
       </c>
       <c r="AG56" s="47">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>0.16891799699822621</v>
       </c>
       <c r="AH56" s="47">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>0.19849492856363835</v>
       </c>
       <c r="AI56" s="47">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>0.16362395495649207</v>
       </c>
       <c r="AJ56" s="47">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>0.15543956940140272</v>
       </c>
       <c r="AK56" s="47">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>3.5288331488995447E-2</v>
       </c>
       <c r="AL56" s="47">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>0.14055917273075449</v>
       </c>
       <c r="AM56" s="47">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>0.17438928975049986</v>
       </c>
       <c r="AN56" s="47">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>0.16934388236234316</v>
       </c>
       <c r="AO56" s="47">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>0.12976810222432561</v>
       </c>
       <c r="AP56" s="47">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>0.19034873651893253</v>
       </c>
       <c r="AQ56" s="47">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>0.1619892231701841</v>
       </c>
       <c r="AR56" s="47">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>0.18311751771316884</v>
       </c>
       <c r="AS56" s="47">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>0.21180057388809181</v>
       </c>
       <c r="AT56" s="47">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>0.24329159212880144</v>
       </c>
       <c r="AU56" s="47">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>0.21869440262761736</v>
       </c>
       <c r="AV56" s="47">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>0.16194985472936618</v>
       </c>
       <c r="AW56" s="47">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>0.1738231098430813</v>
       </c>
       <c r="AX56" s="47">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>0.16599238457877202</v>
       </c>
       <c r="AY56" s="47">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>0.12789959811041388</v>
       </c>
       <c r="AZ56" s="47">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>0.10863233152389778</v>
       </c>
       <c r="BA56" s="47">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>0.11973964762652901</v>
       </c>
       <c r="BB56" s="47">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>0.115234375</v>
       </c>
       <c r="BC56" s="47">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>9.4549015341094556E-2</v>
       </c>
       <c r="BD56" s="47">
-        <f t="shared" ref="BD56:BE56" si="102">BD47/BD46</f>
+        <f t="shared" ref="BD56:BE56" si="104">BD47/BD46</f>
         <v>0.10699327943897925</v>
       </c>
       <c r="BE56" s="47">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>0.87494806813460735</v>
       </c>
       <c r="BO56" s="47">
-        <f t="shared" ref="BO56:BV56" si="103">BO47/BO46</f>
+        <f t="shared" ref="BO56:BV56" si="105">BO47/BO46</f>
         <v>0.89271255060728749</v>
       </c>
       <c r="BP56" s="47">
-        <f t="shared" si="103"/>
+        <f t="shared" si="105"/>
         <v>0.45533769063180829</v>
       </c>
       <c r="BQ56" s="47">
-        <f t="shared" si="103"/>
+        <f t="shared" si="105"/>
         <v>0.40122199592668023</v>
       </c>
       <c r="BR56" s="47">
-        <f t="shared" si="103"/>
+        <f t="shared" si="105"/>
         <v>0.4045850823377462</v>
       </c>
       <c r="BS56" s="47">
-        <f t="shared" si="103"/>
+        <f t="shared" si="105"/>
         <v>0.18381530595941845</v>
       </c>
       <c r="BT56" s="47">
-        <f t="shared" si="103"/>
+        <f t="shared" si="105"/>
         <v>0.22627949888316987</v>
       </c>
       <c r="BU56" s="47">
-        <f t="shared" si="103"/>
+        <f t="shared" si="105"/>
         <v>0.12811009029612397</v>
       </c>
       <c r="BV56" s="47">
-        <f t="shared" si="103"/>
+        <f t="shared" si="105"/>
         <v>0.25499758181525067</v>
       </c>
       <c r="BW56" s="47">
-        <f t="shared" ref="BW56:CA56" si="104">BW47/BW46</f>
+        <f t="shared" ref="BW56:CA56" si="106">BW47/BW46</f>
         <v>0.12157926461723931</v>
       </c>
       <c r="BX56" s="47">
-        <f t="shared" si="104"/>
+        <f t="shared" si="106"/>
         <v>0.16737162676592504</v>
       </c>
       <c r="BY56" s="47">
-        <f t="shared" si="104"/>
+        <f t="shared" si="106"/>
         <v>0.19497553697213643</v>
       </c>
       <c r="BZ56" s="47">
-        <f t="shared" si="104"/>
+        <f t="shared" si="106"/>
         <v>0.17563464620055663</v>
       </c>
       <c r="CA56" s="47">
-        <f t="shared" si="104"/>
+        <f t="shared" si="106"/>
         <v>0.11750137978857393</v>
       </c>
       <c r="CB56" s="57">
-        <v>0.21</v>
+        <v>0.29499999999999998</v>
       </c>
       <c r="CC56" s="57">
         <v>0.21</v>
@@ -30061,311 +30150,311 @@
         <v>0.1937618147448015</v>
       </c>
       <c r="D57" s="47">
-        <f t="shared" ref="D57:BC57" si="105">D48/D37</f>
+        <f t="shared" ref="D57:BC57" si="107">D48/D37</f>
         <v>-0.13260135135135134</v>
       </c>
       <c r="E57" s="47">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>-4.6751188589540409E-2</v>
       </c>
       <c r="F57" s="47">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>4.0378548895899057E-2</v>
       </c>
       <c r="G57" s="47">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>0.15020576131687244</v>
       </c>
       <c r="H57" s="47">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>0.18367346938775511</v>
       </c>
       <c r="I57" s="47">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>0.21081349206349206</v>
       </c>
       <c r="J57" s="47">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>0.202321083172147</v>
       </c>
       <c r="K57" s="47">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>0.25659472422062352</v>
       </c>
       <c r="L57" s="47">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>0.27182130584192438</v>
       </c>
       <c r="M57" s="47">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>0.25163908835466747</v>
       </c>
       <c r="N57" s="47">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>0.18203064139184627</v>
       </c>
       <c r="O57" s="47">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>0.14451030200395146</v>
       </c>
       <c r="P57" s="47">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>0.17788223651657595</v>
       </c>
       <c r="Q57" s="47">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>0.19906687402799378</v>
       </c>
       <c r="R57" s="47">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>0.26720301266689489</v>
       </c>
       <c r="S57" s="47">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>0.32292827945001856</v>
       </c>
       <c r="T57" s="47">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>0.35472343070229956</v>
       </c>
       <c r="U57" s="47">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>0.37469690486378548</v>
       </c>
       <c r="V57" s="47">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>0.40515381995686228</v>
       </c>
       <c r="W57" s="47">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>0.38147410358565736</v>
       </c>
       <c r="X57" s="47">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>0.41776633408432573</v>
       </c>
       <c r="Y57" s="47">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>0.4557513555383424</v>
       </c>
       <c r="Z57" s="47">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>0.32909343200740054</v>
       </c>
       <c r="AA57" s="47">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>0.41684773524987462</v>
       </c>
       <c r="AB57" s="47">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>0.38591187363011109</v>
       </c>
       <c r="AC57" s="47">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>0.37422597799956292</v>
       </c>
       <c r="AD57" s="47">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>0.40682275038429705</v>
       </c>
       <c r="AE57" s="47">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>0.16110632088611793</v>
       </c>
       <c r="AF57" s="47">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>0.15492123652730072</v>
       </c>
       <c r="AG57" s="47">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>0.34506004985270788</v>
       </c>
       <c r="AH57" s="47">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>0.34859121525471964</v>
       </c>
       <c r="AI57" s="47">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>0.27637142696059086</v>
       </c>
       <c r="AJ57" s="47">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>0.27709102584684542</v>
       </c>
       <c r="AK57" s="47">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>0.3654401490451793</v>
       </c>
       <c r="AL57" s="47">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>0.39970075879021055</v>
       </c>
       <c r="AM57" s="47">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>0.36288257995491191</v>
       </c>
       <c r="AN57" s="47">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>0.35746466279189737</v>
       </c>
       <c r="AO57" s="47">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>0.31692519820751464</v>
       </c>
       <c r="AP57" s="47">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>0.30545573342045085</v>
       </c>
       <c r="AQ57" s="47">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>0.26748602551239786</v>
       </c>
       <c r="AR57" s="47">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>0.23201026993269031</v>
       </c>
       <c r="AS57" s="47">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>0.15858410911452694</v>
       </c>
       <c r="AT57" s="47">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>0.1446603450956008</v>
       </c>
       <c r="AU57" s="47">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>0.19930179787048349</v>
       </c>
       <c r="AV57" s="47">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>0.24338260570642833</v>
       </c>
       <c r="AW57" s="47">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>0.33921982076963625</v>
       </c>
       <c r="AX57" s="47">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>0.34947147985640209</v>
       </c>
       <c r="AY57" s="47">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>0.33929502125908656</v>
       </c>
       <c r="AZ57" s="47">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>0.34462900872770086</v>
       </c>
       <c r="BA57" s="47">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>0.38650865998176848</v>
       </c>
       <c r="BB57" s="47">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>0.43066176166659775</v>
       </c>
       <c r="BC57" s="47">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>0.39334499220116276</v>
       </c>
       <c r="BD57" s="47">
-        <f t="shared" ref="BD57:BE57" si="106">BD48/BD37</f>
+        <f t="shared" ref="BD57:BE57" si="108">BD48/BD37</f>
         <v>0.38591211381429413</v>
       </c>
       <c r="BE57" s="47">
-        <f t="shared" si="106"/>
+        <f t="shared" si="108"/>
         <v>5.2866788962179459E-2</v>
       </c>
       <c r="BO57" s="47">
-        <f t="shared" ref="BO57:BV57" si="107">BO48/BO37</f>
+        <f t="shared" ref="BO57:BV57" si="109">BO48/BO37</f>
         <v>1.0414619768127334E-2</v>
       </c>
       <c r="BP57" s="47">
-        <f t="shared" si="107"/>
+        <f t="shared" si="109"/>
         <v>0.19054878048780488</v>
       </c>
       <c r="BQ57" s="47">
-        <f t="shared" si="107"/>
+        <f t="shared" si="109"/>
         <v>0.2358414888496711</v>
       </c>
       <c r="BR57" s="47">
-        <f t="shared" si="107"/>
+        <f t="shared" si="109"/>
         <v>0.20571173583221777</v>
       </c>
       <c r="BS57" s="47">
-        <f t="shared" si="107"/>
+        <f t="shared" si="109"/>
         <v>0.36967219046240685</v>
       </c>
       <c r="BT57" s="47">
-        <f t="shared" si="107"/>
+        <f t="shared" si="109"/>
         <v>0.39195139350109465</v>
       </c>
       <c r="BU57" s="47">
-        <f t="shared" si="107"/>
+        <f t="shared" si="109"/>
         <v>0.39600272216053584</v>
       </c>
       <c r="BV57" s="47">
-        <f t="shared" si="107"/>
+        <f t="shared" si="109"/>
         <v>0.26146795479298979</v>
       </c>
       <c r="BW57" s="47">
-        <f t="shared" ref="BW57:CA57" si="108">BW48/BW37</f>
+        <f t="shared" ref="BW57:CA57" si="110">BW48/BW37</f>
         <v>0.3390449601582039</v>
       </c>
       <c r="BX57" s="47">
-        <f t="shared" si="108"/>
+        <f t="shared" si="110"/>
         <v>0.33384494059985248</v>
       </c>
       <c r="BY57" s="47">
-        <f t="shared" si="108"/>
+        <f t="shared" si="110"/>
         <v>0.19895548371051977</v>
       </c>
       <c r="BZ57" s="47">
-        <f t="shared" si="108"/>
+        <f t="shared" si="110"/>
         <v>0.28982520644616094</v>
       </c>
       <c r="CA57" s="47">
-        <f t="shared" si="108"/>
+        <f t="shared" si="110"/>
         <v>0.37908584142345642</v>
       </c>
       <c r="CB57" s="57">
         <f>CB48/CB37</f>
-        <v>0.32843806367061162</v>
+        <v>0.28604979099719147</v>
       </c>
       <c r="CC57" s="57">
-        <f t="shared" ref="CC57:CK57" si="109">CC48/CC37</f>
-        <v>0.3230902742507763</v>
+        <f t="shared" ref="CC57:CK57" si="111">CC48/CC37</f>
+        <v>0.29939027425077636</v>
       </c>
       <c r="CD57" s="57">
-        <f t="shared" si="109"/>
+        <f t="shared" si="111"/>
         <v>0.32235630680562749</v>
       </c>
       <c r="CE57" s="57">
-        <f t="shared" si="109"/>
+        <f t="shared" si="111"/>
         <v>0.34873914150322249</v>
       </c>
       <c r="CF57" s="57">
-        <f t="shared" si="109"/>
+        <f t="shared" si="111"/>
         <v>0.36741975157255652</v>
       </c>
       <c r="CG57" s="57">
-        <f t="shared" si="109"/>
+        <f t="shared" si="111"/>
         <v>0.37843978558297042</v>
       </c>
       <c r="CH57" s="57">
-        <f t="shared" si="109"/>
+        <f t="shared" si="111"/>
         <v>0.38975004886917414</v>
       </c>
       <c r="CI57" s="57">
-        <f t="shared" si="109"/>
+        <f t="shared" si="111"/>
         <v>0.40062341898638776</v>
       </c>
       <c r="CJ57" s="57">
-        <f t="shared" si="109"/>
+        <f t="shared" si="111"/>
         <v>0.41192799297393418</v>
       </c>
       <c r="CK57" s="57">
-        <f t="shared" si="109"/>
+        <f t="shared" si="111"/>
         <v>0.42385721969619561</v>
       </c>
     </row>
@@ -30437,64 +30526,64 @@
         <v>10187</v>
       </c>
       <c r="BW59" s="1">
-        <f t="shared" ref="BW59:BW68" si="110">AL59</f>
+        <f t="shared" ref="BW59:BW68" si="112">AL59</f>
         <v>17576</v>
       </c>
       <c r="BX59" s="1">
-        <f t="shared" ref="BX59:BX68" si="111">AP59</f>
+        <f t="shared" ref="BX59:BX68" si="113">AP59</f>
         <v>16601</v>
       </c>
       <c r="BY59" s="1">
-        <f t="shared" ref="BY59:BY68" si="112">AT59</f>
+        <f t="shared" ref="BY59:BY68" si="114">AT59</f>
         <v>14681</v>
       </c>
       <c r="BZ59" s="1">
-        <f t="shared" ref="BZ59:BZ68" si="113">AX59</f>
+        <f t="shared" ref="BZ59:BZ68" si="115">AX59</f>
         <v>41862</v>
       </c>
       <c r="CA59" s="1">
-        <f t="shared" ref="CA59:CA68" si="114">BB59</f>
+        <f t="shared" ref="CA59:CA68" si="116">BB59</f>
         <v>43889</v>
       </c>
       <c r="CB59" s="56">
         <f>CA59+CB48</f>
-        <v>109695.5532945</v>
+        <v>101202.54827075002</v>
       </c>
       <c r="CC59" s="56">
-        <f t="shared" ref="CC59:CK59" si="115">CB59+CC48</f>
-        <v>186256.81363181249</v>
+        <f t="shared" ref="CC59:CK59" si="117">CB59+CC48</f>
+        <v>172147.72538116251</v>
       </c>
       <c r="CD59" s="56">
-        <f t="shared" si="115"/>
-        <v>274121.26136388956</v>
+        <f t="shared" si="117"/>
+        <v>260012.17311323958</v>
       </c>
       <c r="CE59" s="56">
-        <f t="shared" si="115"/>
-        <v>381573.68299036077</v>
+        <f t="shared" si="117"/>
+        <v>367464.5947397108</v>
       </c>
       <c r="CF59" s="56">
-        <f t="shared" si="115"/>
-        <v>508995.07085865916</v>
+        <f t="shared" si="117"/>
+        <v>494885.98260800919</v>
       </c>
       <c r="CG59" s="56">
-        <f t="shared" si="115"/>
-        <v>656065.49994915875</v>
+        <f t="shared" si="117"/>
+        <v>641956.41169850877</v>
       </c>
       <c r="CH59" s="56">
-        <f t="shared" si="115"/>
-        <v>825044.05307133228</v>
+        <f t="shared" si="117"/>
+        <v>810934.9648206823</v>
       </c>
       <c r="CI59" s="56">
-        <f t="shared" si="115"/>
-        <v>1017952.2357981142</v>
+        <f t="shared" si="117"/>
+        <v>1003843.1475474642</v>
       </c>
       <c r="CJ59" s="56">
-        <f t="shared" si="115"/>
-        <v>1237253.3645399772</v>
+        <f t="shared" si="117"/>
+        <v>1223144.2762893273</v>
       </c>
       <c r="CK59" s="56">
-        <f t="shared" si="115"/>
-        <v>1484506.591268511</v>
+        <f t="shared" si="117"/>
+        <v>1470397.5030178609</v>
       </c>
     </row>
     <row r="60" spans="2:89">
@@ -30562,23 +30651,23 @@
         <v>34261</v>
       </c>
       <c r="BW60" s="1">
-        <f t="shared" si="110"/>
+        <f t="shared" si="112"/>
         <v>44378</v>
       </c>
       <c r="BX60" s="1">
-        <f t="shared" si="111"/>
+        <f t="shared" si="113"/>
         <v>31397</v>
       </c>
       <c r="BY60" s="1">
-        <f t="shared" si="112"/>
+        <f t="shared" si="114"/>
         <v>26057</v>
       </c>
       <c r="BZ60" s="1">
-        <f t="shared" si="113"/>
+        <f t="shared" si="115"/>
         <v>23541</v>
       </c>
       <c r="CA60" s="1">
-        <f t="shared" si="114"/>
+        <f t="shared" si="116"/>
         <v>33926</v>
       </c>
     </row>
@@ -30647,23 +30736,23 @@
         <v>17297</v>
       </c>
       <c r="BW61" s="1">
-        <f t="shared" si="110"/>
+        <f t="shared" si="112"/>
         <v>11335</v>
       </c>
       <c r="BX61" s="1">
-        <f t="shared" si="111"/>
+        <f t="shared" si="113"/>
         <v>14039</v>
       </c>
       <c r="BY61" s="1">
-        <f t="shared" si="112"/>
+        <f t="shared" si="114"/>
         <v>13466</v>
       </c>
       <c r="BZ61" s="1">
-        <f t="shared" si="113"/>
+        <f t="shared" si="115"/>
         <v>16169</v>
       </c>
       <c r="CA61" s="1">
-        <f t="shared" si="114"/>
+        <f t="shared" si="116"/>
         <v>16994</v>
       </c>
       <c r="CC61" s="59" t="s">
@@ -30747,23 +30836,23 @@
         <v>11373</v>
       </c>
       <c r="BW62" s="1">
-        <f t="shared" si="110"/>
+        <f t="shared" si="112"/>
         <v>2381</v>
       </c>
       <c r="BX62" s="1">
-        <f t="shared" si="111"/>
+        <f t="shared" si="113"/>
         <v>4629</v>
       </c>
       <c r="BY62" s="1">
-        <f t="shared" si="112"/>
+        <f t="shared" si="114"/>
         <v>5345</v>
       </c>
       <c r="BZ62" s="1">
-        <f t="shared" si="113"/>
+        <f t="shared" si="115"/>
         <v>3793</v>
       </c>
       <c r="CA62" s="1">
-        <f t="shared" si="114"/>
+        <f t="shared" si="116"/>
         <v>5236</v>
       </c>
       <c r="CC62" s="35">
@@ -30850,28 +30939,28 @@
         <v>25074</v>
       </c>
       <c r="BW63" s="1">
-        <f t="shared" si="110"/>
+        <f t="shared" si="112"/>
         <v>6234</v>
       </c>
       <c r="BX63" s="1">
-        <f t="shared" si="111"/>
+        <f t="shared" si="113"/>
         <v>6775</v>
       </c>
       <c r="BY63" s="1">
-        <f t="shared" si="112"/>
+        <f t="shared" si="114"/>
         <v>6201</v>
       </c>
       <c r="BZ63" s="1">
-        <f t="shared" si="113"/>
+        <f t="shared" si="115"/>
         <v>6141</v>
       </c>
       <c r="CA63" s="1">
-        <f t="shared" si="114"/>
+        <f t="shared" si="116"/>
         <v>6070</v>
       </c>
       <c r="CC63" s="56">
         <f>CB44*(1-CB56)</f>
-        <v>64501.581919500008</v>
+        <v>56148.985208250022</v>
       </c>
       <c r="CE63" s="35">
         <f>SUM(BZ59:BZ61)-SUM(BZ71)+BZ64+BZ67+BZ65</f>
@@ -30957,28 +31046,28 @@
         <v>160270</v>
       </c>
       <c r="BW64" s="1">
-        <f t="shared" si="110"/>
+        <f t="shared" si="112"/>
         <v>45633</v>
       </c>
       <c r="BX64" s="1">
-        <f t="shared" si="111"/>
+        <f t="shared" si="113"/>
         <v>57809</v>
       </c>
       <c r="BY64" s="1">
-        <f t="shared" si="112"/>
+        <f t="shared" si="114"/>
         <v>79518</v>
       </c>
       <c r="BZ64" s="1">
-        <f t="shared" si="113"/>
+        <f t="shared" si="115"/>
         <v>96587</v>
       </c>
       <c r="CA64" s="1">
-        <f t="shared" si="114"/>
+        <f t="shared" si="116"/>
         <v>121346</v>
       </c>
       <c r="CC64" s="57">
         <f>CC63/CH63</f>
-        <v>0.28584664778573998</v>
+        <v>0.24883109407115422</v>
       </c>
       <c r="CJ64" s="61" t="s">
         <v>1523</v>
@@ -31053,23 +31142,23 @@
         <v>17372</v>
       </c>
       <c r="BW65" s="1">
-        <f t="shared" si="110"/>
+        <f t="shared" si="112"/>
         <v>9348</v>
       </c>
       <c r="BX65" s="1">
-        <f t="shared" si="111"/>
+        <f t="shared" si="113"/>
         <v>12155</v>
       </c>
       <c r="BY65" s="1">
-        <f t="shared" si="112"/>
+        <f t="shared" si="114"/>
         <v>12673</v>
       </c>
       <c r="BZ65" s="1">
-        <f t="shared" si="113"/>
+        <f t="shared" si="115"/>
         <v>13294</v>
       </c>
       <c r="CA65" s="1">
-        <f t="shared" si="114"/>
+        <f t="shared" si="116"/>
         <v>14922</v>
       </c>
       <c r="CJ65" s="61" t="s">
@@ -31144,23 +31233,23 @@
         <v>0</v>
       </c>
       <c r="BW66" s="1">
-        <f t="shared" si="110"/>
+        <f t="shared" si="112"/>
         <v>623</v>
       </c>
       <c r="BX66" s="1">
-        <f t="shared" si="111"/>
+        <f t="shared" si="113"/>
         <v>634</v>
       </c>
       <c r="BY66" s="1">
-        <f t="shared" si="112"/>
+        <f t="shared" si="114"/>
         <v>897</v>
       </c>
       <c r="BZ66" s="1">
-        <f t="shared" si="113"/>
+        <f t="shared" si="115"/>
         <v>0</v>
       </c>
       <c r="CA66" s="1">
-        <f t="shared" si="114"/>
+        <f t="shared" si="116"/>
         <v>0</v>
       </c>
       <c r="CJ66" s="61" t="s">
@@ -31236,23 +31325,23 @@
         <v>21158</v>
       </c>
       <c r="BW67" s="1">
-        <f t="shared" si="110"/>
+        <f t="shared" si="112"/>
         <v>19050</v>
       </c>
       <c r="BX67" s="1">
-        <f t="shared" si="111"/>
+        <f t="shared" si="113"/>
         <v>19197</v>
       </c>
       <c r="BY67" s="1">
-        <f t="shared" si="112"/>
+        <f t="shared" si="114"/>
         <v>20306</v>
       </c>
       <c r="BZ67" s="1">
-        <f t="shared" si="113"/>
+        <f t="shared" si="115"/>
         <v>20654</v>
       </c>
       <c r="CA67" s="1">
-        <f t="shared" si="114"/>
+        <f t="shared" si="116"/>
         <v>20654</v>
       </c>
       <c r="CJ67" s="61"/>
@@ -31322,23 +31411,23 @@
         <v>6852</v>
       </c>
       <c r="BW68" s="1">
-        <f t="shared" si="110"/>
+        <f t="shared" si="112"/>
         <v>2758</v>
       </c>
       <c r="BX68" s="1">
-        <f t="shared" si="111"/>
+        <f t="shared" si="113"/>
         <v>2751</v>
       </c>
       <c r="BY68" s="1">
-        <f t="shared" si="112"/>
+        <f t="shared" si="114"/>
         <v>6583</v>
       </c>
       <c r="BZ68" s="1">
-        <f t="shared" si="113"/>
+        <f t="shared" si="115"/>
         <v>7582</v>
       </c>
       <c r="CA68" s="1">
-        <f t="shared" si="114"/>
+        <f t="shared" si="116"/>
         <v>13017</v>
       </c>
       <c r="CJ68" s="61" t="s">
@@ -31346,7 +31435,7 @@
       </c>
       <c r="CK68" s="56">
         <f>NPV(CK66,CB48:EJ48)</f>
-        <v>2187277.4285540604</v>
+        <v>2174851.55355309</v>
       </c>
     </row>
     <row r="69" spans="2:141" s="2" customFormat="1" ht="15" customHeight="1">
@@ -31354,71 +31443,71 @@
         <v>249</v>
       </c>
       <c r="AL69" s="2">
-        <f t="shared" ref="AL69:AX69" si="116">SUM(AL59:AL68)</f>
+        <f t="shared" ref="AL69:AX69" si="118">SUM(AL59:AL68)</f>
         <v>159316</v>
       </c>
       <c r="AM69" s="2">
-        <f t="shared" si="116"/>
+        <f t="shared" si="118"/>
         <v>163523</v>
       </c>
       <c r="AN69" s="2">
-        <f t="shared" si="116"/>
+        <f t="shared" si="118"/>
         <v>170609</v>
       </c>
       <c r="AO69" s="2">
-        <f t="shared" si="116"/>
+        <f t="shared" si="118"/>
         <v>169585</v>
       </c>
       <c r="AP69" s="2">
-        <f t="shared" si="116"/>
+        <f t="shared" si="118"/>
         <v>165987</v>
       </c>
       <c r="AQ69" s="2">
-        <f t="shared" si="116"/>
+        <f t="shared" si="118"/>
         <v>164218</v>
       </c>
       <c r="AR69" s="2">
-        <f t="shared" si="116"/>
+        <f t="shared" si="118"/>
         <v>169779</v>
       </c>
       <c r="AS69" s="2">
-        <f t="shared" si="116"/>
+        <f t="shared" si="118"/>
         <v>178894</v>
       </c>
       <c r="AT69" s="2">
-        <f t="shared" si="116"/>
+        <f t="shared" si="118"/>
         <v>185727</v>
       </c>
       <c r="AU69" s="2">
-        <f t="shared" si="116"/>
+        <f t="shared" si="118"/>
         <v>184491</v>
       </c>
       <c r="AV69" s="2">
-        <f t="shared" si="116"/>
+        <f t="shared" si="118"/>
         <v>206688</v>
       </c>
       <c r="AW69" s="2">
-        <f t="shared" si="116"/>
+        <f t="shared" si="118"/>
         <v>216274</v>
       </c>
       <c r="AX69" s="2">
-        <f t="shared" si="116"/>
+        <f t="shared" si="118"/>
         <v>229623</v>
       </c>
       <c r="AY69" s="2">
-        <f t="shared" ref="AY69:BB69" si="117">SUM(AY59:AY68)</f>
+        <f t="shared" ref="AY69:BB69" si="119">SUM(AY59:AY68)</f>
         <v>222844</v>
       </c>
       <c r="AZ69" s="2">
-        <f t="shared" si="117"/>
+        <f t="shared" si="119"/>
         <v>230238</v>
       </c>
       <c r="BA69" s="2">
-        <f t="shared" si="117"/>
+        <f t="shared" si="119"/>
         <v>256408</v>
       </c>
       <c r="BB69" s="2">
-        <f t="shared" si="117"/>
+        <f t="shared" si="119"/>
         <v>276054</v>
       </c>
       <c r="BC69" s="2">
@@ -31533,7 +31622,7 @@
       </c>
       <c r="CK70" s="55">
         <f>CK68/CK69</f>
-        <v>869.00175945731439</v>
+        <v>864.06497956022645</v>
       </c>
     </row>
     <row r="71" spans="2:141" ht="15" customHeight="1">
@@ -31601,23 +31690,23 @@
         <v>7798</v>
       </c>
       <c r="BW71" s="1">
-        <f t="shared" ref="BW71:BW82" si="118">AL71</f>
+        <f t="shared" ref="BW71:BW82" si="120">AL71</f>
         <v>1331</v>
       </c>
       <c r="BX71" s="1">
-        <f t="shared" ref="BX71:BX82" si="119">AP71</f>
+        <f t="shared" ref="BX71:BX82" si="121">AP71</f>
         <v>4083</v>
       </c>
       <c r="BY71" s="1">
-        <f t="shared" ref="BY71:BY82" si="120">AT71</f>
+        <f t="shared" ref="BY71:BY82" si="122">AT71</f>
         <v>4990</v>
       </c>
       <c r="BZ71" s="1">
-        <f t="shared" ref="BZ71:BZ82" si="121">AX71</f>
+        <f t="shared" ref="BZ71:BZ82" si="123">AX71</f>
         <v>4849</v>
       </c>
       <c r="CA71" s="1">
-        <f t="shared" ref="CA71:CA82" si="122">BB71</f>
+        <f t="shared" ref="CA71:CA82" si="124">BB71</f>
         <v>7687</v>
       </c>
       <c r="CJ71" s="61" t="s">
@@ -31693,23 +31782,23 @@
         <v>0</v>
       </c>
       <c r="BW72" s="1">
-        <f t="shared" si="118"/>
+        <f t="shared" si="120"/>
         <v>1093</v>
       </c>
       <c r="BX72" s="1">
-        <f t="shared" si="119"/>
+        <f t="shared" si="121"/>
         <v>1052</v>
       </c>
       <c r="BY72" s="1">
-        <f t="shared" si="120"/>
+        <f t="shared" si="122"/>
         <v>0</v>
       </c>
       <c r="BZ72" s="1">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>0</v>
       </c>
       <c r="CA72" s="1">
-        <f t="shared" si="122"/>
+        <f t="shared" si="124"/>
         <v>0</v>
       </c>
       <c r="CC72" s="34"/>
@@ -31724,7 +31813,7 @@
       </c>
       <c r="CK72" s="63">
         <f>CK70/CK71-1</f>
-        <v>0.30224597182316226</v>
+        <v>0.29484794107720025</v>
       </c>
       <c r="CL72" s="64" t="str">
         <f>IF(CK72&gt;0,"Upside","Downside")</f>
@@ -31796,23 +31885,23 @@
         <v>2113</v>
       </c>
       <c r="BW73" s="1">
-        <f t="shared" si="118"/>
+        <f t="shared" si="120"/>
         <v>1023</v>
       </c>
       <c r="BX73" s="1">
-        <f t="shared" si="119"/>
+        <f t="shared" si="121"/>
         <v>1127</v>
       </c>
       <c r="BY73" s="1">
-        <f t="shared" si="120"/>
+        <f t="shared" si="122"/>
         <v>1117</v>
       </c>
       <c r="BZ73" s="1">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>1623</v>
       </c>
       <c r="CA73" s="1">
-        <f t="shared" si="122"/>
+        <f t="shared" si="124"/>
         <v>1942</v>
       </c>
       <c r="CJ73" s="69" t="str" cm="1">
@@ -31886,23 +31975,23 @@
         <v>27047</v>
       </c>
       <c r="BW74" s="1">
-        <f t="shared" si="118"/>
+        <f t="shared" si="120"/>
         <v>11152</v>
       </c>
       <c r="BX74" s="1">
-        <f t="shared" si="119"/>
+        <f t="shared" si="121"/>
         <v>14312</v>
       </c>
       <c r="BY74" s="1">
-        <f t="shared" si="120"/>
+        <f t="shared" si="122"/>
         <v>1367</v>
       </c>
       <c r="BZ74" s="1">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>25488</v>
       </c>
       <c r="CA74" s="1">
-        <f t="shared" si="122"/>
+        <f t="shared" si="124"/>
         <v>23967</v>
       </c>
     </row>
@@ -31971,23 +32060,23 @@
         <v>0</v>
       </c>
       <c r="BW75" s="1">
-        <f t="shared" si="118"/>
+        <f t="shared" si="120"/>
         <v>382</v>
       </c>
       <c r="BX75" s="1">
-        <f t="shared" si="119"/>
+        <f t="shared" si="121"/>
         <v>561</v>
       </c>
       <c r="BY75" s="1">
-        <f t="shared" si="120"/>
+        <f t="shared" si="122"/>
         <v>0</v>
       </c>
       <c r="BZ75" s="1">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>0</v>
       </c>
       <c r="CA75" s="1">
-        <f t="shared" si="122"/>
+        <f t="shared" si="124"/>
         <v>0</v>
       </c>
     </row>
@@ -32056,23 +32145,23 @@
         <v>20113</v>
       </c>
       <c r="BW76" s="1">
-        <f t="shared" si="118"/>
+        <f t="shared" si="120"/>
         <v>9631</v>
       </c>
       <c r="BX76" s="1">
-        <f t="shared" si="119"/>
+        <f t="shared" si="121"/>
         <v>12746</v>
       </c>
       <c r="BY76" s="1">
-        <f t="shared" si="120"/>
+        <f t="shared" si="122"/>
         <v>19552</v>
       </c>
       <c r="BZ76" s="1">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>17226</v>
       </c>
       <c r="CA76" s="1">
-        <f t="shared" si="122"/>
+        <f t="shared" si="124"/>
         <v>18292</v>
       </c>
     </row>
@@ -32141,23 +32230,23 @@
         <v>28834</v>
       </c>
       <c r="BW77" s="1">
-        <f t="shared" si="118"/>
+        <f t="shared" si="120"/>
         <v>0</v>
       </c>
       <c r="BX77" s="1">
-        <f t="shared" si="119"/>
+        <f t="shared" si="121"/>
         <v>0</v>
       </c>
       <c r="BY77" s="1">
-        <f t="shared" si="120"/>
+        <f t="shared" si="122"/>
         <v>15301</v>
       </c>
       <c r="BZ77" s="1">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>18385</v>
       </c>
       <c r="CA77" s="1">
-        <f t="shared" si="122"/>
+        <f t="shared" si="124"/>
         <v>28826</v>
       </c>
     </row>
@@ -32226,23 +32315,23 @@
         <v>11738</v>
       </c>
       <c r="BW78" s="1">
-        <f t="shared" si="118"/>
+        <f t="shared" si="120"/>
         <v>0</v>
       </c>
       <c r="BX78" s="1">
-        <f t="shared" si="119"/>
+        <f t="shared" si="121"/>
         <v>0</v>
       </c>
       <c r="BY78" s="1">
-        <f t="shared" si="120"/>
+        <f t="shared" si="122"/>
         <v>9923</v>
       </c>
       <c r="BZ78" s="1">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>7514</v>
       </c>
       <c r="CA78" s="1">
-        <f t="shared" si="122"/>
+        <f t="shared" si="124"/>
         <v>9987</v>
       </c>
     </row>
@@ -32311,23 +32400,23 @@
         <v>12135</v>
       </c>
       <c r="BW79" s="1">
-        <f t="shared" si="118"/>
+        <f t="shared" si="120"/>
         <v>6414</v>
       </c>
       <c r="BX79" s="1">
-        <f t="shared" si="119"/>
+        <f t="shared" si="121"/>
         <v>7227</v>
       </c>
       <c r="BY79" s="1">
-        <f t="shared" si="120"/>
+        <f t="shared" si="122"/>
         <v>7764</v>
       </c>
       <c r="BZ79" s="1">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>1370</v>
       </c>
       <c r="CA79" s="1">
-        <f t="shared" si="122"/>
+        <f t="shared" si="124"/>
         <v>2716</v>
       </c>
     </row>
@@ -32336,15 +32425,15 @@
         <v>246</v>
       </c>
       <c r="AL80" s="2">
-        <f t="shared" ref="AL80:BB80" si="123">SUM(AL71:AL79)</f>
+        <f t="shared" ref="AL80:BB80" si="125">SUM(AL71:AL79)</f>
         <v>31026</v>
       </c>
       <c r="AM80" s="2">
-        <f t="shared" si="123"/>
+        <f t="shared" si="125"/>
         <v>29866</v>
       </c>
       <c r="AN80" s="2">
-        <f t="shared" si="123"/>
+        <f t="shared" si="125"/>
         <v>32382</v>
       </c>
       <c r="AO80" s="2">
@@ -32352,7 +32441,7 @@
         <v>36225</v>
       </c>
       <c r="AP80" s="2">
-        <f t="shared" si="123"/>
+        <f t="shared" si="125"/>
         <v>41108</v>
       </c>
       <c r="AQ80" s="2">
@@ -32360,7 +32449,7 @@
         <v>40990</v>
       </c>
       <c r="AR80" s="2">
-        <f t="shared" si="123"/>
+        <f t="shared" si="125"/>
         <v>44012</v>
       </c>
       <c r="AS80" s="2">
@@ -32368,39 +32457,39 @@
         <v>54800</v>
       </c>
       <c r="AT80" s="2">
-        <f t="shared" si="123"/>
+        <f t="shared" si="125"/>
         <v>60014</v>
       </c>
       <c r="AU80" s="2">
-        <f t="shared" si="123"/>
+        <f t="shared" si="125"/>
         <v>59696</v>
       </c>
       <c r="AV80" s="2">
-        <f t="shared" si="123"/>
+        <f t="shared" si="125"/>
         <v>72655</v>
       </c>
       <c r="AW80" s="2">
-        <f t="shared" si="123"/>
+        <f t="shared" si="125"/>
         <v>73401</v>
       </c>
       <c r="AX80" s="2">
-        <f t="shared" si="123"/>
+        <f t="shared" si="125"/>
         <v>76455</v>
       </c>
       <c r="AY80" s="2">
-        <f t="shared" si="123"/>
+        <f t="shared" si="125"/>
         <v>73315</v>
       </c>
       <c r="AZ80" s="2">
-        <f t="shared" si="123"/>
+        <f t="shared" si="125"/>
         <v>73475</v>
       </c>
       <c r="BA80" s="2">
-        <f t="shared" si="123"/>
+        <f t="shared" si="125"/>
         <v>91879</v>
       </c>
       <c r="BB80" s="2">
-        <f t="shared" si="123"/>
+        <f t="shared" si="125"/>
         <v>93417</v>
       </c>
       <c r="BC80" s="2">
@@ -32421,23 +32510,23 @@
       <c r="BI80" s="34"/>
       <c r="BJ80" s="34"/>
       <c r="BW80" s="2">
-        <f t="shared" si="118"/>
+        <f t="shared" si="120"/>
         <v>31026</v>
       </c>
       <c r="BX80" s="2">
-        <f t="shared" si="119"/>
+        <f t="shared" si="121"/>
         <v>41108</v>
       </c>
       <c r="BY80" s="2">
-        <f t="shared" si="120"/>
+        <f t="shared" si="122"/>
         <v>60014</v>
       </c>
       <c r="BZ80" s="2">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>76455</v>
       </c>
       <c r="CA80" s="2">
-        <f t="shared" si="122"/>
+        <f t="shared" si="124"/>
         <v>93417</v>
       </c>
       <c r="CB80" s="34"/>
@@ -32568,23 +32657,23 @@
         <v>194066</v>
       </c>
       <c r="BW81" s="1">
-        <f t="shared" si="118"/>
+        <f t="shared" si="120"/>
         <v>128290</v>
       </c>
       <c r="BX81" s="1">
-        <f t="shared" si="119"/>
+        <f t="shared" si="121"/>
         <v>124879</v>
       </c>
       <c r="BY81" s="1">
-        <f t="shared" si="120"/>
+        <f t="shared" si="122"/>
         <v>125713</v>
       </c>
       <c r="BZ81" s="1">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>153168</v>
       </c>
       <c r="CA81" s="1">
-        <f t="shared" si="122"/>
+        <f t="shared" si="124"/>
         <v>182637</v>
       </c>
     </row>
@@ -32593,83 +32682,83 @@
         <v>248</v>
       </c>
       <c r="AL82" s="2">
-        <f t="shared" ref="AL82" si="124">AL80+AL81</f>
+        <f t="shared" ref="AL82" si="126">AL80+AL81</f>
         <v>159316</v>
       </c>
       <c r="AM82" s="2">
-        <f t="shared" ref="AM82" si="125">AM80+AM81</f>
+        <f t="shared" ref="AM82" si="127">AM80+AM81</f>
         <v>163523</v>
       </c>
       <c r="AN82" s="2">
-        <f t="shared" ref="AN82" si="126">AN80+AN81</f>
+        <f t="shared" ref="AN82" si="128">AN80+AN81</f>
         <v>170609</v>
       </c>
       <c r="AO82" s="2">
-        <f t="shared" ref="AO82" si="127">AO80+AO81</f>
+        <f t="shared" ref="AO82" si="129">AO80+AO81</f>
         <v>169585</v>
       </c>
       <c r="AP82" s="2">
-        <f t="shared" ref="AP82" si="128">AP80+AP81</f>
+        <f t="shared" ref="AP82" si="130">AP80+AP81</f>
         <v>165987</v>
       </c>
       <c r="AQ82" s="2">
-        <f t="shared" ref="AQ82" si="129">AQ80+AQ81</f>
+        <f t="shared" ref="AQ82" si="131">AQ80+AQ81</f>
         <v>164218</v>
       </c>
       <c r="AR82" s="2">
-        <f t="shared" ref="AR82" si="130">AR80+AR81</f>
+        <f t="shared" ref="AR82" si="132">AR80+AR81</f>
         <v>169779</v>
       </c>
       <c r="AS82" s="2">
-        <f t="shared" ref="AS82" si="131">AS80+AS81</f>
+        <f t="shared" ref="AS82" si="133">AS80+AS81</f>
         <v>178894</v>
       </c>
       <c r="AT82" s="2">
-        <f t="shared" ref="AT82" si="132">AT80+AT81</f>
+        <f t="shared" ref="AT82" si="134">AT80+AT81</f>
         <v>185727</v>
       </c>
       <c r="AU82" s="2">
-        <f t="shared" ref="AU82" si="133">AU80+AU81</f>
+        <f t="shared" ref="AU82" si="135">AU80+AU81</f>
         <v>184491</v>
       </c>
       <c r="AV82" s="2">
-        <f t="shared" ref="AV82" si="134">AV80+AV81</f>
+        <f t="shared" ref="AV82" si="136">AV80+AV81</f>
         <v>206688</v>
       </c>
       <c r="AW82" s="2">
-        <f t="shared" ref="AW82" si="135">AW80+AW81</f>
+        <f t="shared" ref="AW82" si="137">AW80+AW81</f>
         <v>216274</v>
       </c>
       <c r="AX82" s="2">
-        <f t="shared" ref="AX82" si="136">AX80+AX81</f>
+        <f t="shared" ref="AX82" si="138">AX80+AX81</f>
         <v>229623</v>
       </c>
       <c r="AY82" s="2">
-        <f t="shared" ref="AY82" si="137">AY80+AY81</f>
+        <f t="shared" ref="AY82" si="139">AY80+AY81</f>
         <v>222844</v>
       </c>
       <c r="AZ82" s="2">
-        <f t="shared" ref="AZ82" si="138">AZ80+AZ81</f>
+        <f t="shared" ref="AZ82" si="140">AZ80+AZ81</f>
         <v>230238</v>
       </c>
       <c r="BA82" s="2">
-        <f t="shared" ref="BA82" si="139">BA80+BA81</f>
+        <f t="shared" ref="BA82" si="141">BA80+BA81</f>
         <v>256408</v>
       </c>
       <c r="BB82" s="2">
-        <f t="shared" ref="BB82" si="140">BB80+BB81</f>
+        <f t="shared" ref="BB82" si="142">BB80+BB81</f>
         <v>276054</v>
       </c>
       <c r="BC82" s="2">
-        <f t="shared" ref="BC82:BD82" si="141">BC80+BC81</f>
+        <f t="shared" ref="BC82:BD82" si="143">BC80+BC81</f>
         <v>280213</v>
       </c>
       <c r="BD82" s="2">
-        <f t="shared" si="141"/>
+        <f t="shared" si="143"/>
         <v>294744</v>
       </c>
       <c r="BE82" s="2">
-        <f t="shared" ref="BE82" si="142">BE80+BE81</f>
+        <f t="shared" ref="BE82" si="144">BE80+BE81</f>
         <v>303844</v>
       </c>
       <c r="BF82" s="34"/>
@@ -32678,23 +32767,23 @@
       <c r="BI82" s="34"/>
       <c r="BJ82" s="34"/>
       <c r="BW82" s="2">
-        <f t="shared" si="118"/>
+        <f t="shared" si="120"/>
         <v>159316</v>
       </c>
       <c r="BX82" s="2">
-        <f t="shared" si="119"/>
+        <f t="shared" si="121"/>
         <v>165987</v>
       </c>
       <c r="BY82" s="2">
-        <f t="shared" si="120"/>
+        <f t="shared" si="122"/>
         <v>185727</v>
       </c>
       <c r="BZ82" s="2">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>229623</v>
       </c>
       <c r="CA82" s="2">
-        <f t="shared" si="122"/>
+        <f t="shared" si="124"/>
         <v>276054</v>
       </c>
       <c r="CB82" s="34"/>
@@ -32768,71 +32857,71 @@
         <v>119</v>
       </c>
       <c r="AL84" s="51">
-        <f t="shared" ref="AL84:BB84" si="143">SUM(AL59:AL62)/SUM(AL71:AL75)</f>
+        <f t="shared" ref="AL84:BB84" si="145">SUM(AL59:AL62)/SUM(AL71:AL75)</f>
         <v>5.0510646819304457</v>
       </c>
       <c r="AM84" s="51">
-        <f t="shared" si="143"/>
+        <f t="shared" si="145"/>
         <v>6.0802075961311628</v>
       </c>
       <c r="AN84" s="51">
-        <f t="shared" si="143"/>
+        <f t="shared" si="145"/>
         <v>5.4253731343283578</v>
       </c>
       <c r="AO84" s="51">
-        <f t="shared" si="143"/>
+        <f t="shared" si="145"/>
         <v>4.2342802604985401</v>
       </c>
       <c r="AP84" s="51">
-        <f t="shared" si="143"/>
+        <f t="shared" si="145"/>
         <v>3.1542938254080908</v>
       </c>
       <c r="AQ84" s="51">
-        <f t="shared" si="143"/>
+        <f t="shared" si="145"/>
         <v>2.8106326472541023</v>
       </c>
       <c r="AR84" s="51">
-        <f t="shared" si="143"/>
+        <f t="shared" si="145"/>
         <v>2.5200072016923976</v>
       </c>
       <c r="AS84" s="51">
-        <f t="shared" si="143"/>
+        <f t="shared" si="145"/>
         <v>2.5704147749812667</v>
       </c>
       <c r="AT84" s="51">
-        <f t="shared" si="143"/>
+        <f t="shared" si="145"/>
         <v>7.9674872892694673</v>
       </c>
       <c r="AU84" s="51">
-        <f t="shared" si="143"/>
+        <f t="shared" si="145"/>
         <v>8.6949966865473822</v>
       </c>
       <c r="AV84" s="51">
-        <f t="shared" si="143"/>
+        <f t="shared" si="145"/>
         <v>13.221820946588101</v>
       </c>
       <c r="AW84" s="51">
-        <f t="shared" si="143"/>
+        <f t="shared" si="145"/>
         <v>11.871857013026355</v>
       </c>
       <c r="AX84" s="51">
-        <f t="shared" si="143"/>
+        <f t="shared" si="145"/>
         <v>2.6709949937421777</v>
       </c>
       <c r="AY84" s="51">
-        <f t="shared" si="143"/>
+        <f t="shared" si="145"/>
         <v>2.6806875200170812</v>
       </c>
       <c r="AZ84" s="51">
-        <f t="shared" si="143"/>
+        <f t="shared" si="145"/>
         <v>2.8303584654125316</v>
       </c>
       <c r="BA84" s="51">
-        <f t="shared" si="143"/>
+        <f t="shared" si="145"/>
         <v>2.7322832283228324</v>
       </c>
       <c r="BB84" s="51">
-        <f t="shared" si="143"/>
+        <f t="shared" si="145"/>
         <v>2.9778842719371355</v>
       </c>
       <c r="BC84" s="51">
@@ -32848,23 +32937,23 @@
         <v>1.9784079225066291</v>
       </c>
       <c r="BW84" s="51">
-        <f t="shared" ref="BW84:CA84" si="144">SUM(BW59:BW62)/SUM(BW71:BW75)</f>
+        <f t="shared" ref="BW84:CA84" si="146">SUM(BW59:BW62)/SUM(BW71:BW75)</f>
         <v>5.0510646819304457</v>
       </c>
       <c r="BX84" s="51">
-        <f t="shared" si="144"/>
+        <f t="shared" si="146"/>
         <v>3.1542938254080908</v>
       </c>
       <c r="BY84" s="51">
-        <f t="shared" si="144"/>
+        <f t="shared" si="146"/>
         <v>7.9674872892694673</v>
       </c>
       <c r="BZ84" s="51">
-        <f t="shared" si="144"/>
+        <f t="shared" si="146"/>
         <v>2.6709949937421777</v>
       </c>
       <c r="CA84" s="51">
-        <f t="shared" si="144"/>
+        <f t="shared" si="146"/>
         <v>2.9778842719371355</v>
       </c>
     </row>
@@ -32873,71 +32962,71 @@
         <v>120</v>
       </c>
       <c r="AL85" s="51">
-        <f t="shared" ref="AL85:BB85" si="145">SUM(AL59:AL60)/SUM(AL71:AL75)</f>
+        <f t="shared" ref="AL85:BB85" si="147">SUM(AL59:AL60)/SUM(AL71:AL75)</f>
         <v>4.1355049729657569</v>
       </c>
       <c r="AM85" s="51">
-        <f t="shared" si="145"/>
+        <f t="shared" si="147"/>
         <v>5.0498545254383895</v>
       </c>
       <c r="AN85" s="51">
-        <f t="shared" si="145"/>
+        <f t="shared" si="147"/>
         <v>4.3081887858007262</v>
       </c>
       <c r="AO85" s="51">
-        <f t="shared" si="145"/>
+        <f t="shared" si="147"/>
         <v>3.2604423983831126</v>
       </c>
       <c r="AP85" s="51">
-        <f t="shared" si="145"/>
+        <f t="shared" si="147"/>
         <v>2.2710196356754198</v>
       </c>
       <c r="AQ85" s="51">
-        <f t="shared" si="145"/>
+        <f t="shared" si="147"/>
         <v>2.0814758607606945</v>
       </c>
       <c r="AR85" s="51">
-        <f t="shared" si="145"/>
+        <f t="shared" si="147"/>
         <v>1.8224332718188774</v>
       </c>
       <c r="AS85" s="51">
-        <f t="shared" si="145"/>
+        <f t="shared" si="147"/>
         <v>1.8414069731564331</v>
       </c>
       <c r="AT85" s="51">
-        <f t="shared" si="145"/>
+        <f t="shared" si="147"/>
         <v>5.4506288466684509</v>
       </c>
       <c r="AU85" s="51">
-        <f t="shared" si="145"/>
+        <f t="shared" si="147"/>
         <v>6.2026176275679257</v>
       </c>
       <c r="AV85" s="51">
-        <f t="shared" si="145"/>
+        <f t="shared" si="147"/>
         <v>10.158905151111956</v>
       </c>
       <c r="AW85" s="51">
-        <f t="shared" si="145"/>
+        <f t="shared" si="147"/>
         <v>9.2582550742199334</v>
       </c>
       <c r="AX85" s="51">
-        <f t="shared" si="145"/>
+        <f t="shared" si="147"/>
         <v>2.046401752190238</v>
       </c>
       <c r="AY85" s="51">
-        <f t="shared" si="145"/>
+        <f t="shared" si="147"/>
         <v>2.0682537987971958</v>
       </c>
       <c r="AZ85" s="51">
-        <f t="shared" si="145"/>
+        <f t="shared" si="147"/>
         <v>2.1507924751888607</v>
       </c>
       <c r="BA85" s="51">
-        <f t="shared" si="145"/>
+        <f t="shared" si="147"/>
         <v>2.127212721272127</v>
       </c>
       <c r="BB85" s="51">
-        <f t="shared" si="145"/>
+        <f t="shared" si="147"/>
         <v>2.3161983569472557</v>
       </c>
       <c r="BC85" s="51">
@@ -32953,23 +33042,23 @@
         <v>1.2026624817360247</v>
       </c>
       <c r="BW85" s="51">
-        <f t="shared" ref="BW85:CA85" si="146">SUM(BW59:BW60)/SUM(BW71:BW75)</f>
+        <f t="shared" ref="BW85:CA85" si="148">SUM(BW59:BW60)/SUM(BW71:BW75)</f>
         <v>4.1355049729657569</v>
       </c>
       <c r="BX85" s="51">
-        <f t="shared" si="146"/>
+        <f t="shared" si="148"/>
         <v>2.2710196356754198</v>
       </c>
       <c r="BY85" s="51">
-        <f t="shared" si="146"/>
+        <f t="shared" si="148"/>
         <v>5.4506288466684509</v>
       </c>
       <c r="BZ85" s="51">
-        <f t="shared" si="146"/>
+        <f t="shared" si="148"/>
         <v>2.046401752190238</v>
       </c>
       <c r="CA85" s="51">
-        <f t="shared" si="146"/>
+        <f t="shared" si="148"/>
         <v>2.3161983569472557</v>
       </c>
     </row>
@@ -32978,71 +33067,71 @@
         <v>121</v>
       </c>
       <c r="AL86" s="51">
-        <f t="shared" ref="AL86:BB86" si="147">AL37/AL82</f>
+        <f t="shared" ref="AL86:BB86" si="149">AL37/AL82</f>
         <v>0.1761969921414045</v>
       </c>
       <c r="AM86" s="51">
-        <f t="shared" si="147"/>
+        <f t="shared" si="149"/>
         <v>0.16004476434507683</v>
       </c>
       <c r="AN86" s="51">
-        <f t="shared" si="147"/>
+        <f t="shared" si="149"/>
         <v>0.1704306337883699</v>
       </c>
       <c r="AO86" s="51">
-        <f t="shared" si="147"/>
+        <f t="shared" si="149"/>
         <v>0.17106465784120059</v>
       </c>
       <c r="AP86" s="51">
-        <f t="shared" si="147"/>
+        <f t="shared" si="149"/>
         <v>0.20285323549434595</v>
       </c>
       <c r="AQ86" s="51">
-        <f t="shared" si="147"/>
+        <f t="shared" si="149"/>
         <v>0.16994482943404499</v>
       </c>
       <c r="AR86" s="51">
-        <f t="shared" si="147"/>
+        <f t="shared" si="149"/>
         <v>0.16976186689755507</v>
       </c>
       <c r="AS86" s="51">
-        <f t="shared" si="147"/>
+        <f t="shared" si="149"/>
         <v>0.15491855512202757</v>
       </c>
       <c r="AT86" s="51">
-        <f t="shared" si="147"/>
+        <f t="shared" si="149"/>
         <v>0.17318429738271765</v>
       </c>
       <c r="AU86" s="51">
-        <f t="shared" si="147"/>
+        <f t="shared" si="149"/>
         <v>0.15526502647825638</v>
       </c>
       <c r="AV86" s="51">
-        <f t="shared" si="147"/>
+        <f t="shared" si="149"/>
         <v>0.15481788976621769</v>
       </c>
       <c r="AW86" s="51">
-        <f t="shared" si="147"/>
+        <f t="shared" si="149"/>
         <v>0.1578830557533499</v>
       </c>
       <c r="AX86" s="51">
-        <f t="shared" si="147"/>
+        <f t="shared" si="149"/>
         <v>0.17468633368608547</v>
       </c>
       <c r="AY86" s="51">
-        <f t="shared" si="147"/>
+        <f t="shared" si="149"/>
         <v>0.1635897758072912</v>
       </c>
       <c r="AZ86" s="51">
-        <f t="shared" si="147"/>
+        <f t="shared" si="149"/>
         <v>0.16969831218130804</v>
       </c>
       <c r="BA86" s="51">
-        <f t="shared" si="147"/>
+        <f t="shared" si="149"/>
         <v>0.15829849302673862</v>
       </c>
       <c r="BB86" s="51">
-        <f t="shared" si="147"/>
+        <f t="shared" si="149"/>
         <v>0.17527730081795589</v>
       </c>
       <c r="BC86" s="51">
@@ -33058,23 +33147,23 @@
         <v>0.16864575242558683</v>
       </c>
       <c r="BW86" s="51">
-        <f t="shared" ref="BW86:CA86" si="148">BW37/BW82</f>
+        <f t="shared" ref="BW86:CA86" si="150">BW37/BW82</f>
         <v>0.53958798865148505</v>
       </c>
       <c r="BX86" s="51">
-        <f t="shared" si="148"/>
+        <f t="shared" si="150"/>
         <v>0.71047130196943131</v>
       </c>
       <c r="BY86" s="51">
-        <f t="shared" si="148"/>
+        <f t="shared" si="150"/>
         <v>0.6278516316959839</v>
       </c>
       <c r="BZ86" s="51">
-        <f t="shared" si="148"/>
+        <f t="shared" si="150"/>
         <v>0.58749341311628189</v>
       </c>
       <c r="CA86" s="51">
-        <f t="shared" si="148"/>
+        <f t="shared" si="150"/>
         <v>0.5959015265129286</v>
       </c>
     </row>
@@ -33083,71 +33172,71 @@
         <v>122</v>
       </c>
       <c r="AL87" s="47">
-        <f t="shared" ref="AL87:BB87" si="149">AL48/AL82</f>
+        <f t="shared" ref="AL87:BB87" si="151">AL48/AL82</f>
         <v>7.0426071455472139E-2</v>
       </c>
       <c r="AM87" s="47">
-        <f t="shared" si="149"/>
+        <f t="shared" si="151"/>
         <v>5.8077456993817382E-2</v>
       </c>
       <c r="AN87" s="47">
-        <f t="shared" si="149"/>
+        <f t="shared" si="151"/>
         <v>6.0922929036568998E-2</v>
       </c>
       <c r="AO87" s="47">
-        <f t="shared" si="149"/>
+        <f t="shared" si="151"/>
         <v>5.421470059262317E-2</v>
       </c>
       <c r="AP87" s="47">
-        <f t="shared" si="149"/>
+        <f t="shared" si="151"/>
         <v>6.196268382463687E-2</v>
       </c>
       <c r="AQ87" s="47">
-        <f t="shared" si="149"/>
+        <f t="shared" si="151"/>
         <v>4.5457866981695065E-2</v>
       </c>
       <c r="AR87" s="47">
-        <f t="shared" si="149"/>
+        <f t="shared" si="151"/>
         <v>3.9386496563179191E-2</v>
       </c>
       <c r="AS87" s="47">
-        <f t="shared" si="149"/>
+        <f t="shared" si="151"/>
         <v>2.4567621049336477E-2</v>
       </c>
       <c r="AT87" s="47">
-        <f t="shared" si="149"/>
+        <f t="shared" si="151"/>
         <v>2.5052900224523091E-2</v>
       </c>
       <c r="AU87" s="47">
-        <f t="shared" si="149"/>
+        <f t="shared" si="151"/>
         <v>3.0944598923524726E-2</v>
       </c>
       <c r="AV87" s="47">
-        <f t="shared" si="149"/>
+        <f t="shared" si="151"/>
         <v>3.7679981421272643E-2</v>
       </c>
       <c r="AW87" s="47">
-        <f t="shared" si="149"/>
+        <f t="shared" si="151"/>
         <v>5.3557061875213849E-2</v>
       </c>
       <c r="AX87" s="47">
-        <f t="shared" si="149"/>
+        <f t="shared" si="151"/>
         <v>6.1047891543965546E-2</v>
       </c>
       <c r="AY87" s="47">
-        <f t="shared" si="149"/>
+        <f t="shared" si="151"/>
         <v>5.5505196460304072E-2</v>
       </c>
       <c r="AZ87" s="47">
-        <f t="shared" si="149"/>
+        <f t="shared" si="151"/>
         <v>5.8482961109808114E-2</v>
       </c>
       <c r="BA87" s="47">
-        <f t="shared" si="149"/>
+        <f t="shared" si="151"/>
         <v>6.1183738416898066E-2</v>
       </c>
       <c r="BB87" s="47">
-        <f t="shared" si="149"/>
+        <f t="shared" si="151"/>
         <v>7.5485231150427087E-2</v>
       </c>
       <c r="BC87" s="47">
@@ -33163,23 +33252,23 @@
         <v>8.9157594028514628E-3</v>
       </c>
       <c r="BW87" s="47">
-        <f t="shared" ref="BW87:CA87" si="150">BW48/BW82</f>
+        <f t="shared" ref="BW87:CA87" si="152">BW48/BW82</f>
         <v>0.18294458811418815</v>
       </c>
       <c r="BX87" s="47">
-        <f t="shared" si="150"/>
+        <f t="shared" si="152"/>
         <v>0.23718724960388465</v>
       </c>
       <c r="BY87" s="47">
-        <f t="shared" si="150"/>
+        <f t="shared" si="152"/>
         <v>0.12491452508251358</v>
       </c>
       <c r="BZ87" s="47">
-        <f t="shared" si="150"/>
+        <f t="shared" si="152"/>
         <v>0.17027039974218611</v>
       </c>
       <c r="CA87" s="47">
-        <f t="shared" si="150"/>
+        <f t="shared" si="152"/>
         <v>0.22589783158367566</v>
       </c>
     </row>
@@ -33188,71 +33277,71 @@
         <v>123</v>
       </c>
       <c r="AL88" s="47">
-        <f t="shared" ref="AL88:BB88" si="151">AL48/AL81</f>
+        <f t="shared" ref="AL88:BB88" si="153">AL48/AL81</f>
         <v>8.745810273598878E-2</v>
       </c>
       <c r="AM88" s="47">
-        <f t="shared" si="151"/>
+        <f t="shared" si="153"/>
         <v>7.1055013953627566E-2</v>
       </c>
       <c r="AN88" s="47">
-        <f t="shared" si="151"/>
+        <f t="shared" si="153"/>
         <v>7.5195150006872755E-2</v>
       </c>
       <c r="AO88" s="47">
-        <f t="shared" si="151"/>
+        <f t="shared" si="153"/>
         <v>6.8941211757648474E-2</v>
       </c>
       <c r="AP88" s="47">
-        <f t="shared" si="151"/>
+        <f t="shared" si="153"/>
         <v>8.2359724213038221E-2</v>
       </c>
       <c r="AQ88" s="47">
-        <f t="shared" si="151"/>
+        <f t="shared" si="153"/>
         <v>6.0578764566494629E-2</v>
       </c>
       <c r="AR88" s="47">
-        <f t="shared" si="151"/>
+        <f t="shared" si="153"/>
         <v>5.3169750411475189E-2</v>
       </c>
       <c r="AS88" s="47">
-        <f t="shared" si="151"/>
+        <f t="shared" si="153"/>
         <v>3.5416700243363901E-2</v>
       </c>
       <c r="AT88" s="47">
-        <f t="shared" si="151"/>
+        <f t="shared" si="153"/>
         <v>3.7012878540803255E-2</v>
       </c>
       <c r="AU88" s="47">
-        <f t="shared" si="151"/>
+        <f t="shared" si="153"/>
         <v>4.5747025121198763E-2</v>
       </c>
       <c r="AV88" s="47">
-        <f t="shared" si="151"/>
+        <f t="shared" si="153"/>
         <v>5.8105093521744644E-2</v>
       </c>
       <c r="AW88" s="47">
-        <f t="shared" si="151"/>
+        <f t="shared" si="153"/>
         <v>8.1072001007888125E-2</v>
       </c>
       <c r="AX88" s="47">
-        <f t="shared" si="151"/>
+        <f t="shared" si="153"/>
         <v>9.1520422020265335E-2</v>
       </c>
       <c r="AY88" s="47">
-        <f t="shared" si="151"/>
+        <f t="shared" si="153"/>
         <v>8.271973998354834E-2</v>
       </c>
       <c r="AZ88" s="47">
-        <f t="shared" si="151"/>
+        <f t="shared" si="153"/>
         <v>8.5893992842698857E-2</v>
       </c>
       <c r="BA88" s="47">
-        <f t="shared" si="151"/>
+        <f t="shared" si="153"/>
         <v>9.5350971561244516E-2</v>
       </c>
       <c r="BB88" s="47">
-        <f t="shared" si="151"/>
+        <f t="shared" si="153"/>
         <v>0.11409517239113652</v>
       </c>
       <c r="BC88" s="47">
@@ -33268,23 +33357,23 @@
         <v>1.3959168530293817E-2</v>
       </c>
       <c r="BW88" s="47">
-        <f t="shared" ref="BW88:CA88" si="152">BW48/BW81</f>
+        <f t="shared" ref="BW88:CA88" si="154">BW48/BW81</f>
         <v>0.22718840127835374</v>
       </c>
       <c r="BX88" s="47">
-        <f t="shared" si="152"/>
+        <f t="shared" si="154"/>
         <v>0.31526517669103693</v>
       </c>
       <c r="BY88" s="47">
-        <f t="shared" si="152"/>
+        <f t="shared" si="154"/>
         <v>0.18454734196145187</v>
       </c>
       <c r="BZ88" s="47">
-        <f t="shared" si="152"/>
+        <f t="shared" si="154"/>
         <v>0.25526219575890524</v>
       </c>
       <c r="CA88" s="47">
-        <f t="shared" si="152"/>
+        <f t="shared" si="154"/>
         <v>0.34144231453648494</v>
       </c>
     </row>
@@ -33296,211 +33385,211 @@
         <v>124</v>
       </c>
       <c r="C90" s="1">
-        <f t="shared" ref="C90:BB90" si="153">C48</f>
+        <f t="shared" ref="C90:BB90" si="155">C48</f>
         <v>205</v>
       </c>
       <c r="D90" s="1">
-        <f t="shared" si="153"/>
+        <f t="shared" si="155"/>
         <v>-157</v>
       </c>
       <c r="E90" s="1">
-        <f t="shared" si="153"/>
+        <f t="shared" si="155"/>
         <v>-59</v>
       </c>
       <c r="F90" s="1">
-        <f t="shared" si="153"/>
+        <f t="shared" si="155"/>
         <v>64</v>
       </c>
       <c r="G90" s="1">
-        <f t="shared" si="153"/>
+        <f t="shared" si="155"/>
         <v>219</v>
       </c>
       <c r="H90" s="1">
-        <f t="shared" si="153"/>
+        <f t="shared" si="155"/>
         <v>333</v>
       </c>
       <c r="I90" s="1">
-        <f t="shared" si="153"/>
+        <f t="shared" si="155"/>
         <v>425</v>
       </c>
       <c r="J90" s="1">
-        <f t="shared" si="153"/>
+        <f t="shared" si="155"/>
         <v>523</v>
       </c>
       <c r="K90" s="1">
-        <f t="shared" si="153"/>
+        <f t="shared" si="155"/>
         <v>642</v>
       </c>
       <c r="L90" s="1">
-        <f t="shared" si="153"/>
+        <f t="shared" si="155"/>
         <v>791</v>
       </c>
       <c r="M90" s="1">
-        <f t="shared" si="153"/>
+        <f t="shared" si="155"/>
         <v>806</v>
       </c>
       <c r="N90" s="1">
-        <f t="shared" si="153"/>
+        <f t="shared" si="155"/>
         <v>701</v>
       </c>
       <c r="O90" s="1">
-        <f t="shared" si="153"/>
+        <f t="shared" si="155"/>
         <v>512</v>
       </c>
       <c r="P90" s="1">
-        <f t="shared" si="153"/>
+        <f t="shared" si="155"/>
         <v>719</v>
       </c>
       <c r="Q90" s="1">
-        <f t="shared" si="153"/>
+        <f t="shared" si="155"/>
         <v>896</v>
       </c>
       <c r="R90" s="1">
-        <f t="shared" si="153"/>
+        <f t="shared" si="155"/>
         <v>1561</v>
       </c>
       <c r="S90" s="1">
-        <f t="shared" si="153"/>
+        <f t="shared" si="155"/>
         <v>1738</v>
       </c>
       <c r="T90" s="1">
-        <f t="shared" si="153"/>
+        <f t="shared" si="155"/>
         <v>2283</v>
       </c>
       <c r="U90" s="1">
-        <f t="shared" si="153"/>
+        <f t="shared" si="155"/>
         <v>2627</v>
       </c>
       <c r="V90" s="1">
-        <f t="shared" si="153"/>
+        <f t="shared" si="155"/>
         <v>3569</v>
       </c>
       <c r="W90" s="1">
-        <f t="shared" si="153"/>
+        <f t="shared" si="155"/>
         <v>3064</v>
       </c>
       <c r="X90" s="1">
-        <f t="shared" si="153"/>
+        <f t="shared" si="155"/>
         <v>3894</v>
       </c>
       <c r="Y90" s="1">
-        <f t="shared" si="153"/>
+        <f t="shared" si="155"/>
         <v>4707</v>
       </c>
       <c r="Z90" s="1">
-        <f t="shared" si="153"/>
+        <f t="shared" si="155"/>
         <v>4269</v>
       </c>
       <c r="AA90" s="1">
-        <f t="shared" si="153"/>
+        <f t="shared" si="155"/>
         <v>4988</v>
       </c>
       <c r="AB90" s="1">
-        <f t="shared" si="153"/>
+        <f t="shared" si="155"/>
         <v>5106</v>
       </c>
       <c r="AC90" s="1">
-        <f t="shared" si="153"/>
+        <f t="shared" si="155"/>
         <v>5137</v>
       </c>
       <c r="AD90" s="1">
-        <f t="shared" si="153"/>
+        <f t="shared" si="155"/>
         <v>6881</v>
       </c>
       <c r="AE90" s="1">
-        <f t="shared" si="153"/>
+        <f t="shared" si="155"/>
         <v>2429</v>
       </c>
       <c r="AF90" s="1">
-        <f t="shared" si="153"/>
+        <f t="shared" si="155"/>
         <v>2616</v>
       </c>
       <c r="AG90" s="1">
-        <f t="shared" si="153"/>
+        <f t="shared" si="155"/>
         <v>6091</v>
       </c>
       <c r="AH90" s="1">
-        <f t="shared" si="153"/>
+        <f t="shared" si="155"/>
         <v>7349</v>
       </c>
       <c r="AI90" s="1">
-        <f t="shared" si="153"/>
+        <f t="shared" si="155"/>
         <v>4902</v>
       </c>
       <c r="AJ90" s="1">
-        <f t="shared" si="153"/>
+        <f t="shared" si="155"/>
         <v>5178</v>
       </c>
       <c r="AK90" s="1">
-        <f t="shared" si="153"/>
+        <f t="shared" si="155"/>
         <v>7846</v>
       </c>
       <c r="AL90" s="1">
-        <f t="shared" si="153"/>
+        <f t="shared" si="155"/>
         <v>11220</v>
       </c>
       <c r="AM90" s="1">
-        <f t="shared" si="153"/>
+        <f t="shared" si="155"/>
         <v>9497</v>
       </c>
       <c r="AN90" s="1">
-        <f t="shared" si="153"/>
+        <f t="shared" si="155"/>
         <v>10394</v>
       </c>
       <c r="AO90" s="1">
-        <f t="shared" si="153"/>
+        <f t="shared" si="155"/>
         <v>9194</v>
       </c>
       <c r="AP90" s="1">
-        <f t="shared" si="153"/>
+        <f t="shared" si="155"/>
         <v>10285</v>
       </c>
       <c r="AQ90" s="1">
-        <f t="shared" si="153"/>
+        <f t="shared" si="155"/>
         <v>7465</v>
       </c>
       <c r="AR90" s="1">
-        <f t="shared" si="153"/>
+        <f t="shared" si="155"/>
         <v>6687</v>
       </c>
       <c r="AS90" s="1">
-        <f t="shared" si="153"/>
+        <f t="shared" si="155"/>
         <v>4395</v>
       </c>
       <c r="AT90" s="1">
-        <f t="shared" si="153"/>
+        <f t="shared" si="155"/>
         <v>4653</v>
       </c>
       <c r="AU90" s="1">
-        <f t="shared" si="153"/>
+        <f t="shared" si="155"/>
         <v>5709</v>
       </c>
       <c r="AV90" s="1">
-        <f t="shared" si="153"/>
+        <f t="shared" si="155"/>
         <v>7788</v>
       </c>
       <c r="AW90" s="1">
-        <f t="shared" si="153"/>
+        <f t="shared" si="155"/>
         <v>11583</v>
       </c>
       <c r="AX90" s="1">
-        <f t="shared" si="153"/>
+        <f t="shared" si="155"/>
         <v>14018</v>
       </c>
       <c r="AY90" s="1">
-        <f t="shared" si="153"/>
+        <f t="shared" si="155"/>
         <v>12369</v>
       </c>
       <c r="AZ90" s="1">
-        <f t="shared" si="153"/>
+        <f t="shared" si="155"/>
         <v>13465</v>
       </c>
       <c r="BA90" s="1">
-        <f t="shared" si="153"/>
+        <f t="shared" si="155"/>
         <v>15688</v>
       </c>
       <c r="BB90" s="1">
-        <f t="shared" si="153"/>
+        <f t="shared" si="155"/>
         <v>20838</v>
       </c>
       <c r="BC90" s="1">
@@ -33520,47 +33609,47 @@
         <v>53</v>
       </c>
       <c r="BP90" s="1">
-        <f t="shared" ref="BP90:BP95" si="154">SUM(G90:J90)</f>
+        <f t="shared" ref="BP90:BP95" si="156">SUM(G90:J90)</f>
         <v>1500</v>
       </c>
       <c r="BQ90" s="1">
-        <f t="shared" ref="BQ90:BQ95" si="155">SUM(K90:N90)</f>
+        <f t="shared" ref="BQ90:BQ95" si="157">SUM(K90:N90)</f>
         <v>2940</v>
       </c>
       <c r="BR90" s="1">
-        <f t="shared" ref="BR90:BR95" si="156">SUM(O90:R90)</f>
+        <f t="shared" ref="BR90:BR95" si="158">SUM(O90:R90)</f>
         <v>3688</v>
       </c>
       <c r="BS90" s="1">
-        <f t="shared" ref="BS90:BS95" si="157">SUM(S90:V90)</f>
+        <f t="shared" ref="BS90:BS95" si="159">SUM(S90:V90)</f>
         <v>10217</v>
       </c>
       <c r="BT90" s="1">
-        <f t="shared" ref="BT90:BT95" si="158">SUM(W90:Z90)</f>
+        <f t="shared" ref="BT90:BT95" si="160">SUM(W90:Z90)</f>
         <v>15934</v>
       </c>
       <c r="BU90" s="1">
-        <f t="shared" ref="BU90:BU95" si="159">SUM(AA90:AD90)</f>
+        <f t="shared" ref="BU90:BU95" si="161">SUM(AA90:AD90)</f>
         <v>22112</v>
       </c>
       <c r="BV90" s="1">
-        <f t="shared" ref="BV90:BV95" si="160">SUM(AE90:AH90)</f>
+        <f t="shared" ref="BV90:BV95" si="162">SUM(AE90:AH90)</f>
         <v>18485</v>
       </c>
       <c r="BW90" s="1">
-        <f t="shared" ref="BW90:BZ90" si="161">BW48</f>
+        <f t="shared" ref="BW90:BZ90" si="163">BW48</f>
         <v>29146</v>
       </c>
       <c r="BX90" s="1">
-        <f t="shared" si="161"/>
+        <f t="shared" si="163"/>
         <v>39370</v>
       </c>
       <c r="BY90" s="1">
-        <f t="shared" si="161"/>
+        <f t="shared" si="163"/>
         <v>23200</v>
       </c>
       <c r="BZ90" s="1">
-        <f t="shared" si="161"/>
+        <f t="shared" si="163"/>
         <v>39098</v>
       </c>
       <c r="CA90" s="1">
@@ -33747,31 +33836,31 @@
         <v>1612</v>
       </c>
       <c r="BP91" s="2">
-        <f t="shared" si="154"/>
+        <f t="shared" si="156"/>
         <v>4222</v>
       </c>
       <c r="BQ91" s="2">
-        <f t="shared" si="155"/>
+        <f t="shared" si="157"/>
         <v>7326</v>
       </c>
       <c r="BR91" s="2">
-        <f t="shared" si="156"/>
+        <f t="shared" si="158"/>
         <v>10320</v>
       </c>
       <c r="BS91" s="2">
-        <f t="shared" si="157"/>
+        <f t="shared" si="159"/>
         <v>16108</v>
       </c>
       <c r="BT91" s="2">
-        <f t="shared" si="158"/>
+        <f t="shared" si="160"/>
         <v>24216</v>
       </c>
       <c r="BU91" s="2">
-        <f t="shared" si="159"/>
+        <f t="shared" si="161"/>
         <v>29274</v>
       </c>
       <c r="BV91" s="2">
-        <f t="shared" si="160"/>
+        <f t="shared" si="162"/>
         <v>36314</v>
       </c>
       <c r="BW91" s="2">
@@ -34031,31 +34120,31 @@
         <v>-1235</v>
       </c>
       <c r="BP92" s="1">
-        <f t="shared" si="154"/>
+        <f t="shared" si="156"/>
         <v>-1362</v>
       </c>
       <c r="BQ92" s="1">
-        <f t="shared" si="155"/>
+        <f t="shared" si="157"/>
         <v>-1831</v>
       </c>
       <c r="BR92" s="1">
-        <f t="shared" si="156"/>
+        <f t="shared" si="158"/>
         <v>-2523</v>
       </c>
       <c r="BS92" s="1">
-        <f t="shared" si="157"/>
+        <f t="shared" si="159"/>
         <v>-4491</v>
       </c>
       <c r="BT92" s="1">
-        <f t="shared" si="158"/>
+        <f t="shared" si="160"/>
         <v>-6733</v>
       </c>
       <c r="BU92" s="1">
-        <f t="shared" si="159"/>
+        <f t="shared" si="161"/>
         <v>-13915</v>
       </c>
       <c r="BV92" s="1">
-        <f t="shared" si="160"/>
+        <f t="shared" si="162"/>
         <v>-15102</v>
       </c>
       <c r="BW92" s="1">
@@ -34084,211 +34173,211 @@
         <v>127</v>
       </c>
       <c r="C93" s="2">
-        <f t="shared" ref="C93:BB93" si="162">C91+C92</f>
+        <f t="shared" ref="C93:BB93" si="164">C91+C92</f>
         <v>-12</v>
       </c>
       <c r="D93" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="164"/>
         <v>-173</v>
       </c>
       <c r="E93" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="164"/>
         <v>79</v>
       </c>
       <c r="F93" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="164"/>
         <v>483</v>
       </c>
       <c r="G93" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="164"/>
         <v>392</v>
       </c>
       <c r="H93" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="164"/>
         <v>1054</v>
       </c>
       <c r="I93" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="164"/>
         <v>666</v>
       </c>
       <c r="J93" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="164"/>
         <v>748</v>
       </c>
       <c r="K93" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="164"/>
         <v>922</v>
       </c>
       <c r="L93" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="164"/>
         <v>872</v>
       </c>
       <c r="M93" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="164"/>
         <v>766</v>
       </c>
       <c r="N93" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="164"/>
         <v>2935</v>
       </c>
       <c r="O93" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="164"/>
         <v>1198</v>
       </c>
       <c r="P93" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="164"/>
         <v>1331</v>
       </c>
       <c r="Q93" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="164"/>
         <v>1412</v>
       </c>
       <c r="R93" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="164"/>
         <v>3856</v>
       </c>
       <c r="S93" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="164"/>
         <v>2345</v>
       </c>
       <c r="T93" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="164"/>
         <v>2670</v>
       </c>
       <c r="U93" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="164"/>
         <v>2941</v>
       </c>
       <c r="V93" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="164"/>
         <v>3661</v>
       </c>
       <c r="W93" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="164"/>
         <v>3787</v>
       </c>
       <c r="X93" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="164"/>
         <v>3916</v>
       </c>
       <c r="Y93" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="164"/>
         <v>4372</v>
       </c>
       <c r="Z93" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="164"/>
         <v>5408</v>
       </c>
       <c r="AA93" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="164"/>
         <v>5048</v>
       </c>
       <c r="AB93" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="164"/>
         <v>2838</v>
       </c>
       <c r="AC93" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="164"/>
         <v>4156</v>
       </c>
       <c r="AD93" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="164"/>
         <v>3317</v>
       </c>
       <c r="AE93" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="164"/>
         <v>5471</v>
       </c>
       <c r="AF93" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="164"/>
         <v>4983</v>
       </c>
       <c r="AG93" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="164"/>
         <v>5775</v>
       </c>
       <c r="AH93" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="164"/>
         <v>4983</v>
       </c>
       <c r="AI93" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="164"/>
         <v>7443</v>
       </c>
       <c r="AJ93" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="164"/>
         <v>622</v>
       </c>
       <c r="AK93" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="164"/>
         <v>6140</v>
       </c>
       <c r="AL93" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="164"/>
         <v>9427</v>
       </c>
       <c r="AM93" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="164"/>
         <v>7939</v>
       </c>
       <c r="AN93" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="164"/>
         <v>8635</v>
       </c>
       <c r="AO93" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="164"/>
         <v>9776</v>
       </c>
       <c r="AP93" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="164"/>
         <v>12735</v>
       </c>
       <c r="AQ93" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="164"/>
         <v>8761</v>
       </c>
       <c r="AR93" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="164"/>
         <v>4668</v>
       </c>
       <c r="AS93" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="164"/>
         <v>337</v>
       </c>
       <c r="AT93" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="164"/>
         <v>5523</v>
       </c>
       <c r="AU93" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="164"/>
         <v>7175</v>
       </c>
       <c r="AV93" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="164"/>
         <v>11175</v>
       </c>
       <c r="AW93" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="164"/>
         <v>13906</v>
       </c>
       <c r="AX93" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="164"/>
         <v>11812</v>
       </c>
       <c r="AY93" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="164"/>
         <v>12846</v>
       </c>
       <c r="AZ93" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="164"/>
         <v>11197</v>
       </c>
       <c r="BA93" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="164"/>
         <v>16466</v>
       </c>
       <c r="BB93" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="164"/>
         <v>13563</v>
       </c>
       <c r="BC93" s="2">
@@ -34313,47 +34402,47 @@
         <v>377</v>
       </c>
       <c r="BP93" s="2">
-        <f t="shared" si="154"/>
+        <f t="shared" si="156"/>
         <v>2860</v>
       </c>
       <c r="BQ93" s="2">
-        <f t="shared" si="155"/>
+        <f t="shared" si="157"/>
         <v>5495</v>
       </c>
       <c r="BR93" s="2">
-        <f t="shared" si="156"/>
+        <f t="shared" si="158"/>
         <v>7797</v>
       </c>
       <c r="BS93" s="2">
-        <f t="shared" si="157"/>
+        <f t="shared" si="159"/>
         <v>11617</v>
       </c>
       <c r="BT93" s="2">
-        <f t="shared" si="158"/>
+        <f t="shared" si="160"/>
         <v>17483</v>
       </c>
       <c r="BU93" s="2">
-        <f t="shared" si="159"/>
+        <f t="shared" si="161"/>
         <v>15359</v>
       </c>
       <c r="BV93" s="2">
-        <f t="shared" si="160"/>
+        <f t="shared" si="162"/>
         <v>21212</v>
       </c>
       <c r="BW93" s="2">
-        <f t="shared" ref="BW93:BZ93" si="163">BW91+BW92</f>
+        <f t="shared" ref="BW93:BZ93" si="165">BW91+BW92</f>
         <v>23632</v>
       </c>
       <c r="BX93" s="2">
-        <f t="shared" si="163"/>
+        <f t="shared" si="165"/>
         <v>39085</v>
       </c>
       <c r="BY93" s="2">
-        <f t="shared" si="163"/>
+        <f t="shared" si="165"/>
         <v>19289</v>
       </c>
       <c r="BZ93" s="2">
-        <f t="shared" si="163"/>
+        <f t="shared" si="165"/>
         <v>44068</v>
       </c>
       <c r="CA93" s="2">
@@ -34428,7 +34517,7 @@
         <v>128</v>
       </c>
       <c r="C94" s="1">
-        <f t="shared" ref="C94:BB94" si="164">C49</f>
+        <f t="shared" ref="C94:BB94" si="166">C49</f>
         <v>1347</v>
       </c>
       <c r="D94" s="1">
@@ -34448,191 +34537,191 @@
         <v>2386</v>
       </c>
       <c r="H94" s="1">
-        <f t="shared" si="164"/>
+        <f t="shared" si="166"/>
         <v>2407</v>
       </c>
       <c r="I94" s="1">
-        <f t="shared" si="164"/>
+        <f t="shared" si="166"/>
         <v>2430</v>
       </c>
       <c r="J94" s="1">
-        <f t="shared" si="164"/>
+        <f t="shared" si="166"/>
         <v>2420</v>
       </c>
       <c r="K94" s="1">
-        <f t="shared" si="164"/>
+        <f t="shared" si="166"/>
         <v>2545</v>
       </c>
       <c r="L94" s="1">
-        <f t="shared" si="164"/>
+        <f t="shared" si="166"/>
         <v>2560</v>
       </c>
       <c r="M94" s="1">
-        <f t="shared" si="164"/>
+        <f t="shared" si="166"/>
         <v>2587</v>
       </c>
       <c r="N94" s="1">
-        <f t="shared" si="164"/>
+        <f t="shared" si="166"/>
         <v>2614</v>
       </c>
       <c r="O94" s="1">
-        <f t="shared" si="164"/>
+        <f t="shared" si="166"/>
         <v>2784</v>
       </c>
       <c r="P94" s="1">
-        <f t="shared" si="164"/>
+        <f t="shared" si="166"/>
         <v>2796</v>
       </c>
       <c r="Q94" s="1">
-        <f t="shared" si="164"/>
+        <f t="shared" si="166"/>
         <v>2808</v>
       </c>
       <c r="R94" s="1">
-        <f t="shared" si="164"/>
+        <f t="shared" si="166"/>
         <v>2803</v>
       </c>
       <c r="S94" s="1">
-        <f t="shared" si="164"/>
+        <f t="shared" si="166"/>
         <v>2843</v>
       </c>
       <c r="T94" s="1">
-        <f t="shared" si="164"/>
+        <f t="shared" si="166"/>
         <v>2856</v>
       </c>
       <c r="U94" s="1">
-        <f t="shared" si="164"/>
+        <f t="shared" si="166"/>
         <v>2871</v>
       </c>
       <c r="V94" s="1">
-        <f t="shared" si="164"/>
+        <f t="shared" si="166"/>
         <v>2863</v>
       </c>
       <c r="W94" s="1">
-        <f t="shared" si="164"/>
+        <f t="shared" si="166"/>
         <v>2891</v>
       </c>
       <c r="X94" s="1">
-        <f t="shared" si="164"/>
+        <f t="shared" si="166"/>
         <v>2900</v>
       </c>
       <c r="Y94" s="1">
-        <f t="shared" si="164"/>
+        <f t="shared" si="166"/>
         <v>2904</v>
       </c>
       <c r="Z94" s="1">
-        <f t="shared" si="164"/>
+        <f t="shared" si="166"/>
         <v>2901</v>
       </c>
       <c r="AA94" s="1">
-        <f t="shared" si="164"/>
+        <f t="shared" si="166"/>
         <v>2906</v>
       </c>
       <c r="AB94" s="1">
-        <f t="shared" si="164"/>
+        <f t="shared" si="166"/>
         <v>2895</v>
       </c>
       <c r="AC94" s="1">
-        <f t="shared" si="164"/>
+        <f t="shared" si="166"/>
         <v>2885</v>
       </c>
       <c r="AD94" s="1">
-        <f t="shared" si="164"/>
+        <f t="shared" si="166"/>
         <v>2890</v>
       </c>
       <c r="AE94" s="1">
-        <f t="shared" si="164"/>
+        <f t="shared" si="166"/>
         <v>2856</v>
       </c>
       <c r="AF94" s="1">
-        <f t="shared" si="164"/>
+        <f t="shared" si="166"/>
         <v>2855</v>
       </c>
       <c r="AG94" s="1">
-        <f t="shared" si="164"/>
+        <f t="shared" si="166"/>
         <v>2854</v>
       </c>
       <c r="AH94" s="1">
-        <f t="shared" si="164"/>
+        <f t="shared" si="166"/>
         <v>2854</v>
       </c>
       <c r="AI94" s="1">
-        <f t="shared" si="164"/>
+        <f t="shared" si="166"/>
         <v>2851</v>
       </c>
       <c r="AJ94" s="1">
-        <f t="shared" si="164"/>
+        <f t="shared" si="166"/>
         <v>2850</v>
       </c>
       <c r="AK94" s="1">
-        <f t="shared" si="164"/>
+        <f t="shared" si="166"/>
         <v>2850</v>
       </c>
       <c r="AL94" s="1">
-        <f t="shared" si="164"/>
+        <f t="shared" si="166"/>
         <v>2851</v>
       </c>
       <c r="AM94" s="1">
-        <f t="shared" si="164"/>
+        <f t="shared" si="166"/>
         <v>2847</v>
       </c>
       <c r="AN94" s="1">
-        <f t="shared" si="164"/>
+        <f t="shared" si="166"/>
         <v>2834</v>
       </c>
       <c r="AO94" s="1">
-        <f t="shared" si="164"/>
+        <f t="shared" si="166"/>
         <v>2814</v>
       </c>
       <c r="AP94" s="1">
-        <f t="shared" si="164"/>
+        <f t="shared" si="166"/>
         <v>2815</v>
       </c>
       <c r="AQ94" s="1">
-        <f t="shared" si="164"/>
+        <f t="shared" si="166"/>
         <v>2725</v>
       </c>
       <c r="AR94" s="1">
-        <f t="shared" si="164"/>
+        <f t="shared" si="166"/>
         <v>2704</v>
       </c>
       <c r="AS94" s="1">
-        <f t="shared" si="164"/>
+        <f t="shared" si="166"/>
         <v>2682</v>
       </c>
       <c r="AT94" s="1">
-        <f t="shared" si="164"/>
+        <f t="shared" si="166"/>
         <v>2687</v>
       </c>
       <c r="AU94" s="1">
-        <f t="shared" si="164"/>
+        <f t="shared" si="166"/>
         <v>2587</v>
       </c>
       <c r="AV94" s="1">
-        <f t="shared" si="164"/>
+        <f t="shared" si="166"/>
         <v>2568</v>
       </c>
       <c r="AW94" s="1">
-        <f t="shared" si="164"/>
+        <f t="shared" si="166"/>
         <v>2576</v>
       </c>
       <c r="AX94" s="1">
-        <f t="shared" si="164"/>
+        <f t="shared" si="166"/>
         <v>2574</v>
       </c>
       <c r="AY94" s="1">
-        <f t="shared" si="164"/>
+        <f t="shared" si="166"/>
         <v>2545</v>
       </c>
       <c r="AZ94" s="1">
-        <f t="shared" si="164"/>
+        <f t="shared" si="166"/>
         <v>2534</v>
       </c>
       <c r="BA94" s="1">
-        <f t="shared" si="164"/>
+        <f t="shared" si="166"/>
         <v>2529</v>
       </c>
       <c r="BB94" s="1">
-        <f t="shared" si="164"/>
+        <f t="shared" si="166"/>
         <v>2534</v>
       </c>
       <c r="BC94" s="1">
@@ -34652,47 +34741,47 @@
         <v>1882</v>
       </c>
       <c r="BP94" s="1">
-        <f t="shared" si="154"/>
+        <f t="shared" si="156"/>
         <v>9643</v>
       </c>
       <c r="BQ94" s="1">
-        <f t="shared" si="155"/>
+        <f t="shared" si="157"/>
         <v>10306</v>
       </c>
       <c r="BR94" s="1">
-        <f t="shared" si="156"/>
+        <f t="shared" si="158"/>
         <v>11191</v>
       </c>
       <c r="BS94" s="1">
-        <f t="shared" si="157"/>
+        <f t="shared" si="159"/>
         <v>11433</v>
       </c>
       <c r="BT94" s="1">
-        <f t="shared" si="158"/>
+        <f t="shared" si="160"/>
         <v>11596</v>
       </c>
       <c r="BU94" s="1">
-        <f t="shared" si="159"/>
+        <f t="shared" si="161"/>
         <v>11576</v>
       </c>
       <c r="BV94" s="1">
-        <f t="shared" si="160"/>
+        <f t="shared" si="162"/>
         <v>11419</v>
       </c>
       <c r="BW94" s="1">
-        <f t="shared" ref="BW94:BZ94" si="165">BW49</f>
+        <f t="shared" ref="BW94:BZ94" si="167">BW49</f>
         <v>2850.5</v>
       </c>
       <c r="BX94" s="1">
-        <f t="shared" si="165"/>
+        <f t="shared" si="167"/>
         <v>2827.5</v>
       </c>
       <c r="BY94" s="1">
-        <f t="shared" si="165"/>
+        <f t="shared" si="167"/>
         <v>2699.5</v>
       </c>
       <c r="BZ94" s="1">
-        <f t="shared" si="165"/>
+        <f t="shared" si="167"/>
         <v>2576.25</v>
       </c>
       <c r="CA94" s="1">
@@ -34705,211 +34794,211 @@
         <v>129</v>
       </c>
       <c r="C95" s="39">
-        <f t="shared" ref="C95:BB95" si="166">C93/C94</f>
+        <f t="shared" ref="C95:BB95" si="168">C93/C94</f>
         <v>-8.9086859688195987E-3</v>
       </c>
       <c r="D95" s="39">
-        <f t="shared" si="166"/>
+        <f t="shared" si="168"/>
         <v>-0.12843355605048257</v>
       </c>
       <c r="E95" s="39">
-        <f t="shared" si="166"/>
+        <f t="shared" si="168"/>
         <v>4.2043640234167109E-2</v>
       </c>
       <c r="F95" s="39">
-        <f t="shared" si="166"/>
+        <f t="shared" si="168"/>
         <v>0.19958677685950413</v>
       </c>
       <c r="G95" s="39">
-        <f t="shared" si="166"/>
+        <f t="shared" si="168"/>
         <v>0.16429170159262363</v>
       </c>
       <c r="H95" s="39">
-        <f t="shared" si="166"/>
+        <f t="shared" si="168"/>
         <v>0.43788948899044455</v>
       </c>
       <c r="I95" s="39">
-        <f t="shared" si="166"/>
+        <f t="shared" si="168"/>
         <v>0.27407407407407408</v>
       </c>
       <c r="J95" s="39">
-        <f t="shared" si="166"/>
+        <f t="shared" si="168"/>
         <v>0.30909090909090908</v>
       </c>
       <c r="K95" s="39">
-        <f t="shared" si="166"/>
+        <f t="shared" si="168"/>
         <v>0.36227897838899803</v>
       </c>
       <c r="L95" s="39">
-        <f t="shared" si="166"/>
+        <f t="shared" si="168"/>
         <v>0.34062500000000001</v>
       </c>
       <c r="M95" s="39">
-        <f t="shared" si="166"/>
+        <f t="shared" si="168"/>
         <v>0.29609586393505993</v>
       </c>
       <c r="N95" s="39">
-        <f t="shared" si="166"/>
+        <f t="shared" si="168"/>
         <v>1.1228003060443765</v>
       </c>
       <c r="O95" s="39">
-        <f t="shared" si="166"/>
+        <f t="shared" si="168"/>
         <v>0.43031609195402298</v>
       </c>
       <c r="P95" s="39">
-        <f t="shared" si="166"/>
+        <f t="shared" si="168"/>
         <v>0.47603719599427752</v>
       </c>
       <c r="Q95" s="39">
-        <f t="shared" si="166"/>
+        <f t="shared" si="168"/>
         <v>0.5028490028490028</v>
       </c>
       <c r="R95" s="39">
-        <f t="shared" si="166"/>
+        <f t="shared" si="168"/>
         <v>1.375668926150553</v>
       </c>
       <c r="S95" s="39">
-        <f t="shared" si="166"/>
+        <f t="shared" si="168"/>
         <v>0.82483292296869504</v>
       </c>
       <c r="T95" s="39">
-        <f t="shared" si="166"/>
+        <f t="shared" si="168"/>
         <v>0.93487394957983194</v>
       </c>
       <c r="U95" s="39">
-        <f t="shared" si="166"/>
+        <f t="shared" si="168"/>
         <v>1.0243817485196796</v>
       </c>
       <c r="V95" s="39">
-        <f t="shared" si="166"/>
+        <f t="shared" si="168"/>
         <v>1.2787286063569683</v>
       </c>
       <c r="W95" s="39">
-        <f t="shared" si="166"/>
+        <f t="shared" si="168"/>
         <v>1.3099273607748183</v>
       </c>
       <c r="X95" s="39">
-        <f t="shared" si="166"/>
+        <f t="shared" si="168"/>
         <v>1.3503448275862069</v>
       </c>
       <c r="Y95" s="39">
-        <f t="shared" si="166"/>
+        <f t="shared" si="168"/>
         <v>1.5055096418732783</v>
       </c>
       <c r="Z95" s="39">
-        <f t="shared" si="166"/>
+        <f t="shared" si="168"/>
         <v>1.8641847638745259</v>
       </c>
       <c r="AA95" s="39">
-        <f t="shared" si="166"/>
+        <f t="shared" si="168"/>
         <v>1.7370956641431521</v>
       </c>
       <c r="AB95" s="39">
-        <f t="shared" si="166"/>
+        <f t="shared" si="168"/>
         <v>0.98031088082901552</v>
       </c>
       <c r="AC95" s="39">
-        <f t="shared" si="166"/>
+        <f t="shared" si="168"/>
         <v>1.4405545927209706</v>
       </c>
       <c r="AD95" s="39">
-        <f t="shared" si="166"/>
+        <f t="shared" si="168"/>
         <v>1.147750865051903</v>
       </c>
       <c r="AE95" s="39">
-        <f t="shared" si="166"/>
+        <f t="shared" si="168"/>
         <v>1.9156162464985995</v>
       </c>
       <c r="AF95" s="39">
-        <f t="shared" si="166"/>
+        <f t="shared" si="168"/>
         <v>1.7453590192644484</v>
       </c>
       <c r="AG95" s="39">
-        <f t="shared" si="166"/>
+        <f t="shared" si="168"/>
         <v>2.0234758234057462</v>
       </c>
       <c r="AH95" s="39">
-        <f t="shared" si="166"/>
+        <f t="shared" si="168"/>
         <v>1.7459705676243868</v>
       </c>
       <c r="AI95" s="39">
-        <f t="shared" si="166"/>
+        <f t="shared" si="168"/>
         <v>2.6106629252893723</v>
       </c>
       <c r="AJ95" s="39">
-        <f t="shared" si="166"/>
+        <f t="shared" si="168"/>
         <v>0.21824561403508771</v>
       </c>
       <c r="AK95" s="39">
-        <f t="shared" si="166"/>
+        <f t="shared" si="168"/>
         <v>2.1543859649122807</v>
       </c>
       <c r="AL95" s="39">
-        <f t="shared" si="166"/>
+        <f t="shared" si="168"/>
         <v>3.3065591020694494</v>
       </c>
       <c r="AM95" s="39">
-        <f t="shared" si="166"/>
+        <f t="shared" si="168"/>
         <v>2.7885493501931857</v>
       </c>
       <c r="AN95" s="39">
-        <f t="shared" si="166"/>
+        <f t="shared" si="168"/>
         <v>3.0469301340860975</v>
       </c>
       <c r="AO95" s="39">
-        <f t="shared" si="166"/>
+        <f t="shared" si="168"/>
         <v>3.4740582800284292</v>
       </c>
       <c r="AP95" s="39">
-        <f t="shared" si="166"/>
+        <f t="shared" si="168"/>
         <v>4.5239786856127884</v>
       </c>
       <c r="AQ95" s="39">
-        <f t="shared" si="166"/>
+        <f t="shared" si="168"/>
         <v>3.2150458715596328</v>
       </c>
       <c r="AR95" s="39">
-        <f t="shared" si="166"/>
+        <f t="shared" si="168"/>
         <v>1.7263313609467457</v>
       </c>
       <c r="AS95" s="39">
-        <f t="shared" si="166"/>
+        <f t="shared" si="168"/>
         <v>0.1256524981357196</v>
       </c>
       <c r="AT95" s="39">
-        <f t="shared" si="166"/>
+        <f t="shared" si="168"/>
         <v>2.0554521771492369</v>
       </c>
       <c r="AU95" s="39">
-        <f t="shared" si="166"/>
+        <f t="shared" si="168"/>
         <v>2.7734827986084269</v>
       </c>
       <c r="AV95" s="39">
-        <f t="shared" si="166"/>
+        <f t="shared" si="168"/>
         <v>4.3516355140186915</v>
       </c>
       <c r="AW95" s="39">
-        <f t="shared" si="166"/>
+        <f t="shared" si="168"/>
         <v>5.3982919254658386</v>
       </c>
       <c r="AX95" s="39">
-        <f t="shared" si="166"/>
+        <f t="shared" si="168"/>
         <v>4.5889665889665894</v>
       </c>
       <c r="AY95" s="39">
-        <f t="shared" si="166"/>
+        <f t="shared" si="168"/>
         <v>5.0475442043222003</v>
       </c>
       <c r="AZ95" s="39">
-        <f t="shared" si="166"/>
+        <f t="shared" si="168"/>
         <v>4.4187056037884771</v>
       </c>
       <c r="BA95" s="39">
-        <f t="shared" si="166"/>
+        <f t="shared" si="168"/>
         <v>6.5108738631870304</v>
       </c>
       <c r="BB95" s="39">
-        <f t="shared" si="166"/>
+        <f t="shared" si="168"/>
         <v>5.3524072612470404</v>
       </c>
       <c r="BC95" s="39">
@@ -34929,47 +35018,47 @@
         <v>1.0758420415166463</v>
       </c>
       <c r="BP95" s="39">
-        <f t="shared" si="154"/>
+        <f t="shared" si="156"/>
         <v>1.1853461737480513</v>
       </c>
       <c r="BQ95" s="39">
-        <f t="shared" si="155"/>
+        <f t="shared" si="157"/>
         <v>2.1218001483684343</v>
       </c>
       <c r="BR95" s="39">
-        <f t="shared" si="156"/>
+        <f t="shared" si="158"/>
         <v>2.784871216947856</v>
       </c>
       <c r="BS95" s="39">
-        <f t="shared" si="157"/>
+        <f t="shared" si="159"/>
         <v>4.0628172274251746</v>
       </c>
       <c r="BT95" s="39">
-        <f t="shared" si="158"/>
+        <f t="shared" si="160"/>
         <v>6.0299665941088296</v>
       </c>
       <c r="BU95" s="39">
-        <f t="shared" si="159"/>
+        <f t="shared" si="161"/>
         <v>5.3057120027450413</v>
       </c>
       <c r="BV95" s="39">
-        <f t="shared" si="160"/>
+        <f t="shared" si="162"/>
         <v>7.4304216567931807</v>
       </c>
       <c r="BW95" s="39">
-        <f t="shared" ref="BW95:BZ95" si="167">BW93/BW94</f>
+        <f t="shared" ref="BW95:BZ95" si="169">BW93/BW94</f>
         <v>8.2904753552008419</v>
       </c>
       <c r="BX95" s="39">
-        <f t="shared" si="167"/>
+        <f t="shared" si="169"/>
         <v>13.823165340406719</v>
       </c>
       <c r="BY95" s="39">
-        <f t="shared" si="167"/>
+        <f t="shared" si="169"/>
         <v>7.1453972957955179</v>
       </c>
       <c r="BZ95" s="39">
-        <f t="shared" si="167"/>
+        <f t="shared" si="169"/>
         <v>17.105482775351771</v>
       </c>
       <c r="CA95" s="39">

--- a/META_Model.xlsx
+++ b/META_Model.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\OneDrive\Desktop\Equity Research\Models\Communication Services\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC054366-E3D7-4D81-A9A7-8DE95392ED04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EB5F888-2822-4CE7-8A1B-8A16E357A6C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
